--- a/mapping/field_mapping.xlsx
+++ b/mapping/field_mapping.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Water collectives\WHS Assessment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Water collectives\WHS Assessment\auto gen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1D395AB-3C22-484B-AF27-62AD18FBE0E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D71BEE19-B12A-428A-88D5-973C9D0D2442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B03A0D84-276C-499F-A511-71567CA886FB}"/>
   </bookViews>
@@ -84,33 +84,18 @@
     <t>1. Basic Information</t>
   </si>
   <si>
-    <t>geo.district</t>
-  </si>
-  <si>
-    <t>geo.block</t>
-  </si>
-  <si>
     <t>B3</t>
   </si>
   <si>
-    <t>geo.gp</t>
-  </si>
-  <si>
     <t>Grama panchayat</t>
   </si>
   <si>
     <t>Habitation</t>
   </si>
   <si>
-    <t>geo.village</t>
-  </si>
-  <si>
     <t>Name of the Project</t>
   </si>
   <si>
-    <t>geo.project</t>
-  </si>
-  <si>
     <t>Funding</t>
   </si>
   <si>
@@ -121,9 +106,6 @@
   </si>
   <si>
     <t>B8</t>
-  </si>
-  <si>
-    <t>geo.fund</t>
   </si>
   <si>
     <t>Submitted at</t>
@@ -578,126 +560,9 @@
     <t>6. Lead_statement</t>
   </si>
   <si>
-    <t>whs.hhs_covered</t>
-  </si>
-  <si>
-    <t>whs.extent_rabi</t>
-  </si>
-  <si>
-    <t>whs.structure_gps</t>
-  </si>
-  <si>
-    <t>basic_details_repairs.district</t>
-  </si>
-  <si>
-    <t>basic_details_repairs.village</t>
-  </si>
-  <si>
-    <t>discharge.Discarge</t>
-  </si>
-  <si>
-    <t>basic_info.Date</t>
-  </si>
-  <si>
-    <t>jungle_clearance.volume_jc</t>
-  </si>
-  <si>
-    <t>earthwork_dam.earthwork_us</t>
-  </si>
-  <si>
-    <t>earthwork_dam.earthwork_ds</t>
-  </si>
-  <si>
-    <t>earthwork_dam.earthwork_bw</t>
-  </si>
-  <si>
-    <t>Dam_guidewall.volume_apron1</t>
-  </si>
-  <si>
-    <t>Dam_guidewall.volume_apron2</t>
-  </si>
-  <si>
-    <t>cbagw.guidewall_height_cbagw</t>
-  </si>
-  <si>
-    <t>cost.cost_cement_MT</t>
-  </si>
-  <si>
-    <t>cost.cost_sand_cum</t>
-  </si>
-  <si>
-    <t>cost.cost_steel_ton</t>
-  </si>
-  <si>
-    <t>metal.plainroad_kms_mamidipalli_metal</t>
-  </si>
-  <si>
-    <t>metal.ghatroad_kms_mamidipalli_metal</t>
-  </si>
-  <si>
-    <t>sand.plainroad_kms_from_Kothavalasa_sand</t>
-  </si>
-  <si>
-    <t>sand.ghatroad_kms_from_Kothavalasa_sand</t>
-  </si>
-  <si>
-    <t>stone.stone_kms</t>
-  </si>
-  <si>
-    <t>whs.small_marg_hhs%</t>
-  </si>
-  <si>
-    <t>whs.local_name</t>
-  </si>
-  <si>
     <t>Left side dam guide Wall</t>
   </si>
   <si>
-    <t>cd.volume_soil_tobe_removed_canal_cd</t>
-  </si>
-  <si>
-    <t>datd.volume_soil_datd</t>
-  </si>
-  <si>
-    <t>ncg_.basement_soilwork_ncgbs</t>
-  </si>
-  <si>
-    <t>Dam_guidewall.soilwork_abutment_right</t>
-  </si>
-  <si>
-    <t>Dam_guidewall.soilwork_abutment_left</t>
-  </si>
-  <si>
-    <t>Dam_guidewall.cc148_abutment_left</t>
-  </si>
-  <si>
-    <t>Dam_guidewall.cc148_abutment_right</t>
-  </si>
-  <si>
-    <t>Dam_guidewall.soilwork_gw_right</t>
-  </si>
-  <si>
-    <t>Dam_guidewall.soilwork_gw_left</t>
-  </si>
-  <si>
-    <t>Dam_guidewall.cc148_gw_right</t>
-  </si>
-  <si>
-    <t>Dam_guidewall.cc148_gw_left</t>
-  </si>
-  <si>
-    <t>ncg_.volume_cc148_basement_concrete_ncgbs</t>
-  </si>
-  <si>
-    <t>cc124_tobe_filled.total_volume_cc124_tbf_wc</t>
-  </si>
-  <si>
-    <t>tr.volume_tp</t>
-  </si>
-  <si>
-    <t>sand.lead_sand_ktv_km</t>
-  </si>
-  <si>
     <t>lead_metal_mamidipalli_km</t>
   </si>
   <si>
@@ -711,6 +576,141 @@
   </si>
   <si>
     <t>Static</t>
+  </si>
+  <si>
+    <t>geo-district</t>
+  </si>
+  <si>
+    <t>geo-block</t>
+  </si>
+  <si>
+    <t>geo-gp</t>
+  </si>
+  <si>
+    <t>geo-village</t>
+  </si>
+  <si>
+    <t>geo-project</t>
+  </si>
+  <si>
+    <t>geo-fund</t>
+  </si>
+  <si>
+    <t>whs-hhs_covered</t>
+  </si>
+  <si>
+    <t>whs-extent_rabi</t>
+  </si>
+  <si>
+    <t>whs-small_marg_hhs%</t>
+  </si>
+  <si>
+    <t>whs-structure_gps</t>
+  </si>
+  <si>
+    <t>basic_details_repairs-district</t>
+  </si>
+  <si>
+    <t>basic_details_repairs-village</t>
+  </si>
+  <si>
+    <t>whs-local_name</t>
+  </si>
+  <si>
+    <t>discharge-Discarge</t>
+  </si>
+  <si>
+    <t>basic_info-Date</t>
+  </si>
+  <si>
+    <t>jungle_clearance-volume_jc</t>
+  </si>
+  <si>
+    <t>earthwork_dam-earthwork_us</t>
+  </si>
+  <si>
+    <t>earthwork_dam-earthwork_ds</t>
+  </si>
+  <si>
+    <t>earthwork_dam-earthwork_bw</t>
+  </si>
+  <si>
+    <t>Dam_guidewall-soilwork_abutment_right</t>
+  </si>
+  <si>
+    <t>Dam_guidewall-soilwork_abutment_left</t>
+  </si>
+  <si>
+    <t>Dam_guidewall-soilwork_gw_right</t>
+  </si>
+  <si>
+    <t>Dam_guidewall-soilwork_gw_left</t>
+  </si>
+  <si>
+    <t>Dam_guidewall-volume_apron1</t>
+  </si>
+  <si>
+    <t>Dam_guidewall-volume_apron2</t>
+  </si>
+  <si>
+    <t>datd-volume_soil_datd</t>
+  </si>
+  <si>
+    <t>cd-volume_soil_tobe_removed_canal_cd</t>
+  </si>
+  <si>
+    <t>ncg_-basement_soilwork_ncgbs</t>
+  </si>
+  <si>
+    <t>Dam_guidewall-cc148_abutment_right</t>
+  </si>
+  <si>
+    <t>Dam_guidewall-cc148_abutment_left</t>
+  </si>
+  <si>
+    <t>Dam_guidewall-cc148_gw_right</t>
+  </si>
+  <si>
+    <t>Dam_guidewall-cc148_gw_left</t>
+  </si>
+  <si>
+    <t>ncg_-volume_cc148_basement_concrete_ncgbs</t>
+  </si>
+  <si>
+    <t>cbagw-guidewall_height_cbagw</t>
+  </si>
+  <si>
+    <t>cc124_tobe_filled-total_volume_cc124_tbf_wc</t>
+  </si>
+  <si>
+    <t>tr-volume_tp</t>
+  </si>
+  <si>
+    <t>cost-cost_cement_MT</t>
+  </si>
+  <si>
+    <t>cost-cost_sand_cum</t>
+  </si>
+  <si>
+    <t>cost-cost_steel_ton</t>
+  </si>
+  <si>
+    <t>metal-plainroad_kms_mamidipalli_metal</t>
+  </si>
+  <si>
+    <t>metal-ghatroad_kms_mamidipalli_metal</t>
+  </si>
+  <si>
+    <t>sand-plainroad_kms_from_Kothavalasa_sand</t>
+  </si>
+  <si>
+    <t>sand-ghatroad_kms_from_Kothavalasa_sand</t>
+  </si>
+  <si>
+    <t>sand-lead_sand_ktv_km</t>
+  </si>
+  <si>
+    <t>stone-stone_kms</t>
   </si>
 </sst>
 </file>
@@ -948,7 +948,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1103,15 +1103,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1124,7 +1115,6 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1500,16 +1490,16 @@
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="72" t="s">
-        <v>215</v>
+      <c r="J1" s="68" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1529,19 +1519,19 @@
         <v>17</v>
       </c>
       <c r="F2" s="40" t="s">
-        <v>18</v>
+        <v>174</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>10</v>
       </c>
       <c r="J2" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1552,7 +1542,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D3" s="36" t="s">
         <v>12</v>
@@ -1561,19 +1551,19 @@
         <v>17</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>19</v>
+        <v>175</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>10</v>
       </c>
       <c r="J3" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1587,25 +1577,25 @@
         <v>8</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F4" s="41" t="s">
-        <v>21</v>
+        <v>176</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1619,25 +1609,25 @@
         <v>11</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F5" s="41" t="s">
-        <v>24</v>
+        <v>177</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1651,25 +1641,25 @@
         <v>13</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="41" t="s">
-        <v>26</v>
+        <v>178</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1680,28 +1670,28 @@
         <v>7</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F7" s="41" t="s">
-        <v>31</v>
+        <v>179</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>15</v>
       </c>
       <c r="J7" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1712,28 +1702,28 @@
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F8" s="41" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>10</v>
       </c>
       <c r="J8" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1744,24 +1734,24 @@
         <v>7</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="41"/>
       <c r="G9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9" s="73" t="s">
-        <v>38</v>
+        <v>33</v>
+      </c>
+      <c r="H9" s="69" t="s">
+        <v>32</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="74" t="s">
-        <v>218</v>
+      <c r="J9" s="70" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1772,24 +1762,24 @@
         <v>7</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="41"/>
       <c r="G10" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J10" s="74" t="s">
-        <v>218</v>
+      <c r="J10" s="70" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -1800,28 +1790,28 @@
         <v>7</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F11" s="42" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>10</v>
       </c>
       <c r="J11" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1832,28 +1822,28 @@
         <v>7</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="42" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>10</v>
       </c>
       <c r="J12" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -1864,26 +1854,26 @@
         <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="42"/>
       <c r="G13" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="J13" t="s">
-        <v>217</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -1894,28 +1884,28 @@
         <v>7</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="42" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>10</v>
       </c>
       <c r="J14" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -1926,28 +1916,28 @@
         <v>7</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F15" s="43" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I15" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J15" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -1968,28 +1958,28 @@
         <v>14</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F17" s="41" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I17" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J17" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -2001,25 +1991,25 @@
         <v>8</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F18" s="41" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I18" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J18" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2031,21 +2021,21 @@
         <v>11</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E19" s="22"/>
       <c r="F19" s="41"/>
       <c r="G19" s="22" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="J19" t="s">
-        <v>217</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2057,21 +2047,21 @@
         <v>13</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E20" s="22"/>
       <c r="F20" s="41"/>
       <c r="G20" s="22" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="J20" t="s">
-        <v>217</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2080,28 +2070,28 @@
         <v>14</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F21" s="41" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I21" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J21" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2110,28 +2100,28 @@
         <v>14</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F22" s="45" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I22" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J22" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2140,28 +2130,28 @@
         <v>14</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F23" s="45" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H23" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I23" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J23" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
@@ -2170,24 +2160,24 @@
         <v>14</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E24" s="24"/>
       <c r="F24" s="45"/>
       <c r="G24" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H24" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I24" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="J24" s="74" t="s">
-        <v>218</v>
+      <c r="J24" s="70" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
@@ -2196,28 +2186,28 @@
         <v>14</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F25" s="46" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H25" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I25" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J25" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
@@ -2226,24 +2216,24 @@
         <v>14</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E26" s="24"/>
       <c r="F26" s="45"/>
       <c r="G26" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I26" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="J26" s="74" t="s">
-        <v>218</v>
+      <c r="J26" s="70" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2252,28 +2242,28 @@
         <v>14</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F27" s="47" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I27" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J27" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2282,28 +2272,28 @@
         <v>14</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F28" s="47" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I28" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J28" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2312,88 +2302,88 @@
         <v>14</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="D29" s="59" t="s">
-        <v>71</v>
+        <v>43</v>
+      </c>
+      <c r="D29" s="56" t="s">
+        <v>65</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F29" s="47" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I29" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J29" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" s="63" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="56"/>
-      <c r="B30" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" s="58" t="s">
-        <v>52</v>
-      </c>
-      <c r="D30" s="59" t="s">
-        <v>72</v>
-      </c>
-      <c r="E30" s="60" t="s">
-        <v>56</v>
-      </c>
-      <c r="F30" s="61" t="s">
-        <v>202</v>
-      </c>
-      <c r="G30" s="62" t="s">
-        <v>37</v>
-      </c>
-      <c r="H30" s="62" t="s">
-        <v>38</v>
-      </c>
-      <c r="I30" s="58" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="6"/>
+      <c r="B30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="E30" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="F30" s="58" t="s">
+        <v>193</v>
+      </c>
+      <c r="G30" s="59" t="s">
+        <v>31</v>
+      </c>
+      <c r="H30" s="59" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J30" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" s="63" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="56"/>
-      <c r="B31" s="57" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31" s="58" t="s">
-        <v>53</v>
-      </c>
-      <c r="D31" s="59" t="s">
-        <v>73</v>
-      </c>
-      <c r="E31" s="60" t="s">
-        <v>56</v>
-      </c>
-      <c r="F31" s="64" t="s">
-        <v>203</v>
-      </c>
-      <c r="G31" s="62" t="s">
-        <v>37</v>
-      </c>
-      <c r="H31" s="62" t="s">
-        <v>38</v>
-      </c>
-      <c r="I31" s="58" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="6"/>
+      <c r="B31" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D31" s="56" t="s">
+        <v>67</v>
+      </c>
+      <c r="E31" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="F31" s="60" t="s">
+        <v>194</v>
+      </c>
+      <c r="G31" s="59" t="s">
+        <v>31</v>
+      </c>
+      <c r="H31" s="59" t="s">
+        <v>32</v>
+      </c>
+      <c r="I31" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J31" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2402,28 +2392,28 @@
         <v>14</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="F32" s="61" t="s">
-        <v>206</v>
+        <v>50</v>
+      </c>
+      <c r="F32" s="58" t="s">
+        <v>195</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I32" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J32" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2432,28 +2422,28 @@
         <v>14</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D33" s="65" t="s">
-        <v>198</v>
+        <v>110</v>
+      </c>
+      <c r="D33" s="61" t="s">
+        <v>168</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="F33" s="61" t="s">
-        <v>207</v>
+        <v>50</v>
+      </c>
+      <c r="F33" s="58" t="s">
+        <v>196</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I33" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J33" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2462,28 +2452,28 @@
         <v>14</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F34" s="47" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I34" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J34" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2492,28 +2482,28 @@
         <v>14</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E35" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="F35" s="61" t="s">
-        <v>186</v>
+        <v>50</v>
+      </c>
+      <c r="F35" s="58" t="s">
+        <v>198</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I35" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J35" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -2522,28 +2512,28 @@
         <v>14</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="F36" s="64" t="s">
-        <v>200</v>
+        <v>50</v>
+      </c>
+      <c r="F36" s="60" t="s">
+        <v>199</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I36" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J36" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2554,28 +2544,28 @@
         <v>14</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E37" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="F37" s="64" t="s">
-        <v>199</v>
+        <v>50</v>
+      </c>
+      <c r="F37" s="60" t="s">
+        <v>200</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I37" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J37" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2586,28 +2576,28 @@
         <v>14</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D38" s="28" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E38" s="24" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F38" s="50" t="s">
         <v>201</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I38" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J38" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2618,56 +2608,56 @@
         <v>14</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E39" s="24" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F39" s="50" t="s">
         <v>201</v>
       </c>
       <c r="G39" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H39" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="I39" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="J39" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" s="66" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="62"/>
+      <c r="B40" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="64" t="s">
+        <v>117</v>
+      </c>
+      <c r="D40" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="E40" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="F40" s="48"/>
+      <c r="G40" s="65" t="s">
+        <v>31</v>
+      </c>
+      <c r="H40" s="65" t="s">
+        <v>32</v>
+      </c>
+      <c r="I40" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="H39" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="I39" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="J39" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" s="70" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="66"/>
-      <c r="B40" s="67" t="s">
-        <v>14</v>
-      </c>
-      <c r="C40" s="68" t="s">
-        <v>123</v>
-      </c>
-      <c r="D40" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="E40" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="F40" s="48"/>
-      <c r="G40" s="69" t="s">
-        <v>37</v>
-      </c>
-      <c r="H40" s="69" t="s">
-        <v>38</v>
-      </c>
-      <c r="I40" s="66" t="s">
-        <v>43</v>
-      </c>
       <c r="J40" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
@@ -2676,24 +2666,24 @@
         <v>14</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E41" s="30"/>
       <c r="F41" s="51"/>
       <c r="G41" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I41" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="J41" s="74" t="s">
-        <v>218</v>
+      <c r="J41" s="70" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2702,26 +2692,26 @@
         <v>14</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D42" s="21" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E42" s="14"/>
       <c r="F42" s="47" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G42" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I42" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="H42" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I42" s="29" t="s">
-        <v>43</v>
-      </c>
       <c r="J42" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2730,26 +2720,26 @@
         <v>14</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E43" s="14"/>
       <c r="F43" s="47" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G43" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I43" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="H43" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I43" s="29" t="s">
-        <v>43</v>
-      </c>
       <c r="J43" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2758,26 +2748,26 @@
         <v>14</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="47" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I44" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J44" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2786,26 +2776,26 @@
         <v>14</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D45" s="21" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E45" s="14"/>
       <c r="F45" s="47" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="G45" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I45" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="H45" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I45" s="29" t="s">
-        <v>43</v>
-      </c>
       <c r="J45" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2814,26 +2804,26 @@
         <v>14</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E46" s="14"/>
       <c r="F46" s="47" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="G46" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I46" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="H46" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I46" s="29" t="s">
-        <v>43</v>
-      </c>
       <c r="J46" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2842,26 +2832,26 @@
         <v>14</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E47" s="14"/>
-      <c r="F47" s="61" t="s">
-        <v>186</v>
+      <c r="F47" s="58" t="s">
+        <v>198</v>
       </c>
       <c r="G47" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I47" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="H47" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I47" s="29" t="s">
-        <v>43</v>
-      </c>
       <c r="J47" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2870,26 +2860,26 @@
         <v>14</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D48" s="28" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E48" s="31"/>
       <c r="F48" s="52" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G48" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I48" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="H48" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I48" s="29" t="s">
-        <v>43</v>
-      </c>
       <c r="J48" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2898,52 +2888,52 @@
         <v>14</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D49" s="28" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E49" s="31"/>
       <c r="F49" s="52" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G49" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I49" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="H49" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I49" s="29" t="s">
-        <v>43</v>
-      </c>
       <c r="J49" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" s="70" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="66"/>
-      <c r="B50" s="67" t="s">
-        <v>14</v>
-      </c>
-      <c r="C50" s="68" t="s">
-        <v>133</v>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" s="66" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="62"/>
+      <c r="B50" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" s="64" t="s">
+        <v>127</v>
       </c>
       <c r="D50" s="26" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E50" s="27"/>
       <c r="F50" s="48"/>
-      <c r="G50" s="69" t="s">
+      <c r="G50" s="65" t="s">
+        <v>31</v>
+      </c>
+      <c r="H50" s="65" t="s">
+        <v>32</v>
+      </c>
+      <c r="I50" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="H50" s="69" t="s">
-        <v>38</v>
-      </c>
-      <c r="I50" s="66" t="s">
-        <v>43</v>
-      </c>
       <c r="J50" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
@@ -2952,24 +2942,24 @@
         <v>14</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D51" s="25" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E51" s="30"/>
       <c r="F51" s="51"/>
       <c r="G51" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H51" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I51" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="J51" s="74" t="s">
-        <v>218</v>
+      <c r="J51" s="70" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2978,26 +2968,26 @@
         <v>14</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E52" s="14"/>
       <c r="F52" s="47" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="G52" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I52" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="H52" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I52" s="29" t="s">
-        <v>43</v>
-      </c>
       <c r="J52" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3006,26 +2996,26 @@
         <v>14</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E53" s="14"/>
       <c r="F53" s="47" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="G53" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I53" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="H53" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I53" s="29" t="s">
-        <v>43</v>
-      </c>
       <c r="J53" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3034,26 +3024,26 @@
         <v>14</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E54" s="14"/>
       <c r="F54" s="47" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="G54" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I54" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="H54" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I54" s="29" t="s">
-        <v>43</v>
-      </c>
       <c r="J54" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3062,26 +3052,26 @@
         <v>14</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E55" s="14"/>
-      <c r="F55" s="61" t="s">
-        <v>202</v>
+      <c r="F55" s="58" t="s">
+        <v>193</v>
       </c>
       <c r="G55" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I55" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="H55" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I55" s="29" t="s">
-        <v>43</v>
-      </c>
       <c r="J55" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3090,26 +3080,26 @@
         <v>14</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E56" s="14"/>
-      <c r="F56" s="64" t="s">
-        <v>203</v>
+      <c r="F56" s="60" t="s">
+        <v>194</v>
       </c>
       <c r="G56" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I56" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="H56" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I56" s="29" t="s">
-        <v>43</v>
-      </c>
       <c r="J56" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3118,26 +3108,26 @@
         <v>14</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E57" s="14"/>
-      <c r="F57" s="61" t="s">
-        <v>206</v>
+      <c r="F57" s="58" t="s">
+        <v>195</v>
       </c>
       <c r="G57" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H57" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I57" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J57" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3146,26 +3136,26 @@
         <v>14</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E58" s="14"/>
-      <c r="F58" s="61" t="s">
-        <v>207</v>
+      <c r="F58" s="58" t="s">
+        <v>196</v>
       </c>
       <c r="G58" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I58" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="H58" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I58" s="29" t="s">
-        <v>43</v>
-      </c>
       <c r="J58" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
@@ -3174,24 +3164,24 @@
         <v>14</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E59" s="21"/>
       <c r="F59" s="46"/>
       <c r="G59" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I59" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="H59" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I59" s="29" t="s">
-        <v>43</v>
-      </c>
       <c r="J59" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
@@ -3200,24 +3190,24 @@
         <v>14</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E60" s="21"/>
       <c r="F60" s="46"/>
       <c r="G60" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I60" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="H60" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I60" s="29" t="s">
-        <v>43</v>
-      </c>
       <c r="J60" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3226,26 +3216,26 @@
         <v>14</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D61" s="21" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E61" s="14"/>
       <c r="F61" s="47" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="G61" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I61" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J61" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3254,26 +3244,26 @@
         <v>14</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="D62" s="28" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E62" s="31"/>
       <c r="F62" s="52" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G62" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I62" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="H62" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I62" s="29" t="s">
-        <v>43</v>
-      </c>
       <c r="J62" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3282,52 +3272,52 @@
         <v>14</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D63" s="28" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E63" s="31"/>
       <c r="F63" s="52" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G63" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I63" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="H63" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I63" s="29" t="s">
-        <v>43</v>
-      </c>
       <c r="J63" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" s="70" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A64" s="66"/>
-      <c r="B64" s="67" t="s">
-        <v>14</v>
-      </c>
-      <c r="C64" s="68" t="s">
-        <v>147</v>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" s="66" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A64" s="62"/>
+      <c r="B64" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="C64" s="64" t="s">
+        <v>141</v>
       </c>
       <c r="D64" s="26" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E64" s="27"/>
       <c r="F64" s="48"/>
-      <c r="G64" s="69" t="s">
+      <c r="G64" s="65" t="s">
+        <v>31</v>
+      </c>
+      <c r="H64" s="65" t="s">
+        <v>32</v>
+      </c>
+      <c r="I64" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="H64" s="69" t="s">
-        <v>38</v>
-      </c>
-      <c r="I64" s="66" t="s">
-        <v>43</v>
-      </c>
       <c r="J64" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
@@ -3336,24 +3326,24 @@
         <v>14</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D65" s="25" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E65" s="30"/>
       <c r="F65" s="51"/>
       <c r="G65" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H65" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I65" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="J65" s="74" t="s">
-        <v>218</v>
+      <c r="J65" s="70" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3362,26 +3352,26 @@
         <v>14</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D66" s="21" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E66" s="14"/>
       <c r="F66" s="47" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I66" s="29" t="s">
         <v>10</v>
       </c>
       <c r="J66" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3390,26 +3380,26 @@
         <v>14</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D67" s="21" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E67" s="14"/>
-      <c r="F67" s="71" t="s">
-        <v>211</v>
+      <c r="F67" s="67" t="s">
+        <v>208</v>
       </c>
       <c r="G67" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I67" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="H67" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I67" s="29" t="s">
-        <v>43</v>
-      </c>
       <c r="J67" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -3418,24 +3408,24 @@
         <v>14</v>
       </c>
       <c r="C68" s="18" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D68" s="21" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E68" s="14"/>
-      <c r="F68" s="71"/>
+      <c r="F68" s="67"/>
       <c r="G68" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I68" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="H68" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I68" s="29" t="s">
-        <v>43</v>
-      </c>
       <c r="J68" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -3444,24 +3434,24 @@
         <v>14</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D69" s="21" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E69" s="14"/>
-      <c r="F69" s="71"/>
+      <c r="F69" s="67"/>
       <c r="G69" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I69" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="H69" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I69" s="29" t="s">
-        <v>43</v>
-      </c>
       <c r="J69" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
@@ -3470,24 +3460,24 @@
         <v>14</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D70" s="32" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E70" s="33"/>
       <c r="F70" s="53"/>
       <c r="G70" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H70" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I70" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="J70" s="74" t="s">
-        <v>218</v>
+      <c r="J70" s="70" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3496,52 +3486,52 @@
         <v>14</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E71" s="14"/>
       <c r="F71" s="47" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I71" s="29" t="s">
         <v>10</v>
       </c>
       <c r="J71" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" s="70" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A72" s="66"/>
-      <c r="B72" s="67" t="s">
-        <v>14</v>
-      </c>
-      <c r="C72" s="68" t="s">
-        <v>155</v>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" s="66" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A72" s="62"/>
+      <c r="B72" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="C72" s="64" t="s">
+        <v>149</v>
       </c>
       <c r="D72" s="26" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E72" s="27"/>
       <c r="F72" s="48"/>
-      <c r="G72" s="69" t="s">
+      <c r="G72" s="65" t="s">
+        <v>31</v>
+      </c>
+      <c r="H72" s="65" t="s">
+        <v>32</v>
+      </c>
+      <c r="I72" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="H72" s="69" t="s">
-        <v>38</v>
-      </c>
-      <c r="I72" s="66" t="s">
-        <v>43</v>
-      </c>
       <c r="J72" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
@@ -3550,24 +3540,24 @@
         <v>14</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D73" s="25" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E73" s="30"/>
       <c r="F73" s="51"/>
       <c r="G73" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H73" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I73" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="J73" s="74" t="s">
-        <v>218</v>
+      <c r="J73" s="70" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -3576,28 +3566,28 @@
         <v>14</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D74" s="34" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F74" s="54" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="G74" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H74" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I74" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J74" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3606,28 +3596,28 @@
         <v>14</v>
       </c>
       <c r="C75" s="18" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D75" s="21" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F75" s="47" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="G75" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H75" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I75" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J75" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3636,28 +3626,28 @@
         <v>14</v>
       </c>
       <c r="C76" s="18" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D76" s="21" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F76" s="47" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="G76" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H76" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I76" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J76" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -3666,28 +3656,28 @@
         <v>14</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D77" s="21" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F77" s="47" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="G77" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H77" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I77" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J77" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -3696,28 +3686,28 @@
         <v>14</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D78" s="21" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F78" s="47" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="G78" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H78" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I78" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J78" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3726,26 +3716,26 @@
         <v>14</v>
       </c>
       <c r="C79" s="18" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D79" s="35" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E79" s="15"/>
       <c r="F79" s="51" t="s">
-        <v>214</v>
-      </c>
-      <c r="G79" s="73" t="s">
-        <v>37</v>
+        <v>169</v>
+      </c>
+      <c r="G79" s="69" t="s">
+        <v>31</v>
       </c>
       <c r="H79" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I79" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J79" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3754,26 +3744,26 @@
         <v>14</v>
       </c>
       <c r="C80" s="18" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D80" s="21" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F80" s="47"/>
       <c r="G80" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I80" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="J80" s="74" t="s">
-        <v>218</v>
+      <c r="J80" s="70" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3782,28 +3772,28 @@
         <v>14</v>
       </c>
       <c r="C81" s="18" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D81" s="21" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F81" s="46" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="G81" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H81" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I81" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J81" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3812,28 +3802,28 @@
         <v>14</v>
       </c>
       <c r="C82" s="18" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D82" s="21" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F82" s="46" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="G82" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H82" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I82" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J82" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3842,26 +3832,26 @@
         <v>14</v>
       </c>
       <c r="C83" s="18" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D83" s="35" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E83" s="15"/>
       <c r="F83" s="51" t="s">
-        <v>213</v>
-      </c>
-      <c r="G83" s="73" t="s">
-        <v>37</v>
+        <v>217</v>
+      </c>
+      <c r="G83" s="69" t="s">
+        <v>31</v>
       </c>
       <c r="H83" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I83" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J83" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3870,26 +3860,26 @@
         <v>14</v>
       </c>
       <c r="C84" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="D84" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="E84" s="13" t="s">
         <v>167</v>
-      </c>
-      <c r="D84" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="E84" s="13" t="s">
-        <v>173</v>
       </c>
       <c r="F84" s="47"/>
       <c r="G84" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I84" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="J84" s="74" t="s">
-        <v>218</v>
+      <c r="J84" s="70" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -3898,28 +3888,28 @@
         <v>14</v>
       </c>
       <c r="C85" s="18" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D85" s="21" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F85" s="47" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="G85" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H85" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I85" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J85" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -3928,28 +3918,28 @@
         <v>14</v>
       </c>
       <c r="C86" s="18" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D86" s="21" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F86" s="47" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="G86" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H86" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I86" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J86" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3958,26 +3948,26 @@
         <v>14</v>
       </c>
       <c r="C87" s="18" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D87" s="35" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E87" s="15"/>
       <c r="F87" s="51" t="s">
-        <v>214</v>
+        <v>169</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I87" s="29" t="s">
         <v>10</v>
       </c>
       <c r="J87" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3986,28 +3976,28 @@
         <v>14</v>
       </c>
       <c r="C88" s="18" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D88" s="21" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F88" s="49" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="G88" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H88" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I88" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J88" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -4016,28 +4006,28 @@
         <v>14</v>
       </c>
       <c r="C89" s="18" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D89" s="21" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F89" s="47" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="G89" s="17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H89" s="17" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I89" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J89" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/mapping/field_mapping.xlsx
+++ b/mapping/field_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Water collectives\WHS Assessment\auto gen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D71BEE19-B12A-428A-88D5-973C9D0D2442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5BCC76C-4B50-4C9F-B22E-86E0FB29EF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B03A0D84-276C-499F-A511-71567CA886FB}"/>
   </bookViews>
@@ -106,9 +106,6 @@
   </si>
   <si>
     <t>B8</t>
-  </si>
-  <si>
-    <t>Submitted at</t>
   </si>
   <si>
     <t>B9</t>
@@ -711,6 +708,9 @@
   </si>
   <si>
     <t>stone-stone_kms</t>
+  </si>
+  <si>
+    <t>SubmissionDate</t>
   </si>
 </sst>
 </file>
@@ -1490,16 +1490,16 @@
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J1" s="68" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1519,19 +1519,19 @@
         <v>17</v>
       </c>
       <c r="F2" s="40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>10</v>
       </c>
       <c r="J2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1551,19 +1551,19 @@
         <v>17</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>10</v>
       </c>
       <c r="J3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1583,19 +1583,19 @@
         <v>17</v>
       </c>
       <c r="F4" s="41" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1615,19 +1615,19 @@
         <v>17</v>
       </c>
       <c r="F5" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1647,19 +1647,19 @@
         <v>17</v>
       </c>
       <c r="F6" s="41" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1679,19 +1679,19 @@
         <v>17</v>
       </c>
       <c r="F7" s="41" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>15</v>
       </c>
       <c r="J7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1710,20 +1710,20 @@
       <c r="E8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="41" t="s">
-        <v>26</v>
+      <c r="F8" t="s">
+        <v>218</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>10</v>
       </c>
       <c r="J8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1734,24 +1734,24 @@
         <v>7</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>27</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>28</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="41"/>
       <c r="G9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H9" s="69" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>10</v>
       </c>
       <c r="J9" s="70" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1762,24 +1762,24 @@
         <v>7</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="41"/>
       <c r="G10" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>10</v>
       </c>
       <c r="J10" s="70" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -1790,28 +1790,28 @@
         <v>7</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F11" s="42" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>10</v>
       </c>
       <c r="J11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1822,28 +1822,28 @@
         <v>7</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="42" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>10</v>
       </c>
       <c r="J12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -1854,26 +1854,26 @@
         <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="42"/>
       <c r="G13" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -1884,28 +1884,28 @@
         <v>7</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="42" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>10</v>
       </c>
       <c r="J14" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -1916,28 +1916,28 @@
         <v>7</v>
       </c>
       <c r="C15" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="16" t="s">
         <v>47</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>48</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F15" s="43" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I15" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -1961,25 +1961,25 @@
         <v>18</v>
       </c>
       <c r="D17" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="E17" s="22" t="s">
-        <v>50</v>
-      </c>
       <c r="F17" s="41" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I17" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -1991,25 +1991,25 @@
         <v>8</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F18" s="41" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I18" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2021,21 +2021,21 @@
         <v>11</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E19" s="22"/>
       <c r="F19" s="41"/>
       <c r="G19" s="22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2047,21 +2047,21 @@
         <v>13</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E20" s="22"/>
       <c r="F20" s="41"/>
       <c r="G20" s="22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2073,25 +2073,25 @@
         <v>24</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>17</v>
       </c>
       <c r="F21" s="41" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I21" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J21" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2103,25 +2103,25 @@
         <v>25</v>
       </c>
       <c r="D22" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="E22" s="24" t="s">
-        <v>57</v>
-      </c>
       <c r="F22" s="45" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I22" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J22" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2130,28 +2130,28 @@
         <v>14</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F23" s="45" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H23" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I23" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
@@ -2160,24 +2160,24 @@
         <v>14</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E24" s="24"/>
       <c r="F24" s="45"/>
       <c r="G24" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H24" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I24" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J24" s="70" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
@@ -2186,28 +2186,28 @@
         <v>14</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F25" s="46" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H25" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I25" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J25" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
@@ -2216,24 +2216,24 @@
         <v>14</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E26" s="24"/>
       <c r="F26" s="45"/>
       <c r="G26" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I26" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J26" s="70" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2242,28 +2242,28 @@
         <v>14</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F27" s="47" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I27" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J27" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2272,28 +2272,28 @@
         <v>14</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F28" s="47" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I28" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J28" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2302,28 +2302,28 @@
         <v>14</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D29" s="56" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F29" s="47" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I29" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J29" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2332,28 +2332,28 @@
         <v>14</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D30" s="56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E30" s="57" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F30" s="58" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G30" s="59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H30" s="59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I30" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J30" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2362,28 +2362,28 @@
         <v>14</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D31" s="56" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E31" s="57" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F31" s="60" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G31" s="59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H31" s="59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I31" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J31" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2392,28 +2392,28 @@
         <v>14</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F32" s="58" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I32" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J32" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2422,28 +2422,28 @@
         <v>14</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D33" s="61" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F33" s="58" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I33" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J33" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2452,28 +2452,28 @@
         <v>14</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F34" s="47" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I34" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J34" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2482,28 +2482,28 @@
         <v>14</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E35" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F35" s="58" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I35" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J35" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -2512,28 +2512,28 @@
         <v>14</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F36" s="60" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I36" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J36" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2544,28 +2544,28 @@
         <v>14</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E37" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F37" s="60" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I37" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J37" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2576,28 +2576,28 @@
         <v>14</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D38" s="28" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E38" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F38" s="50" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I38" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J38" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2608,28 +2608,28 @@
         <v>14</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E39" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F39" s="50" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I39" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="66" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -2638,26 +2638,26 @@
         <v>14</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E40" s="38" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F40" s="48"/>
       <c r="G40" s="65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H40" s="65" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I40" s="62" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J40" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
@@ -2666,24 +2666,24 @@
         <v>14</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E41" s="30"/>
       <c r="F41" s="51"/>
       <c r="G41" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I41" s="29" t="s">
         <v>10</v>
       </c>
       <c r="J41" s="70" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2692,26 +2692,26 @@
         <v>14</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D42" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E42" s="14"/>
       <c r="F42" s="47" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I42" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J42" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2720,26 +2720,26 @@
         <v>14</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E43" s="14"/>
       <c r="F43" s="47" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I43" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J43" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2748,26 +2748,26 @@
         <v>14</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="47" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I44" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J44" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2776,26 +2776,26 @@
         <v>14</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D45" s="21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E45" s="14"/>
       <c r="F45" s="47" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I45" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J45" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2804,26 +2804,26 @@
         <v>14</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E46" s="14"/>
       <c r="F46" s="47" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I46" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J46" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2832,26 +2832,26 @@
         <v>14</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E47" s="14"/>
       <c r="F47" s="58" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I47" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J47" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2860,26 +2860,26 @@
         <v>14</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D48" s="28" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E48" s="31"/>
       <c r="F48" s="52" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I48" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J48" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2888,26 +2888,26 @@
         <v>14</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D49" s="28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E49" s="31"/>
       <c r="F49" s="52" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I49" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J49" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="66" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -2916,24 +2916,24 @@
         <v>14</v>
       </c>
       <c r="C50" s="64" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D50" s="26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E50" s="27"/>
       <c r="F50" s="48"/>
       <c r="G50" s="65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H50" s="65" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I50" s="62" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J50" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
@@ -2942,24 +2942,24 @@
         <v>14</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D51" s="25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E51" s="30"/>
       <c r="F51" s="51"/>
       <c r="G51" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H51" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I51" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J51" s="70" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2968,26 +2968,26 @@
         <v>14</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E52" s="14"/>
       <c r="F52" s="47" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I52" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J52" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2996,26 +2996,26 @@
         <v>14</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E53" s="14"/>
       <c r="F53" s="47" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I53" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J53" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3024,26 +3024,26 @@
         <v>14</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E54" s="14"/>
       <c r="F54" s="47" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I54" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J54" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3052,26 +3052,26 @@
         <v>14</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E55" s="14"/>
       <c r="F55" s="58" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I55" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J55" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3080,26 +3080,26 @@
         <v>14</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E56" s="14"/>
       <c r="F56" s="60" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I56" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J56" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3108,26 +3108,26 @@
         <v>14</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E57" s="14"/>
       <c r="F57" s="58" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G57" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H57" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I57" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J57" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3136,26 +3136,26 @@
         <v>14</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E58" s="14"/>
       <c r="F58" s="58" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I58" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J58" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
@@ -3164,24 +3164,24 @@
         <v>14</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E59" s="21"/>
       <c r="F59" s="46"/>
       <c r="G59" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I59" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J59" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
@@ -3190,24 +3190,24 @@
         <v>14</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E60" s="21"/>
       <c r="F60" s="46"/>
       <c r="G60" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I60" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J60" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3216,26 +3216,26 @@
         <v>14</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D61" s="21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E61" s="14"/>
       <c r="F61" s="47" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G61" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I61" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J61" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3244,26 +3244,26 @@
         <v>14</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D62" s="28" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E62" s="31"/>
       <c r="F62" s="52" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I62" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J62" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3272,26 +3272,26 @@
         <v>14</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D63" s="28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E63" s="31"/>
       <c r="F63" s="52" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I63" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J63" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="64" spans="1:10" s="66" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -3300,24 +3300,24 @@
         <v>14</v>
       </c>
       <c r="C64" s="64" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D64" s="26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E64" s="27"/>
       <c r="F64" s="48"/>
       <c r="G64" s="65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H64" s="65" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I64" s="62" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
@@ -3326,24 +3326,24 @@
         <v>14</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D65" s="25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E65" s="30"/>
       <c r="F65" s="51"/>
       <c r="G65" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H65" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I65" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J65" s="70" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3352,26 +3352,26 @@
         <v>14</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D66" s="21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E66" s="14"/>
       <c r="F66" s="47" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I66" s="29" t="s">
         <v>10</v>
       </c>
       <c r="J66" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3380,26 +3380,26 @@
         <v>14</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D67" s="21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E67" s="14"/>
       <c r="F67" s="67" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I67" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J67" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -3408,24 +3408,24 @@
         <v>14</v>
       </c>
       <c r="C68" s="18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D68" s="21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E68" s="14"/>
       <c r="F68" s="67"/>
       <c r="G68" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I68" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J68" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -3434,24 +3434,24 @@
         <v>14</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D69" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E69" s="14"/>
       <c r="F69" s="67"/>
       <c r="G69" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I69" s="29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J69" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
@@ -3460,24 +3460,24 @@
         <v>14</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D70" s="32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E70" s="33"/>
       <c r="F70" s="53"/>
       <c r="G70" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H70" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I70" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J70" s="70" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3486,26 +3486,26 @@
         <v>14</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E71" s="14"/>
       <c r="F71" s="47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I71" s="29" t="s">
         <v>10</v>
       </c>
       <c r="J71" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="72" spans="1:10" s="66" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -3514,24 +3514,24 @@
         <v>14</v>
       </c>
       <c r="C72" s="64" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D72" s="26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E72" s="27"/>
       <c r="F72" s="48"/>
       <c r="G72" s="65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H72" s="65" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I72" s="62" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J72" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
@@ -3540,24 +3540,24 @@
         <v>14</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D73" s="25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E73" s="30"/>
       <c r="F73" s="51"/>
       <c r="G73" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H73" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I73" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J73" s="70" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -3566,28 +3566,28 @@
         <v>14</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D74" s="34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F74" s="54" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G74" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H74" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I74" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J74" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3596,28 +3596,28 @@
         <v>14</v>
       </c>
       <c r="C75" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D75" s="21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F75" s="47" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G75" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H75" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I75" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J75" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3626,28 +3626,28 @@
         <v>14</v>
       </c>
       <c r="C76" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D76" s="21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F76" s="47" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G76" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H76" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I76" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J76" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -3656,28 +3656,28 @@
         <v>14</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D77" s="21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F77" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G77" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H77" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I77" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J77" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -3686,28 +3686,28 @@
         <v>14</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D78" s="21" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F78" s="47" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G78" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H78" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I78" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J78" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3716,26 +3716,26 @@
         <v>14</v>
       </c>
       <c r="C79" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D79" s="35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E79" s="15"/>
       <c r="F79" s="51" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G79" s="69" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H79" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I79" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J79" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3744,26 +3744,26 @@
         <v>14</v>
       </c>
       <c r="C80" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D80" s="21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F80" s="47"/>
       <c r="G80" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I80" s="29" t="s">
         <v>10</v>
       </c>
       <c r="J80" s="70" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3772,28 +3772,28 @@
         <v>14</v>
       </c>
       <c r="C81" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D81" s="21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F81" s="46" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G81" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H81" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I81" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J81" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3802,28 +3802,28 @@
         <v>14</v>
       </c>
       <c r="C82" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D82" s="21" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F82" s="46" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G82" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H82" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I82" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J82" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3832,26 +3832,26 @@
         <v>14</v>
       </c>
       <c r="C83" s="18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D83" s="35" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E83" s="15"/>
       <c r="F83" s="51" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G83" s="69" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H83" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I83" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J83" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3860,26 +3860,26 @@
         <v>14</v>
       </c>
       <c r="C84" s="18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D84" s="21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F84" s="47"/>
       <c r="G84" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I84" s="29" t="s">
         <v>10</v>
       </c>
       <c r="J84" s="70" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -3888,28 +3888,28 @@
         <v>14</v>
       </c>
       <c r="C85" s="18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D85" s="21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F85" s="47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G85" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H85" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I85" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J85" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -3918,28 +3918,28 @@
         <v>14</v>
       </c>
       <c r="C86" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D86" s="21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F86" s="47" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G86" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H86" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I86" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3948,26 +3948,26 @@
         <v>14</v>
       </c>
       <c r="C87" s="18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D87" s="35" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E87" s="15"/>
       <c r="F87" s="51" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I87" s="29" t="s">
         <v>10</v>
       </c>
       <c r="J87" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3976,28 +3976,28 @@
         <v>14</v>
       </c>
       <c r="C88" s="18" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D88" s="21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F88" s="49" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G88" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H88" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I88" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J88" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -4006,28 +4006,28 @@
         <v>14</v>
       </c>
       <c r="C89" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="D89" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="E89" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="D89" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="E89" s="13" t="s">
-        <v>167</v>
-      </c>
       <c r="F89" s="47" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G89" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H89" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I89" s="18" t="s">
         <v>10</v>
       </c>
       <c r="J89" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/mapping/field_mapping.xlsx
+++ b/mapping/field_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Water collectives\WHS Assessment\auto gen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5BCC76C-4B50-4C9F-B22E-86E0FB29EF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB3D833-7D59-4E6B-B40E-B72CC18A9DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B03A0D84-276C-499F-A511-71567CA886FB}"/>
   </bookViews>
@@ -54,39 +54,24 @@
     <t>Input Data Sheet-G</t>
   </si>
   <si>
-    <t>B4</t>
-  </si>
-  <si>
     <t>District</t>
   </si>
   <si>
     <t>Available</t>
   </si>
   <si>
-    <t>B5</t>
-  </si>
-  <si>
     <t>Mandal</t>
   </si>
   <si>
-    <t>B6</t>
-  </si>
-  <si>
     <t>Input Data Sheet-T</t>
   </si>
   <si>
     <t>To be Added</t>
   </si>
   <si>
-    <t>B2</t>
-  </si>
-  <si>
     <t>1. Basic Information</t>
   </si>
   <si>
-    <t>B3</t>
-  </si>
-  <si>
     <t>Grama panchayat</t>
   </si>
   <si>
@@ -102,15 +87,6 @@
     <t>Year of proposal</t>
   </si>
   <si>
-    <t>B7</t>
-  </si>
-  <si>
-    <t>B8</t>
-  </si>
-  <si>
-    <t>B9</t>
-  </si>
-  <si>
     <t>Work Details:</t>
   </si>
   <si>
@@ -129,46 +105,25 @@
     <t>Fixed text</t>
   </si>
   <si>
-    <t>B10</t>
-  </si>
-  <si>
     <t>Expected outcome of the work</t>
   </si>
   <si>
-    <t>B11</t>
-  </si>
-  <si>
     <t>Later</t>
   </si>
   <si>
     <t>No of families covered in Watrer collective</t>
   </si>
   <si>
-    <t>B13</t>
-  </si>
-  <si>
     <t>Present Irrigated area</t>
   </si>
   <si>
-    <t>B14</t>
-  </si>
-  <si>
     <t>Additional area brought  under irrigation (acres)</t>
   </si>
   <si>
-    <t>B15</t>
-  </si>
-  <si>
     <t>KML</t>
   </si>
   <si>
     <t>% of small and marginal farmers covered</t>
-  </si>
-  <si>
-    <t>B16</t>
-  </si>
-  <si>
-    <t>B17</t>
   </si>
   <si>
     <t>GPS Location</t>
@@ -239,9 +194,6 @@
     <t>Earth work excavation</t>
   </si>
   <si>
-    <t>B12</t>
-  </si>
-  <si>
     <t>U/S Cut off</t>
   </si>
   <si>
@@ -380,180 +332,6 @@
     <t>Cost of steel at site of work per ton</t>
   </si>
   <si>
-    <t>B18</t>
-  </si>
-  <si>
-    <t>B19</t>
-  </si>
-  <si>
-    <t>B20</t>
-  </si>
-  <si>
-    <t>B21</t>
-  </si>
-  <si>
-    <t>B22</t>
-  </si>
-  <si>
-    <t>B23</t>
-  </si>
-  <si>
-    <t>B24</t>
-  </si>
-  <si>
-    <t>B25</t>
-  </si>
-  <si>
-    <t>B26</t>
-  </si>
-  <si>
-    <t>B27</t>
-  </si>
-  <si>
-    <t>B28</t>
-  </si>
-  <si>
-    <t>B29</t>
-  </si>
-  <si>
-    <t>B30</t>
-  </si>
-  <si>
-    <t>B31</t>
-  </si>
-  <si>
-    <t>B32</t>
-  </si>
-  <si>
-    <t>B33</t>
-  </si>
-  <si>
-    <t>B34</t>
-  </si>
-  <si>
-    <t>B35</t>
-  </si>
-  <si>
-    <t>B36</t>
-  </si>
-  <si>
-    <t>B37</t>
-  </si>
-  <si>
-    <t>B38</t>
-  </si>
-  <si>
-    <t>B39</t>
-  </si>
-  <si>
-    <t>B40</t>
-  </si>
-  <si>
-    <t>B41</t>
-  </si>
-  <si>
-    <t>B42</t>
-  </si>
-  <si>
-    <t>B43</t>
-  </si>
-  <si>
-    <t>B44</t>
-  </si>
-  <si>
-    <t>B45</t>
-  </si>
-  <si>
-    <t>B46</t>
-  </si>
-  <si>
-    <t>B47</t>
-  </si>
-  <si>
-    <t>B48</t>
-  </si>
-  <si>
-    <t>B49</t>
-  </si>
-  <si>
-    <t>B50</t>
-  </si>
-  <si>
-    <t>B51</t>
-  </si>
-  <si>
-    <t>B52</t>
-  </si>
-  <si>
-    <t>B53</t>
-  </si>
-  <si>
-    <t>B54</t>
-  </si>
-  <si>
-    <t>B55</t>
-  </si>
-  <si>
-    <t>B56</t>
-  </si>
-  <si>
-    <t>B57</t>
-  </si>
-  <si>
-    <t>B58</t>
-  </si>
-  <si>
-    <t>B59</t>
-  </si>
-  <si>
-    <t>B60</t>
-  </si>
-  <si>
-    <t>B61</t>
-  </si>
-  <si>
-    <t>B62</t>
-  </si>
-  <si>
-    <t>B63</t>
-  </si>
-  <si>
-    <t>B64</t>
-  </si>
-  <si>
-    <t>B65</t>
-  </si>
-  <si>
-    <t>B66</t>
-  </si>
-  <si>
-    <t>B67</t>
-  </si>
-  <si>
-    <t>B68</t>
-  </si>
-  <si>
-    <t>B69</t>
-  </si>
-  <si>
-    <t>B70</t>
-  </si>
-  <si>
-    <t>B71</t>
-  </si>
-  <si>
-    <t>B72</t>
-  </si>
-  <si>
-    <t>B73</t>
-  </si>
-  <si>
-    <t>B74</t>
-  </si>
-  <si>
-    <t>B75</t>
-  </si>
-  <si>
     <t>6. Lead_statement</t>
   </si>
   <si>
@@ -711,6 +489,228 @@
   </si>
   <si>
     <t>SubmissionDate</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>C11</t>
+  </si>
+  <si>
+    <t>C13</t>
+  </si>
+  <si>
+    <t>C14</t>
+  </si>
+  <si>
+    <t>C15</t>
+  </si>
+  <si>
+    <t>C16</t>
+  </si>
+  <si>
+    <t>C17</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>C18</t>
+  </si>
+  <si>
+    <t>C19</t>
+  </si>
+  <si>
+    <t>C20</t>
+  </si>
+  <si>
+    <t>C21</t>
+  </si>
+  <si>
+    <t>C22</t>
+  </si>
+  <si>
+    <t>C23</t>
+  </si>
+  <si>
+    <t>C24</t>
+  </si>
+  <si>
+    <t>C25</t>
+  </si>
+  <si>
+    <t>C26</t>
+  </si>
+  <si>
+    <t>C27</t>
+  </si>
+  <si>
+    <t>C28</t>
+  </si>
+  <si>
+    <t>C29</t>
+  </si>
+  <si>
+    <t>C30</t>
+  </si>
+  <si>
+    <t>C31</t>
+  </si>
+  <si>
+    <t>C32</t>
+  </si>
+  <si>
+    <t>C33</t>
+  </si>
+  <si>
+    <t>C34</t>
+  </si>
+  <si>
+    <t>C35</t>
+  </si>
+  <si>
+    <t>C36</t>
+  </si>
+  <si>
+    <t>C37</t>
+  </si>
+  <si>
+    <t>C38</t>
+  </si>
+  <si>
+    <t>C39</t>
+  </si>
+  <si>
+    <t>C40</t>
+  </si>
+  <si>
+    <t>C41</t>
+  </si>
+  <si>
+    <t>C42</t>
+  </si>
+  <si>
+    <t>C43</t>
+  </si>
+  <si>
+    <t>C44</t>
+  </si>
+  <si>
+    <t>C45</t>
+  </si>
+  <si>
+    <t>C46</t>
+  </si>
+  <si>
+    <t>C47</t>
+  </si>
+  <si>
+    <t>C48</t>
+  </si>
+  <si>
+    <t>C49</t>
+  </si>
+  <si>
+    <t>C50</t>
+  </si>
+  <si>
+    <t>C51</t>
+  </si>
+  <si>
+    <t>C52</t>
+  </si>
+  <si>
+    <t>C53</t>
+  </si>
+  <si>
+    <t>C54</t>
+  </si>
+  <si>
+    <t>C55</t>
+  </si>
+  <si>
+    <t>C56</t>
+  </si>
+  <si>
+    <t>C57</t>
+  </si>
+  <si>
+    <t>C58</t>
+  </si>
+  <si>
+    <t>C59</t>
+  </si>
+  <si>
+    <t>C60</t>
+  </si>
+  <si>
+    <t>C61</t>
+  </si>
+  <si>
+    <t>C62</t>
+  </si>
+  <si>
+    <t>C63</t>
+  </si>
+  <si>
+    <t>C64</t>
+  </si>
+  <si>
+    <t>C65</t>
+  </si>
+  <si>
+    <t>C66</t>
+  </si>
+  <si>
+    <t>C67</t>
+  </si>
+  <si>
+    <t>C68</t>
+  </si>
+  <si>
+    <t>C69</t>
+  </si>
+  <si>
+    <t>C70</t>
+  </si>
+  <si>
+    <t>C71</t>
+  </si>
+  <si>
+    <t>C72</t>
+  </si>
+  <si>
+    <t>C73</t>
+  </si>
+  <si>
+    <t>C74</t>
+  </si>
+  <si>
+    <t>C75</t>
   </si>
 </sst>
 </file>
@@ -1490,16 +1490,16 @@
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J1" s="68" t="s">
-        <v>169</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1510,28 +1510,28 @@
         <v>7</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>16</v>
+        <v>145</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F2" s="40" t="s">
-        <v>173</v>
+        <v>99</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1542,28 +1542,28 @@
         <v>7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>18</v>
+        <v>146</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F3" s="40" t="s">
-        <v>174</v>
+        <v>100</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J3" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1574,28 +1574,28 @@
         <v>7</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>8</v>
+        <v>147</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F4" s="41" t="s">
-        <v>175</v>
+        <v>101</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J4" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1606,28 +1606,28 @@
         <v>7</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>11</v>
+        <v>148</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F5" s="41" t="s">
-        <v>176</v>
+        <v>102</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J5" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1638,28 +1638,28 @@
         <v>7</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>17</v>
-      </c>
       <c r="F6" s="41" t="s">
-        <v>177</v>
+        <v>103</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J6" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1670,28 +1670,28 @@
         <v>7</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F7" s="41" t="s">
-        <v>178</v>
+        <v>104</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J7" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1702,28 +1702,28 @@
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>218</v>
+        <v>144</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J8" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1734,24 +1734,24 @@
         <v>7</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>26</v>
+        <v>152</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="41"/>
       <c r="G9" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H9" s="69" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J9" s="70" t="s">
-        <v>172</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1762,24 +1762,24 @@
         <v>7</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>35</v>
+        <v>153</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="41"/>
       <c r="G10" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J10" s="70" t="s">
-        <v>172</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -1790,28 +1790,28 @@
         <v>7</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>38</v>
+        <v>154</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F11" s="42" t="s">
-        <v>179</v>
+        <v>105</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J11" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1822,28 +1822,28 @@
         <v>7</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>40</v>
+        <v>155</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F12" s="42" t="s">
-        <v>180</v>
+        <v>106</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J12" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -1854,26 +1854,26 @@
         <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F13" s="42"/>
       <c r="G13" s="2" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J13" t="s">
-        <v>171</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -1884,28 +1884,28 @@
         <v>7</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>45</v>
+        <v>157</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F14" s="42" t="s">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J14" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -1916,28 +1916,28 @@
         <v>7</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>46</v>
+        <v>158</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F15" s="43" t="s">
-        <v>182</v>
+        <v>108</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I15" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J15" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -1955,585 +1955,585 @@
     <row r="17" spans="1:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="18"/>
       <c r="B17" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>18</v>
+        <v>146</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="F17" s="41" t="s">
-        <v>183</v>
+        <v>109</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I17" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J17" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>8</v>
+        <v>147</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="F18" s="41" t="s">
-        <v>184</v>
+        <v>110</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I18" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J18" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
       <c r="B19" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>11</v>
+        <v>148</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="E19" s="22"/>
       <c r="F19" s="41"/>
       <c r="G19" s="22" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J19" t="s">
-        <v>171</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>13</v>
+        <v>149</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="E20" s="22"/>
       <c r="F20" s="41"/>
       <c r="G20" s="22" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J20" t="s">
-        <v>171</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="B21" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F21" s="41" t="s">
-        <v>185</v>
+        <v>111</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I21" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J21" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
       <c r="B22" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F22" s="45" t="s">
-        <v>186</v>
+        <v>112</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I22" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J22" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="6"/>
       <c r="B23" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>26</v>
+        <v>152</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F23" s="45" t="s">
-        <v>187</v>
+        <v>113</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H23" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I23" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J23" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
       <c r="B24" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>33</v>
+        <v>159</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="E24" s="24"/>
       <c r="F24" s="45"/>
       <c r="G24" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H24" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I24" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J24" s="70" t="s">
-        <v>172</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6"/>
       <c r="B25" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>35</v>
+        <v>153</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="F25" s="46" t="s">
-        <v>188</v>
+        <v>114</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H25" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I25" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J25" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
       <c r="B26" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>61</v>
+        <v>160</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E26" s="24"/>
       <c r="F26" s="45"/>
       <c r="G26" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I26" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J26" s="70" t="s">
-        <v>172</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>38</v>
+        <v>154</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="F27" s="47" t="s">
-        <v>189</v>
+        <v>115</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I27" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J27" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>40</v>
+        <v>155</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="F28" s="47" t="s">
-        <v>190</v>
+        <v>116</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I28" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J28" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="D29" s="56" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="F29" s="47" t="s">
-        <v>191</v>
+        <v>117</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I29" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J29" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>45</v>
+        <v>157</v>
       </c>
       <c r="D30" s="56" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="E30" s="57" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="F30" s="58" t="s">
-        <v>192</v>
+        <v>118</v>
       </c>
       <c r="G30" s="59" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H30" s="59" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I30" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J30" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>46</v>
+        <v>158</v>
       </c>
       <c r="D31" s="56" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="E31" s="57" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="F31" s="60" t="s">
-        <v>193</v>
+        <v>119</v>
       </c>
       <c r="G31" s="59" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H31" s="59" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I31" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J31" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
       <c r="B32" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>108</v>
+        <v>161</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="F32" s="58" t="s">
-        <v>194</v>
+        <v>120</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I32" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J32" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="6"/>
       <c r="B33" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>109</v>
+        <v>162</v>
       </c>
       <c r="D33" s="61" t="s">
-        <v>167</v>
+        <v>93</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="F33" s="58" t="s">
-        <v>195</v>
+        <v>121</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I33" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J33" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="6"/>
       <c r="B34" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>110</v>
+        <v>163</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="F34" s="47" t="s">
-        <v>196</v>
+        <v>122</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I34" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J34" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="6"/>
       <c r="B35" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>111</v>
+        <v>164</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="E35" s="24" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="F35" s="58" t="s">
-        <v>197</v>
+        <v>123</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I35" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J35" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A36" s="6"/>
       <c r="B36" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>112</v>
+        <v>165</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="F36" s="60" t="s">
-        <v>198</v>
+        <v>124</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I36" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J36" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2541,31 +2541,31 @@
         <v>4</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>113</v>
+        <v>166</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="E37" s="24" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="F37" s="60" t="s">
-        <v>199</v>
+        <v>125</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I37" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J37" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2573,31 +2573,31 @@
         <v>5</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>114</v>
+        <v>167</v>
       </c>
       <c r="D38" s="28" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="E38" s="24" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="F38" s="50" t="s">
-        <v>200</v>
+        <v>126</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I38" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J38" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2605,1429 +2605,1429 @@
         <v>6</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>115</v>
+        <v>168</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="E39" s="24" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="F39" s="50" t="s">
-        <v>200</v>
+        <v>126</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I39" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J39" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="66" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="62"/>
       <c r="B40" s="63" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>116</v>
+        <v>169</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="E40" s="38" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="F40" s="48"/>
       <c r="G40" s="65" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H40" s="65" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I40" s="62" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J40" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A41" s="29"/>
       <c r="B41" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>117</v>
+        <v>170</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="E41" s="30"/>
       <c r="F41" s="51"/>
       <c r="G41" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I41" s="29" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J41" s="70" t="s">
-        <v>172</v>
+        <v>98</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="29"/>
       <c r="B42" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>118</v>
+        <v>171</v>
       </c>
       <c r="D42" s="21" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="E42" s="14"/>
       <c r="F42" s="47" t="s">
-        <v>201</v>
+        <v>127</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I42" s="29" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J42" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="29"/>
       <c r="B43" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="E43" s="14"/>
       <c r="F43" s="47" t="s">
-        <v>202</v>
+        <v>128</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I43" s="29" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J43" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="29"/>
       <c r="B44" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="47" t="s">
-        <v>203</v>
+        <v>129</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I44" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J44" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="29"/>
       <c r="B45" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>121</v>
+        <v>174</v>
       </c>
       <c r="D45" s="21" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="E45" s="14"/>
       <c r="F45" s="47" t="s">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I45" s="29" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J45" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="29"/>
       <c r="B46" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>122</v>
+        <v>175</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="E46" s="14"/>
       <c r="F46" s="47" t="s">
-        <v>196</v>
+        <v>122</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I46" s="29" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J46" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="29"/>
       <c r="B47" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="E47" s="14"/>
       <c r="F47" s="58" t="s">
-        <v>197</v>
+        <v>123</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I47" s="29" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J47" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="29"/>
       <c r="B48" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>124</v>
+        <v>177</v>
       </c>
       <c r="D48" s="28" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="E48" s="31"/>
       <c r="F48" s="52" t="s">
-        <v>205</v>
+        <v>131</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I48" s="29" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J48" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="29"/>
       <c r="B49" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>125</v>
+        <v>178</v>
       </c>
       <c r="D49" s="28" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="E49" s="31"/>
       <c r="F49" s="52" t="s">
-        <v>205</v>
+        <v>131</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I49" s="29" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J49" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="66" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="62"/>
       <c r="B50" s="63" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C50" s="64" t="s">
-        <v>126</v>
+        <v>179</v>
       </c>
       <c r="D50" s="26" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="E50" s="27"/>
       <c r="F50" s="48"/>
       <c r="G50" s="65" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H50" s="65" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I50" s="62" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J50" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A51" s="29"/>
       <c r="B51" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>127</v>
+        <v>180</v>
       </c>
       <c r="D51" s="25" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="E51" s="30"/>
       <c r="F51" s="51"/>
       <c r="G51" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H51" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I51" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J51" s="70" t="s">
-        <v>172</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="29"/>
       <c r="B52" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>128</v>
+        <v>181</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="E52" s="14"/>
       <c r="F52" s="47" t="s">
-        <v>189</v>
+        <v>115</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I52" s="29" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J52" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="29"/>
       <c r="B53" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>129</v>
+        <v>182</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="E53" s="14"/>
       <c r="F53" s="47" t="s">
-        <v>190</v>
+        <v>116</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I53" s="29" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J53" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="29"/>
       <c r="B54" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>130</v>
+        <v>183</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="E54" s="14"/>
       <c r="F54" s="47" t="s">
-        <v>191</v>
+        <v>117</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I54" s="29" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J54" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="29"/>
       <c r="B55" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>131</v>
+        <v>184</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="E55" s="14"/>
       <c r="F55" s="58" t="s">
-        <v>192</v>
+        <v>118</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I55" s="29" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J55" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="29"/>
       <c r="B56" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>132</v>
+        <v>185</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="E56" s="14"/>
       <c r="F56" s="60" t="s">
-        <v>193</v>
+        <v>119</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I56" s="29" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J56" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="29"/>
       <c r="B57" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>133</v>
+        <v>186</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E57" s="14"/>
       <c r="F57" s="58" t="s">
-        <v>194</v>
+        <v>120</v>
       </c>
       <c r="G57" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H57" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I57" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J57" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="29"/>
       <c r="B58" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>134</v>
+        <v>187</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="E58" s="14"/>
       <c r="F58" s="58" t="s">
-        <v>195</v>
+        <v>121</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I58" s="29" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J58" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A59" s="29"/>
       <c r="B59" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="E59" s="21"/>
       <c r="F59" s="46"/>
       <c r="G59" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I59" s="29" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J59" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A60" s="29"/>
       <c r="B60" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>136</v>
+        <v>189</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="E60" s="21"/>
       <c r="F60" s="46"/>
       <c r="G60" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I60" s="29" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J60" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="29"/>
       <c r="B61" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>137</v>
+        <v>190</v>
       </c>
       <c r="D61" s="21" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="E61" s="14"/>
       <c r="F61" s="47" t="s">
-        <v>206</v>
+        <v>132</v>
       </c>
       <c r="G61" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I61" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J61" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="29"/>
       <c r="B62" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>138</v>
+        <v>191</v>
       </c>
       <c r="D62" s="28" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="E62" s="31"/>
       <c r="F62" s="52" t="s">
-        <v>205</v>
+        <v>131</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I62" s="29" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J62" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="29"/>
       <c r="B63" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>139</v>
+        <v>192</v>
       </c>
       <c r="D63" s="28" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="E63" s="31"/>
       <c r="F63" s="52" t="s">
-        <v>205</v>
+        <v>131</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I63" s="29" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J63" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="64" spans="1:10" s="66" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="62"/>
       <c r="B64" s="63" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C64" s="64" t="s">
-        <v>140</v>
+        <v>193</v>
       </c>
       <c r="D64" s="26" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="E64" s="27"/>
       <c r="F64" s="48"/>
       <c r="G64" s="65" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H64" s="65" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I64" s="62" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J64" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A65" s="29"/>
       <c r="B65" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>141</v>
+        <v>194</v>
       </c>
       <c r="D65" s="25" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="E65" s="30"/>
       <c r="F65" s="51"/>
       <c r="G65" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H65" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I65" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J65" s="70" t="s">
-        <v>172</v>
+        <v>98</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="29"/>
       <c r="B66" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>142</v>
+        <v>195</v>
       </c>
       <c r="D66" s="21" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="E66" s="14"/>
       <c r="F66" s="47" t="s">
-        <v>207</v>
+        <v>133</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I66" s="29" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J66" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="29"/>
       <c r="B67" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>143</v>
+        <v>196</v>
       </c>
       <c r="D67" s="21" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="E67" s="14"/>
       <c r="F67" s="67" t="s">
-        <v>207</v>
+        <v>133</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I67" s="29" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J67" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A68" s="29"/>
       <c r="B68" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C68" s="18" t="s">
-        <v>144</v>
+        <v>197</v>
       </c>
       <c r="D68" s="21" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E68" s="14"/>
       <c r="F68" s="67"/>
       <c r="G68" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I68" s="29" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J68" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A69" s="29"/>
       <c r="B69" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>145</v>
+        <v>198</v>
       </c>
       <c r="D69" s="21" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="E69" s="14"/>
       <c r="F69" s="67"/>
       <c r="G69" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I69" s="29" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J69" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A70" s="29"/>
       <c r="B70" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>146</v>
+        <v>199</v>
       </c>
       <c r="D70" s="32" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E70" s="33"/>
       <c r="F70" s="53"/>
       <c r="G70" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H70" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I70" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J70" s="70" t="s">
-        <v>172</v>
+        <v>98</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="29"/>
       <c r="B71" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>147</v>
+        <v>200</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E71" s="14"/>
       <c r="F71" s="47" t="s">
-        <v>208</v>
+        <v>134</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I71" s="29" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J71" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="72" spans="1:10" s="66" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="62"/>
       <c r="B72" s="63" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C72" s="64" t="s">
-        <v>148</v>
+        <v>201</v>
       </c>
       <c r="D72" s="26" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="E72" s="27"/>
       <c r="F72" s="48"/>
       <c r="G72" s="65" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H72" s="65" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I72" s="62" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J72" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A73" s="29"/>
       <c r="B73" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>149</v>
+        <v>202</v>
       </c>
       <c r="D73" s="25" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="E73" s="30"/>
       <c r="F73" s="51"/>
       <c r="G73" s="2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H73" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I73" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J73" s="70" t="s">
-        <v>172</v>
+        <v>98</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A74" s="29"/>
       <c r="B74" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>150</v>
+        <v>203</v>
       </c>
       <c r="D74" s="34" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>166</v>
+        <v>92</v>
       </c>
       <c r="F74" s="54" t="s">
-        <v>209</v>
+        <v>135</v>
       </c>
       <c r="G74" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H74" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I74" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J74" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="29"/>
       <c r="B75" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C75" s="18" t="s">
-        <v>151</v>
+        <v>204</v>
       </c>
       <c r="D75" s="21" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>166</v>
+        <v>92</v>
       </c>
       <c r="F75" s="47" t="s">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="G75" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H75" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I75" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J75" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="29"/>
       <c r="B76" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C76" s="18" t="s">
-        <v>152</v>
+        <v>205</v>
       </c>
       <c r="D76" s="21" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>166</v>
+        <v>92</v>
       </c>
       <c r="F76" s="47" t="s">
-        <v>211</v>
+        <v>137</v>
       </c>
       <c r="G76" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H76" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I76" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J76" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A77" s="29"/>
       <c r="B77" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>153</v>
+        <v>206</v>
       </c>
       <c r="D77" s="21" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>166</v>
+        <v>92</v>
       </c>
       <c r="F77" s="47" t="s">
-        <v>212</v>
+        <v>138</v>
       </c>
       <c r="G77" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H77" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I77" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J77" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A78" s="29"/>
       <c r="B78" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>154</v>
+        <v>207</v>
       </c>
       <c r="D78" s="21" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>166</v>
+        <v>92</v>
       </c>
       <c r="F78" s="47" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
       <c r="G78" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H78" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I78" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J78" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="29"/>
       <c r="B79" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C79" s="18" t="s">
-        <v>155</v>
+        <v>208</v>
       </c>
       <c r="D79" s="35" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="E79" s="15"/>
       <c r="F79" s="51" t="s">
-        <v>168</v>
+        <v>94</v>
       </c>
       <c r="G79" s="69" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H79" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I79" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J79" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="29"/>
       <c r="B80" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C80" s="18" t="s">
-        <v>156</v>
+        <v>209</v>
       </c>
       <c r="D80" s="21" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>166</v>
+        <v>92</v>
       </c>
       <c r="F80" s="47"/>
       <c r="G80" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I80" s="29" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J80" s="70" t="s">
-        <v>172</v>
+        <v>98</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="29"/>
       <c r="B81" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C81" s="18" t="s">
-        <v>157</v>
+        <v>210</v>
       </c>
       <c r="D81" s="21" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>166</v>
+        <v>92</v>
       </c>
       <c r="F81" s="46" t="s">
-        <v>214</v>
+        <v>140</v>
       </c>
       <c r="G81" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H81" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I81" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J81" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="29"/>
       <c r="B82" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C82" s="18" t="s">
-        <v>158</v>
+        <v>211</v>
       </c>
       <c r="D82" s="21" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>166</v>
+        <v>92</v>
       </c>
       <c r="F82" s="46" t="s">
-        <v>215</v>
+        <v>141</v>
       </c>
       <c r="G82" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H82" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I82" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J82" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="29"/>
       <c r="B83" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C83" s="18" t="s">
-        <v>159</v>
+        <v>212</v>
       </c>
       <c r="D83" s="35" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="E83" s="15"/>
       <c r="F83" s="51" t="s">
-        <v>216</v>
+        <v>142</v>
       </c>
       <c r="G83" s="69" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H83" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I83" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J83" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="29"/>
       <c r="B84" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C84" s="18" t="s">
-        <v>160</v>
+        <v>213</v>
       </c>
       <c r="D84" s="21" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>166</v>
+        <v>92</v>
       </c>
       <c r="F84" s="47"/>
       <c r="G84" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I84" s="29" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J84" s="70" t="s">
-        <v>172</v>
+        <v>98</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A85" s="29"/>
       <c r="B85" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C85" s="18" t="s">
-        <v>161</v>
+        <v>214</v>
       </c>
       <c r="D85" s="21" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>166</v>
+        <v>92</v>
       </c>
       <c r="F85" s="47" t="s">
-        <v>212</v>
+        <v>138</v>
       </c>
       <c r="G85" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H85" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I85" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J85" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A86" s="29"/>
       <c r="B86" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C86" s="18" t="s">
-        <v>162</v>
+        <v>215</v>
       </c>
       <c r="D86" s="21" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>166</v>
+        <v>92</v>
       </c>
       <c r="F86" s="47" t="s">
-        <v>213</v>
+        <v>139</v>
       </c>
       <c r="G86" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H86" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I86" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J86" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="29"/>
       <c r="B87" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C87" s="18" t="s">
-        <v>163</v>
+        <v>216</v>
       </c>
       <c r="D87" s="35" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="E87" s="15"/>
       <c r="F87" s="51" t="s">
-        <v>168</v>
+        <v>94</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I87" s="29" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J87" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="29"/>
       <c r="B88" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C88" s="18" t="s">
-        <v>164</v>
+        <v>217</v>
       </c>
       <c r="D88" s="21" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>166</v>
+        <v>92</v>
       </c>
       <c r="F88" s="49" t="s">
-        <v>217</v>
+        <v>143</v>
       </c>
       <c r="G88" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H88" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I88" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J88" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="29"/>
       <c r="B89" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C89" s="18" t="s">
-        <v>165</v>
+        <v>218</v>
       </c>
       <c r="D89" s="21" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>166</v>
+        <v>92</v>
       </c>
       <c r="F89" s="47" t="s">
-        <v>211</v>
+        <v>137</v>
       </c>
       <c r="G89" s="17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H89" s="17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I89" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J89" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/mapping/field_mapping.xlsx
+++ b/mapping/field_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Water collectives\WHS Assessment\auto gen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB3D833-7D59-4E6B-B40E-B72CC18A9DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D74C489-25A6-4637-8D50-A84E523D1ACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B03A0D84-276C-499F-A511-71567CA886FB}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="221">
   <si>
     <t>Sl.No</t>
   </si>
@@ -124,9 +124,6 @@
   </si>
   <si>
     <t>% of small and marginal farmers covered</t>
-  </si>
-  <si>
-    <t>GPS Location</t>
   </si>
   <si>
     <t>Diversion location name</t>
@@ -377,12 +374,6 @@
     <t>whs-extent_rabi</t>
   </si>
   <si>
-    <t>whs-small_marg_hhs%</t>
-  </si>
-  <si>
-    <t>whs-structure_gps</t>
-  </si>
-  <si>
     <t>basic_details_repairs-district</t>
   </si>
   <si>
@@ -711,13 +702,28 @@
   </si>
   <si>
     <t>C75</t>
+  </si>
+  <si>
+    <t>whs-small_marg_hhs_perc</t>
+  </si>
+  <si>
+    <t>Lattitude- source</t>
+  </si>
+  <si>
+    <t>Longitude- source</t>
+  </si>
+  <si>
+    <t>whs-structure_gps-Latitude</t>
+  </si>
+  <si>
+    <t>whs-structure_gps-Longitude</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -882,6 +888,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -948,7 +961,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1000,12 +1013,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1068,12 +1075,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1142,6 +1143,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1464,7 +1469,7 @@
     <col min="3" max="3" width="9.140625" style="3"/>
     <col min="4" max="4" width="39" style="10" customWidth="1"/>
     <col min="5" max="5" width="28.7109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.42578125" style="55" customWidth="1"/>
+    <col min="6" max="6" width="38.42578125" style="51" customWidth="1"/>
     <col min="7" max="8" width="18.28515625" customWidth="1"/>
     <col min="9" max="9" width="28.140625" style="3" customWidth="1"/>
     <col min="10" max="10" width="15.7109375" bestFit="1" customWidth="1"/>
@@ -1486,7 +1491,7 @@
       <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="37" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
@@ -1498,8 +1503,8 @@
       <c r="I1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="68" t="s">
-        <v>95</v>
+      <c r="J1" s="64" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1510,16 +1515,16 @@
         <v>7</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="D2" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2" s="34" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="40" t="s">
-        <v>99</v>
+      <c r="F2" s="38" t="s">
+        <v>98</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>22</v>
@@ -1531,7 +1536,7 @@
         <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1542,16 +1547,16 @@
         <v>7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D3" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3" s="34" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="40" t="s">
-        <v>100</v>
+      <c r="F3" s="38" t="s">
+        <v>99</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>22</v>
@@ -1563,7 +1568,7 @@
         <v>9</v>
       </c>
       <c r="J3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1574,7 +1579,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>14</v>
@@ -1582,8 +1587,8 @@
       <c r="E4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="41" t="s">
-        <v>101</v>
+      <c r="F4" s="39" t="s">
+        <v>100</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>22</v>
@@ -1595,7 +1600,7 @@
         <v>9</v>
       </c>
       <c r="J4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1606,7 +1611,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>15</v>
@@ -1614,8 +1619,8 @@
       <c r="E5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="41" t="s">
-        <v>102</v>
+      <c r="F5" s="39" t="s">
+        <v>101</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>22</v>
@@ -1627,7 +1632,7 @@
         <v>9</v>
       </c>
       <c r="J5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1638,7 +1643,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>16</v>
@@ -1646,8 +1651,8 @@
       <c r="E6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="41" t="s">
-        <v>103</v>
+      <c r="F6" s="39" t="s">
+        <v>102</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>22</v>
@@ -1659,7 +1664,7 @@
         <v>12</v>
       </c>
       <c r="J6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1670,16 +1675,16 @@
         <v>7</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D7" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="D7" s="35" t="s">
         <v>17</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="41" t="s">
-        <v>104</v>
+      <c r="F7" s="39" t="s">
+        <v>103</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>22</v>
@@ -1691,7 +1696,7 @@
         <v>12</v>
       </c>
       <c r="J7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1702,7 +1707,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>18</v>
@@ -1711,7 +1716,7 @@
         <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>22</v>
@@ -1723,7 +1728,7 @@
         <v>9</v>
       </c>
       <c r="J8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1734,24 +1739,24 @@
         <v>7</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E9" s="7"/>
-      <c r="F9" s="41"/>
+      <c r="F9" s="39"/>
       <c r="G9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="69" t="s">
+      <c r="H9" s="65" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J9" s="70" t="s">
-        <v>98</v>
+      <c r="J9" s="66" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1762,13 +1767,13 @@
         <v>7</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>25</v>
       </c>
       <c r="E10" s="7"/>
-      <c r="F10" s="41"/>
+      <c r="F10" s="39"/>
       <c r="G10" s="2" t="s">
         <v>24</v>
       </c>
@@ -1778,8 +1783,8 @@
       <c r="I10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J10" s="70" t="s">
-        <v>98</v>
+      <c r="J10" s="66" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -1790,7 +1795,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>27</v>
@@ -1798,8 +1803,8 @@
       <c r="E11" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="42" t="s">
-        <v>105</v>
+      <c r="F11" s="40" t="s">
+        <v>104</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>22</v>
@@ -1811,7 +1816,7 @@
         <v>9</v>
       </c>
       <c r="J11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1822,7 +1827,7 @@
         <v>7</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>28</v>
@@ -1830,8 +1835,8 @@
       <c r="E12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="42" t="s">
-        <v>106</v>
+      <c r="F12" s="40" t="s">
+        <v>105</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>22</v>
@@ -1843,7 +1848,7 @@
         <v>9</v>
       </c>
       <c r="J12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -1854,7 +1859,7 @@
         <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>29</v>
@@ -1862,7 +1867,7 @@
       <c r="E13" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="42"/>
+      <c r="F13" s="40"/>
       <c r="G13" s="2" t="s">
         <v>30</v>
       </c>
@@ -1873,7 +1878,7 @@
         <v>26</v>
       </c>
       <c r="J13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -1884,7 +1889,7 @@
         <v>7</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D14" s="16" t="s">
         <v>31</v>
@@ -1892,8 +1897,8 @@
       <c r="E14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="42" t="s">
-        <v>107</v>
+      <c r="F14" s="40" t="s">
+        <v>216</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>22</v>
@@ -1905,7 +1910,7 @@
         <v>9</v>
       </c>
       <c r="J14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -1916,16 +1921,16 @@
         <v>7</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>32</v>
+        <v>155</v>
+      </c>
+      <c r="D15" s="67" t="s">
+        <v>217</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="43" t="s">
-        <v>108</v>
+      <c r="F15" s="68" t="s">
+        <v>219</v>
       </c>
       <c r="G15" s="17" t="s">
         <v>22</v>
@@ -1937,96 +1942,122 @@
         <v>9</v>
       </c>
       <c r="J15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="18"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="18"/>
-      <c r="J16"/>
+      <c r="A16" s="6">
+        <v>14</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D16" s="67" t="s">
+        <v>218</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="68" t="s">
+        <v>220</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="17" spans="1:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="18"/>
+      <c r="A17" s="6">
+        <v>15</v>
+      </c>
       <c r="B17" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="D17" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="22" t="s">
+      <c r="F17" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>16</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D18" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="F17" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="G17" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H17" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I17" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="6"/>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="D18" s="21" t="s">
+      <c r="E18" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H18" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J18" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>17</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="F18" s="41" t="s">
-        <v>110</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H18" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J18" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="6"/>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" s="22"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="22" t="s">
-        <v>38</v>
+      <c r="E19" s="20"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="20" t="s">
+        <v>37</v>
       </c>
       <c r="H19" s="17" t="s">
         <v>23</v>
@@ -2035,24 +2066,26 @@
         <v>26</v>
       </c>
       <c r="J19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="6"/>
+      <c r="A20" s="6">
+        <v>18</v>
+      </c>
       <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D20" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="20"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="20" t="s">
         <v>37</v>
-      </c>
-      <c r="E20" s="22"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="22" t="s">
-        <v>38</v>
       </c>
       <c r="H20" s="17" t="s">
         <v>23</v>
@@ -2061,25 +2094,27 @@
         <v>26</v>
       </c>
       <c r="J20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
+      <c r="A21" s="6">
+        <v>19</v>
+      </c>
       <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>39</v>
+        <v>147</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>38</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F21" s="41" t="s">
-        <v>111</v>
+      <c r="F21" s="39" t="s">
+        <v>108</v>
       </c>
       <c r="G21" s="17" t="s">
         <v>22</v>
@@ -2091,82 +2126,88 @@
         <v>9</v>
       </c>
       <c r="J21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="6"/>
+      <c r="A22" s="6">
+        <v>20</v>
+      </c>
       <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="D22" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="F22" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I22" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J22" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>21</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D23" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="F22" s="45" t="s">
-        <v>112</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I22" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J22" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="6"/>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="D23" s="21" t="s">
+      <c r="E23" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23" s="41" t="s">
+        <v>110</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I23" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J23" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>22</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="D24" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="E23" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="45" t="s">
-        <v>113</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H23" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I23" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J23" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="6"/>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="D24" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" s="24"/>
-      <c r="F24" s="45"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="41"/>
       <c r="G24" s="2" t="s">
         <v>24</v>
       </c>
@@ -2176,53 +2217,57 @@
       <c r="I24" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="J24" s="70" t="s">
-        <v>98</v>
+      <c r="J24" s="66" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A25" s="6"/>
+      <c r="A25" s="6">
+        <v>23</v>
+      </c>
       <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="D25" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="G25" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H25" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I25" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J25" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <v>24</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="D26" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="E25" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="F25" s="46" t="s">
-        <v>114</v>
-      </c>
-      <c r="G25" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H25" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I25" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J25" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="6"/>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="D26" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="E26" s="24"/>
-      <c r="F26" s="45"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="41"/>
       <c r="G26" s="2" t="s">
         <v>24</v>
       </c>
@@ -2232,297 +2277,317 @@
       <c r="I26" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="J26" s="70" t="s">
-        <v>98</v>
+      <c r="J26" s="66" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="6"/>
+      <c r="A27" s="6">
+        <v>25</v>
+      </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="G27" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H27" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I27" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J27" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>26</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="G28" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H28" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I28" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J28" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <v>27</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D29" s="52" t="s">
+        <v>47</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F29" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="G29" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H29" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I29" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J29" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>28</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="D27" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="E27" s="24" t="s">
+      <c r="D30" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F30" s="54" t="s">
+        <v>115</v>
+      </c>
+      <c r="G30" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="H30" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="I30" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J30" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>29</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="D31" s="52" t="s">
+        <v>49</v>
+      </c>
+      <c r="E31" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="G31" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="H31" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="I31" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J31" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>30</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="E32" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F32" s="54" t="s">
+        <v>117</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H32" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I32" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J32" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>31</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="D33" s="57" t="s">
+        <v>92</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F33" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="G33" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H33" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I33" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J33" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>32</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F34" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="G34" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H34" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I34" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J34" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>33</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="D35" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E35" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F35" s="54" t="s">
+        <v>120</v>
+      </c>
+      <c r="G35" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H35" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I35" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J35" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
         <v>34</v>
       </c>
-      <c r="F27" s="47" t="s">
-        <v>115</v>
-      </c>
-      <c r="G27" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H27" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I27" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="6"/>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="D28" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="E28" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="F28" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="G28" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H28" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I28" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J28" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="6"/>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="D29" s="56" t="s">
-        <v>48</v>
-      </c>
-      <c r="E29" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="F29" s="47" t="s">
-        <v>117</v>
-      </c>
-      <c r="G29" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H29" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I29" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J29" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="6"/>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="D30" s="56" t="s">
-        <v>49</v>
-      </c>
-      <c r="E30" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="F30" s="58" t="s">
-        <v>118</v>
-      </c>
-      <c r="G30" s="59" t="s">
-        <v>22</v>
-      </c>
-      <c r="H30" s="59" t="s">
-        <v>23</v>
-      </c>
-      <c r="I30" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J30" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="6"/>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="D31" s="56" t="s">
-        <v>50</v>
-      </c>
-      <c r="E31" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="F31" s="60" t="s">
-        <v>119</v>
-      </c>
-      <c r="G31" s="59" t="s">
-        <v>22</v>
-      </c>
-      <c r="H31" s="59" t="s">
-        <v>23</v>
-      </c>
-      <c r="I31" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J31" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="6"/>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="D32" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="E32" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="F32" s="58" t="s">
-        <v>120</v>
-      </c>
-      <c r="G32" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H32" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I32" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J32" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="6"/>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="18" t="s">
+      <c r="B36" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="D33" s="61" t="s">
-        <v>93</v>
-      </c>
-      <c r="E33" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="F33" s="58" t="s">
+      <c r="D36" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F36" s="56" t="s">
         <v>121</v>
       </c>
-      <c r="G33" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H33" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I33" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J33" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="6"/>
-      <c r="B34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="D34" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E34" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="F34" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="G34" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H34" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I34" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J34" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="6"/>
-      <c r="B35" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="D35" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E35" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="F35" s="58" t="s">
-        <v>123</v>
-      </c>
-      <c r="G35" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H35" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I35" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J35" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A36" s="6"/>
-      <c r="B36" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="D36" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="E36" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="F36" s="60" t="s">
-        <v>124</v>
-      </c>
       <c r="G36" s="17" t="s">
         <v>22</v>
       </c>
@@ -2533,7 +2598,7 @@
         <v>9</v>
       </c>
       <c r="J36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2544,16 +2609,16 @@
         <v>11</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="D37" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="E37" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="F37" s="60" t="s">
-        <v>125</v>
+        <v>163</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F37" s="56" t="s">
+        <v>122</v>
       </c>
       <c r="G37" s="17" t="s">
         <v>22</v>
@@ -2565,7 +2630,7 @@
         <v>9</v>
       </c>
       <c r="J37" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2576,16 +2641,16 @@
         <v>11</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="D38" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="E38" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="F38" s="50" t="s">
-        <v>126</v>
+        <v>164</v>
+      </c>
+      <c r="D38" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="E38" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F38" s="46" t="s">
+        <v>123</v>
       </c>
       <c r="G38" s="17" t="s">
         <v>22</v>
@@ -2597,7 +2662,7 @@
         <v>9</v>
       </c>
       <c r="J38" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2608,347 +2673,347 @@
         <v>11</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="D39" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="E39" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F39" s="46" t="s">
+        <v>123</v>
+      </c>
+      <c r="G39" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H39" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I39" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J39" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" s="62" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="58"/>
+      <c r="B40" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="60" t="s">
+        <v>166</v>
+      </c>
+      <c r="D40" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="E39" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="F39" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="G39" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H39" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I39" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J39" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" s="66" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="62"/>
-      <c r="B40" s="63" t="s">
-        <v>11</v>
-      </c>
-      <c r="C40" s="64" t="s">
-        <v>169</v>
-      </c>
-      <c r="D40" s="26" t="s">
+      <c r="E40" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="F40" s="44"/>
+      <c r="G40" s="61" t="s">
+        <v>22</v>
+      </c>
+      <c r="H40" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="I40" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="J40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="27"/>
+      <c r="B41" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="D41" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="E40" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="F40" s="48"/>
-      <c r="G40" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="H40" s="65" t="s">
-        <v>23</v>
-      </c>
-      <c r="I40" s="62" t="s">
-        <v>26</v>
-      </c>
-      <c r="J40" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="29"/>
-      <c r="B41" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C41" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="D41" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="E41" s="30"/>
-      <c r="F41" s="51"/>
+      <c r="E41" s="28"/>
+      <c r="F41" s="47"/>
       <c r="G41" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I41" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="J41" s="70" t="s">
-        <v>98</v>
+      <c r="I41" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="J41" s="66" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="29"/>
+      <c r="A42" s="27"/>
       <c r="B42" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C42" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="D42" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E42" s="14"/>
+      <c r="F42" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I42" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="J42" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="27"/>
+      <c r="B43" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="D43" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="E43" s="14"/>
+      <c r="F43" s="43" t="s">
+        <v>125</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I43" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="J43" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="27"/>
+      <c r="B44" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="D44" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="E44" s="1"/>
+      <c r="F44" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="G44" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H44" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I44" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J44" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="27"/>
+      <c r="B45" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="D42" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="E42" s="14"/>
-      <c r="F42" s="47" t="s">
+      <c r="D45" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="E45" s="14"/>
+      <c r="F45" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I42" s="29" t="s">
+      <c r="G45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I45" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="J42" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="29"/>
-      <c r="B43" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C43" s="18" t="s">
+      <c r="J45" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="27"/>
+      <c r="B46" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="D43" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="E43" s="14"/>
-      <c r="F43" s="47" t="s">
+      <c r="D46" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E46" s="14"/>
+      <c r="F46" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I46" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="J46" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="27"/>
+      <c r="B47" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="D47" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E47" s="14"/>
+      <c r="F47" s="54" t="s">
+        <v>120</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I47" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="J47" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="27"/>
+      <c r="B48" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="D48" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="E48" s="29"/>
+      <c r="F48" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I43" s="29" t="s">
+      <c r="G48" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I48" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="J43" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="29"/>
-      <c r="B44" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C44" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="D44" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="E44" s="1"/>
-      <c r="F44" s="47" t="s">
-        <v>129</v>
-      </c>
-      <c r="G44" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H44" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I44" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J44" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="29"/>
-      <c r="B45" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C45" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="D45" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="E45" s="14"/>
-      <c r="F45" s="47" t="s">
-        <v>130</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I45" s="29" t="s">
+      <c r="J48" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="27"/>
+      <c r="B49" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="D49" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="E49" s="29"/>
+      <c r="F49" s="48" t="s">
+        <v>128</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I49" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="J45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="29"/>
-      <c r="B46" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C46" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="D46" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E46" s="14"/>
-      <c r="F46" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I46" s="29" t="s">
+      <c r="J49" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" s="62" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="58"/>
+      <c r="B50" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="C50" s="60" t="s">
+        <v>176</v>
+      </c>
+      <c r="D50" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="E50" s="25"/>
+      <c r="F50" s="44"/>
+      <c r="G50" s="61" t="s">
+        <v>22</v>
+      </c>
+      <c r="H50" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="I50" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="J46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="29"/>
-      <c r="B47" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C47" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="D47" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E47" s="14"/>
-      <c r="F47" s="58" t="s">
-        <v>123</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I47" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="J47" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="29"/>
-      <c r="B48" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C48" s="18" t="s">
+      <c r="J50" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="27"/>
+      <c r="B51" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="D48" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="E48" s="31"/>
-      <c r="F48" s="52" t="s">
-        <v>131</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I48" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="J48" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="29"/>
-      <c r="B49" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C49" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="D49" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="E49" s="31"/>
-      <c r="F49" s="52" t="s">
-        <v>131</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I49" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="J49" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" s="66" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="62"/>
-      <c r="B50" s="63" t="s">
-        <v>11</v>
-      </c>
-      <c r="C50" s="64" t="s">
-        <v>179</v>
-      </c>
-      <c r="D50" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="E50" s="27"/>
-      <c r="F50" s="48"/>
-      <c r="G50" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="H50" s="65" t="s">
-        <v>23</v>
-      </c>
-      <c r="I50" s="62" t="s">
-        <v>26</v>
-      </c>
-      <c r="J50" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="29"/>
-      <c r="B51" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C51" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="D51" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="E51" s="30"/>
-      <c r="F51" s="51"/>
+      <c r="D51" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="E51" s="28"/>
+      <c r="F51" s="47"/>
       <c r="G51" s="2" t="s">
         <v>24</v>
       </c>
@@ -2958,381 +3023,381 @@
       <c r="I51" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="J51" s="70" t="s">
-        <v>98</v>
+      <c r="J51" s="66" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="29"/>
+      <c r="A52" s="27"/>
       <c r="B52" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C52" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="D52" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E52" s="14"/>
+      <c r="F52" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I52" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="J52" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="27"/>
+      <c r="B53" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="D53" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E53" s="14"/>
+      <c r="F53" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I53" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="J53" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="27"/>
+      <c r="B54" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="D54" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E54" s="14"/>
+      <c r="F54" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I54" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="J54" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="27"/>
+      <c r="B55" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="D52" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="E52" s="14"/>
-      <c r="F52" s="47" t="s">
+      <c r="D55" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E55" s="14"/>
+      <c r="F55" s="54" t="s">
         <v>115</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I52" s="29" t="s">
+      <c r="G55" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I55" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="J52" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="29"/>
-      <c r="B53" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C53" s="18" t="s">
+      <c r="J55" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A56" s="27"/>
+      <c r="B56" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="D53" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="E53" s="14"/>
-      <c r="F53" s="47" t="s">
+      <c r="D56" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="E56" s="14"/>
+      <c r="F56" s="56" t="s">
         <v>116</v>
       </c>
-      <c r="G53" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I53" s="29" t="s">
+      <c r="G56" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I56" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="J53" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="29"/>
-      <c r="B54" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C54" s="18" t="s">
+      <c r="J56" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="27"/>
+      <c r="B57" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="D54" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="E54" s="14"/>
-      <c r="F54" s="47" t="s">
+      <c r="D57" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="E57" s="14"/>
+      <c r="F57" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="G54" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I54" s="29" t="s">
+      <c r="G57" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H57" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I57" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J57" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A58" s="27"/>
+      <c r="B58" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="D58" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="E58" s="14"/>
+      <c r="F58" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I58" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="J54" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="29"/>
-      <c r="B55" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C55" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="D55" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="E55" s="14"/>
-      <c r="F55" s="58" t="s">
-        <v>118</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I55" s="29" t="s">
+      <c r="J58" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A59" s="27"/>
+      <c r="B59" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="D59" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="E59" s="19"/>
+      <c r="F59" s="42"/>
+      <c r="G59" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I59" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="J55" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="29"/>
-      <c r="B56" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C56" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="D56" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="E56" s="14"/>
-      <c r="F56" s="60" t="s">
-        <v>119</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I56" s="29" t="s">
+      <c r="J59" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A60" s="27"/>
+      <c r="B60" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="D60" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="E60" s="19"/>
+      <c r="F60" s="42"/>
+      <c r="G60" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I60" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="J56" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="29"/>
-      <c r="B57" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C57" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="D57" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="E57" s="14"/>
-      <c r="F57" s="58" t="s">
-        <v>120</v>
-      </c>
-      <c r="G57" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H57" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I57" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J57" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="29"/>
-      <c r="B58" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C58" s="18" t="s">
+      <c r="J60" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A61" s="27"/>
+      <c r="B61" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="D58" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="E58" s="14"/>
-      <c r="F58" s="58" t="s">
-        <v>121</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I58" s="29" t="s">
+      <c r="D61" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="E61" s="14"/>
+      <c r="F61" s="43" t="s">
+        <v>129</v>
+      </c>
+      <c r="G61" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H61" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I61" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J61" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="27"/>
+      <c r="B62" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="D62" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="E62" s="29"/>
+      <c r="F62" s="48" t="s">
+        <v>128</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I62" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="J58" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A59" s="29"/>
-      <c r="B59" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C59" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="D59" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E59" s="21"/>
-      <c r="F59" s="46"/>
-      <c r="G59" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I59" s="29" t="s">
+      <c r="J62" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A63" s="27"/>
+      <c r="B63" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="D63" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="E63" s="29"/>
+      <c r="F63" s="48" t="s">
+        <v>128</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I63" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="J59" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A60" s="29"/>
-      <c r="B60" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C60" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="D60" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="E60" s="21"/>
-      <c r="F60" s="46"/>
-      <c r="G60" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I60" s="29" t="s">
+      <c r="J63" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" s="62" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A64" s="58"/>
+      <c r="B64" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" s="60" t="s">
+        <v>190</v>
+      </c>
+      <c r="D64" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="E64" s="25"/>
+      <c r="F64" s="44"/>
+      <c r="G64" s="61" t="s">
+        <v>22</v>
+      </c>
+      <c r="H64" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="I64" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="J60" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="29"/>
-      <c r="B61" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C61" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="D61" s="21" t="s">
+      <c r="J64" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A65" s="27"/>
+      <c r="B65" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="D65" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="E61" s="14"/>
-      <c r="F61" s="47" t="s">
-        <v>132</v>
-      </c>
-      <c r="G61" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H61" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I61" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J61" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="29"/>
-      <c r="B62" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C62" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="D62" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="E62" s="31"/>
-      <c r="F62" s="52" t="s">
-        <v>131</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I62" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="J62" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="29"/>
-      <c r="B63" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C63" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="D63" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="E63" s="31"/>
-      <c r="F63" s="52" t="s">
-        <v>131</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I63" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="J63" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" s="66" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A64" s="62"/>
-      <c r="B64" s="63" t="s">
-        <v>11</v>
-      </c>
-      <c r="C64" s="64" t="s">
-        <v>193</v>
-      </c>
-      <c r="D64" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="E64" s="27"/>
-      <c r="F64" s="48"/>
-      <c r="G64" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="H64" s="65" t="s">
-        <v>23</v>
-      </c>
-      <c r="I64" s="62" t="s">
-        <v>26</v>
-      </c>
-      <c r="J64" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="29"/>
-      <c r="B65" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C65" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="D65" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="E65" s="30"/>
-      <c r="F65" s="51"/>
+      <c r="E65" s="28"/>
+      <c r="F65" s="47"/>
       <c r="G65" s="2" t="s">
         <v>24</v>
       </c>
@@ -3342,131 +3407,131 @@
       <c r="I65" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="J65" s="70" t="s">
-        <v>98</v>
+      <c r="J65" s="66" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="29"/>
+      <c r="A66" s="27"/>
       <c r="B66" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C66" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="D66" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E66" s="14"/>
+      <c r="F66" s="43" t="s">
+        <v>130</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I66" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="J66" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A67" s="27"/>
+      <c r="B67" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="D67" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E67" s="14"/>
+      <c r="F67" s="63" t="s">
+        <v>130</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I67" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="J67" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A68" s="27"/>
+      <c r="B68" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="D68" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="E68" s="14"/>
+      <c r="F68" s="63"/>
+      <c r="G68" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I68" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="J68" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A69" s="27"/>
+      <c r="B69" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="D66" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="E66" s="14"/>
-      <c r="F66" s="47" t="s">
-        <v>133</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I66" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="J66" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="29"/>
-      <c r="B67" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C67" s="18" t="s">
+      <c r="D69" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="E69" s="14"/>
+      <c r="F69" s="63"/>
+      <c r="G69" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I69" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="J69" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A70" s="27"/>
+      <c r="B70" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="D67" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="E67" s="14"/>
-      <c r="F67" s="67" t="s">
-        <v>133</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I67" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="J67" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A68" s="29"/>
-      <c r="B68" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C68" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="D68" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="E68" s="14"/>
-      <c r="F68" s="67"/>
-      <c r="G68" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I68" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="J68" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="29"/>
-      <c r="B69" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C69" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="D69" s="21" t="s">
+      <c r="D70" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="E69" s="14"/>
-      <c r="F69" s="67"/>
-      <c r="G69" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H69" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I69" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="J69" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A70" s="29"/>
-      <c r="B70" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C70" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="D70" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="E70" s="33"/>
-      <c r="F70" s="53"/>
+      <c r="E70" s="31"/>
+      <c r="F70" s="49"/>
       <c r="G70" s="2" t="s">
         <v>24</v>
       </c>
@@ -3476,77 +3541,77 @@
       <c r="I70" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="J70" s="70" t="s">
-        <v>98</v>
+      <c r="J70" s="66" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A71" s="29"/>
+      <c r="A71" s="27"/>
       <c r="B71" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="D71" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="D71" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E71" s="14"/>
+      <c r="F71" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I71" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="J71" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" s="62" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A72" s="58"/>
+      <c r="B72" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" s="60" t="s">
+        <v>198</v>
+      </c>
+      <c r="D72" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="E71" s="14"/>
-      <c r="F71" s="47" t="s">
-        <v>134</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I71" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="J71" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" s="66" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A72" s="62"/>
-      <c r="B72" s="63" t="s">
-        <v>11</v>
-      </c>
-      <c r="C72" s="64" t="s">
-        <v>201</v>
-      </c>
-      <c r="D72" s="26" t="s">
+      <c r="E72" s="25"/>
+      <c r="F72" s="44"/>
+      <c r="G72" s="61" t="s">
+        <v>22</v>
+      </c>
+      <c r="H72" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="I72" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="J72" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A73" s="27"/>
+      <c r="B73" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="D73" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="E72" s="27"/>
-      <c r="F72" s="48"/>
-      <c r="G72" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="H72" s="65" t="s">
-        <v>23</v>
-      </c>
-      <c r="I72" s="62" t="s">
-        <v>26</v>
-      </c>
-      <c r="J72" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="29"/>
-      <c r="B73" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C73" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="D73" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E73" s="30"/>
-      <c r="F73" s="51"/>
+      <c r="E73" s="28"/>
+      <c r="F73" s="47"/>
       <c r="G73" s="2" t="s">
         <v>24</v>
       </c>
@@ -3556,466 +3621,466 @@
       <c r="I73" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="J73" s="70" t="s">
-        <v>98</v>
+      <c r="J73" s="66" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A74" s="29"/>
+      <c r="A74" s="27"/>
       <c r="B74" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="D74" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="F74" s="50" t="s">
+        <v>132</v>
+      </c>
+      <c r="G74" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H74" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I74" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J74" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A75" s="27"/>
+      <c r="B75" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="D75" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="F75" s="43" t="s">
+        <v>133</v>
+      </c>
+      <c r="G75" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H75" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I75" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J75" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A76" s="27"/>
+      <c r="B76" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="D76" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="F76" s="43" t="s">
+        <v>134</v>
+      </c>
+      <c r="G76" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H76" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I76" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J76" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A77" s="27"/>
+      <c r="B77" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C77" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="D74" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="E74" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="F74" s="54" t="s">
+      <c r="D77" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="E77" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="F77" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="G74" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H74" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I74" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J74" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A75" s="29"/>
-      <c r="B75" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C75" s="18" t="s">
+      <c r="G77" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H77" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I77" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J77" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A78" s="27"/>
+      <c r="B78" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="D75" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="E75" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="F75" s="47" t="s">
+      <c r="D78" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="E78" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="F78" s="43" t="s">
         <v>136</v>
       </c>
-      <c r="G75" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H75" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I75" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J75" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="29"/>
-      <c r="B76" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C76" s="18" t="s">
+      <c r="G78" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H78" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I78" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J78" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A79" s="27"/>
+      <c r="B79" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="D76" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="E76" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="F76" s="47" t="s">
-        <v>137</v>
-      </c>
-      <c r="G76" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H76" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I76" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J76" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A77" s="29"/>
-      <c r="B77" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C77" s="18" t="s">
+      <c r="D79" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="E79" s="15"/>
+      <c r="F79" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="G79" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="H79" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I79" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J79" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A80" s="27"/>
+      <c r="B80" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C80" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="D77" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="E77" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="F77" s="47" t="s">
-        <v>138</v>
-      </c>
-      <c r="G77" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H77" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I77" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J77" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="29"/>
-      <c r="B78" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C78" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="D78" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="E78" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="F78" s="47" t="s">
-        <v>139</v>
-      </c>
-      <c r="G78" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H78" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I78" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J78" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="29"/>
-      <c r="B79" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C79" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="D79" s="35" t="s">
+      <c r="D80" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="E79" s="15"/>
-      <c r="F79" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="G79" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="H79" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I79" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J79" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="29"/>
-      <c r="B80" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C80" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="D80" s="21" t="s">
-        <v>83</v>
-      </c>
       <c r="E80" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="F80" s="47"/>
+        <v>91</v>
+      </c>
+      <c r="F80" s="43"/>
       <c r="G80" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I80" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="J80" s="70" t="s">
-        <v>98</v>
+      <c r="I80" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="J80" s="66" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A81" s="29"/>
+      <c r="A81" s="27"/>
       <c r="B81" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="D81" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="E81" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="F81" s="42" t="s">
+        <v>137</v>
+      </c>
+      <c r="G81" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H81" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I81" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J81" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A82" s="27"/>
+      <c r="B82" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="D82" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="E82" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="F82" s="42" t="s">
+        <v>138</v>
+      </c>
+      <c r="G82" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H82" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I82" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J82" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A83" s="27"/>
+      <c r="B83" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C83" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="D83" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="E83" s="15"/>
+      <c r="F83" s="47" t="s">
+        <v>139</v>
+      </c>
+      <c r="G83" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="H83" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I83" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J83" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A84" s="27"/>
+      <c r="B84" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="D81" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="E81" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="F81" s="46" t="s">
-        <v>140</v>
-      </c>
-      <c r="G81" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H81" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I81" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J81" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A82" s="29"/>
-      <c r="B82" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C82" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="D82" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="E82" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="F82" s="46" t="s">
-        <v>141</v>
-      </c>
-      <c r="G82" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H82" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I82" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J82" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A83" s="29"/>
-      <c r="B83" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C83" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="D83" s="35" t="s">
-        <v>86</v>
-      </c>
-      <c r="E83" s="15"/>
-      <c r="F83" s="51" t="s">
-        <v>142</v>
-      </c>
-      <c r="G83" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="H83" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I83" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J83" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A84" s="29"/>
-      <c r="B84" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C84" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="D84" s="21" t="s">
-        <v>79</v>
+      <c r="D84" s="19" t="s">
+        <v>78</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="F84" s="47"/>
+        <v>91</v>
+      </c>
+      <c r="F84" s="43"/>
       <c r="G84" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I84" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="J84" s="70" t="s">
-        <v>98</v>
+      <c r="I84" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="J84" s="66" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A85" s="29"/>
+      <c r="A85" s="27"/>
       <c r="B85" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C85" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="D85" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="E85" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="F85" s="43" t="s">
+        <v>135</v>
+      </c>
+      <c r="G85" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H85" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I85" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J85" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A86" s="27"/>
+      <c r="B86" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C86" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="D86" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="F86" s="43" t="s">
+        <v>136</v>
+      </c>
+      <c r="G86" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H86" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I86" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J86" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A87" s="27"/>
+      <c r="B87" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="D87" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="E87" s="15"/>
+      <c r="F87" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I87" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="J87" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A88" s="27"/>
+      <c r="B88" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="D85" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="E85" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="F85" s="47" t="s">
-        <v>138</v>
-      </c>
-      <c r="G85" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H85" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I85" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J85" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A86" s="29"/>
-      <c r="B86" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C86" s="18" t="s">
+      <c r="D88" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="E88" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="F88" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="G88" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H88" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I88" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J88" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A89" s="27"/>
+      <c r="B89" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="D86" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="E86" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="F86" s="47" t="s">
-        <v>139</v>
-      </c>
-      <c r="G86" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H86" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I86" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J86" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A87" s="29"/>
-      <c r="B87" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C87" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="D87" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="E87" s="15"/>
-      <c r="F87" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I87" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="J87" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A88" s="29"/>
-      <c r="B88" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C88" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="D88" s="21" t="s">
+      <c r="D89" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="E88" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="F88" s="49" t="s">
-        <v>143</v>
-      </c>
-      <c r="G88" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="H88" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I88" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="J88" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A89" s="29"/>
-      <c r="B89" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C89" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="D89" s="21" t="s">
+      <c r="E89" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="E89" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="F89" s="47" t="s">
-        <v>137</v>
+      <c r="F89" s="43" t="s">
+        <v>134</v>
       </c>
       <c r="G89" s="17" t="s">
         <v>22</v>
@@ -4027,7 +4092,7 @@
         <v>9</v>
       </c>
       <c r="J89" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/mapping/field_mapping.xlsx
+++ b/mapping/field_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Water collectives\WHS Assessment\auto gen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D74C489-25A6-4637-8D50-A84E523D1ACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CDBC2E9-379F-409D-BF1E-B70075F15BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B03A0D84-276C-499F-A511-71567CA886FB}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="221">
   <si>
     <t>Sl.No</t>
   </si>
@@ -1772,7 +1772,9 @@
       <c r="D10" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="7"/>
+      <c r="E10" s="7" t="s">
+        <v>13</v>
+      </c>
       <c r="F10" s="39"/>
       <c r="G10" s="2" t="s">
         <v>24</v>

--- a/mapping/field_mapping.xlsx
+++ b/mapping/field_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Water collectives\WHS Assessment\auto gen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CDBC2E9-379F-409D-BF1E-B70075F15BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845ADD18-9230-483A-B2D6-C2EA87031A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B03A0D84-276C-499F-A511-71567CA886FB}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="222">
   <si>
     <t>Sl.No</t>
   </si>
@@ -718,12 +718,15 @@
   <si>
     <t>whs-structure_gps-Longitude</t>
   </si>
+  <si>
+    <t>Mamidipalli</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -806,12 +809,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -961,7 +958,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1043,7 +1040,6 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1063,60 +1059,57 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1131,7 +1124,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1146,7 +1139,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1469,7 +1462,7 @@
     <col min="3" max="3" width="9.140625" style="3"/>
     <col min="4" max="4" width="39" style="10" customWidth="1"/>
     <col min="5" max="5" width="28.7109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.42578125" style="51" customWidth="1"/>
+    <col min="6" max="6" width="38.42578125" style="49" customWidth="1"/>
     <col min="7" max="8" width="18.28515625" customWidth="1"/>
     <col min="9" max="9" width="28.140625" style="3" customWidth="1"/>
     <col min="10" max="10" width="15.7109375" bestFit="1" customWidth="1"/>
@@ -1491,7 +1484,7 @@
       <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="35" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
@@ -1503,7 +1496,7 @@
       <c r="I1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="64" t="s">
+      <c r="J1" s="62" t="s">
         <v>94</v>
       </c>
     </row>
@@ -1517,13 +1510,13 @@
       <c r="C2" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="33" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="38" t="s">
+      <c r="F2" s="36" t="s">
         <v>98</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -1549,13 +1542,13 @@
       <c r="C3" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="34" t="s">
+      <c r="D3" s="33" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="38" t="s">
+      <c r="F3" s="36" t="s">
         <v>99</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -1587,7 +1580,7 @@
       <c r="E4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="39" t="s">
+      <c r="F4" s="37" t="s">
         <v>100</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -1619,7 +1612,7 @@
       <c r="E5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="39" t="s">
+      <c r="F5" s="37" t="s">
         <v>101</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -1651,7 +1644,7 @@
       <c r="E6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="39" t="s">
+      <c r="F6" s="37" t="s">
         <v>102</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -1677,13 +1670,13 @@
       <c r="C7" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="34" t="s">
         <v>17</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="39" t="s">
+      <c r="F7" s="37" t="s">
         <v>103</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -1745,17 +1738,17 @@
         <v>19</v>
       </c>
       <c r="E9" s="7"/>
-      <c r="F9" s="39"/>
+      <c r="F9" s="37"/>
       <c r="G9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="65" t="s">
+      <c r="H9" s="63" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J9" s="66" t="s">
+      <c r="J9" s="64" t="s">
         <v>97</v>
       </c>
     </row>
@@ -1775,7 +1768,7 @@
       <c r="E10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="39"/>
+      <c r="F10" s="37"/>
       <c r="G10" s="2" t="s">
         <v>24</v>
       </c>
@@ -1785,7 +1778,7 @@
       <c r="I10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J10" s="66" t="s">
+      <c r="J10" s="64" t="s">
         <v>97</v>
       </c>
     </row>
@@ -1805,7 +1798,7 @@
       <c r="E11" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="40" t="s">
+      <c r="F11" s="38" t="s">
         <v>104</v>
       </c>
       <c r="G11" s="2" t="s">
@@ -1837,7 +1830,7 @@
       <c r="E12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="40" t="s">
+      <c r="F12" s="38" t="s">
         <v>105</v>
       </c>
       <c r="G12" s="2" t="s">
@@ -1869,7 +1862,7 @@
       <c r="E13" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="40"/>
+      <c r="F13" s="38"/>
       <c r="G13" s="2" t="s">
         <v>30</v>
       </c>
@@ -1899,7 +1892,7 @@
       <c r="E14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="40" t="s">
+      <c r="F14" s="38" t="s">
         <v>216</v>
       </c>
       <c r="G14" s="2" t="s">
@@ -1925,13 +1918,13 @@
       <c r="C15" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="D15" s="67" t="s">
+      <c r="D15" s="65" t="s">
         <v>217</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="68" t="s">
+      <c r="F15" s="66" t="s">
         <v>219</v>
       </c>
       <c r="G15" s="17" t="s">
@@ -1957,13 +1950,13 @@
       <c r="C16" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="D16" s="67" t="s">
+      <c r="D16" s="65" t="s">
         <v>218</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="68" t="s">
+      <c r="F16" s="66" t="s">
         <v>220</v>
       </c>
       <c r="G16" s="17" t="s">
@@ -1995,7 +1988,7 @@
       <c r="E17" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="F17" s="39" t="s">
+      <c r="F17" s="37" t="s">
         <v>106</v>
       </c>
       <c r="G17" s="17" t="s">
@@ -2027,7 +2020,7 @@
       <c r="E18" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="F18" s="39" t="s">
+      <c r="F18" s="37" t="s">
         <v>107</v>
       </c>
       <c r="G18" s="17" t="s">
@@ -2057,7 +2050,7 @@
         <v>35</v>
       </c>
       <c r="E19" s="20"/>
-      <c r="F19" s="39"/>
+      <c r="F19" s="37"/>
       <c r="G19" s="20" t="s">
         <v>37</v>
       </c>
@@ -2085,7 +2078,7 @@
         <v>36</v>
       </c>
       <c r="E20" s="20"/>
-      <c r="F20" s="39"/>
+      <c r="F20" s="37"/>
       <c r="G20" s="20" t="s">
         <v>37</v>
       </c>
@@ -2115,7 +2108,7 @@
       <c r="E21" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F21" s="39" t="s">
+      <c r="F21" s="37" t="s">
         <v>108</v>
       </c>
       <c r="G21" s="17" t="s">
@@ -2147,7 +2140,7 @@
       <c r="E22" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="F22" s="41" t="s">
+      <c r="F22" s="39" t="s">
         <v>109</v>
       </c>
       <c r="G22" s="17" t="s">
@@ -2179,7 +2172,7 @@
       <c r="E23" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="41" t="s">
+      <c r="F23" s="39" t="s">
         <v>110</v>
       </c>
       <c r="G23" s="17" t="s">
@@ -2209,7 +2202,7 @@
         <v>42</v>
       </c>
       <c r="E24" s="22"/>
-      <c r="F24" s="41"/>
+      <c r="F24" s="39"/>
       <c r="G24" s="2" t="s">
         <v>24</v>
       </c>
@@ -2219,7 +2212,7 @@
       <c r="I24" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="J24" s="66" t="s">
+      <c r="J24" s="64" t="s">
         <v>97</v>
       </c>
     </row>
@@ -2239,7 +2232,7 @@
       <c r="E25" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="F25" s="42" t="s">
+      <c r="F25" s="40" t="s">
         <v>111</v>
       </c>
       <c r="G25" s="17" t="s">
@@ -2269,7 +2262,7 @@
         <v>44</v>
       </c>
       <c r="E26" s="22"/>
-      <c r="F26" s="41"/>
+      <c r="F26" s="39"/>
       <c r="G26" s="2" t="s">
         <v>24</v>
       </c>
@@ -2279,7 +2272,7 @@
       <c r="I26" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="J26" s="66" t="s">
+      <c r="J26" s="64" t="s">
         <v>97</v>
       </c>
     </row>
@@ -2299,7 +2292,7 @@
       <c r="E27" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="F27" s="43" t="s">
+      <c r="F27" s="41" t="s">
         <v>112</v>
       </c>
       <c r="G27" s="17" t="s">
@@ -2331,7 +2324,7 @@
       <c r="E28" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="43" t="s">
+      <c r="F28" s="41" t="s">
         <v>113</v>
       </c>
       <c r="G28" s="17" t="s">
@@ -2357,13 +2350,13 @@
       <c r="C29" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="D29" s="52" t="s">
+      <c r="D29" s="50" t="s">
         <v>47</v>
       </c>
       <c r="E29" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="F29" s="43" t="s">
+      <c r="F29" s="41" t="s">
         <v>114</v>
       </c>
       <c r="G29" s="17" t="s">
@@ -2389,19 +2382,19 @@
       <c r="C30" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="D30" s="52" t="s">
+      <c r="D30" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="E30" s="53" t="s">
+      <c r="E30" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="54" t="s">
+      <c r="F30" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="G30" s="55" t="s">
-        <v>22</v>
-      </c>
-      <c r="H30" s="55" t="s">
+      <c r="G30" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="H30" s="53" t="s">
         <v>23</v>
       </c>
       <c r="I30" s="18" t="s">
@@ -2421,19 +2414,19 @@
       <c r="C31" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="D31" s="52" t="s">
+      <c r="D31" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="E31" s="53" t="s">
+      <c r="E31" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="F31" s="56" t="s">
+      <c r="F31" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="G31" s="55" t="s">
-        <v>22</v>
-      </c>
-      <c r="H31" s="55" t="s">
+      <c r="G31" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="H31" s="53" t="s">
         <v>23</v>
       </c>
       <c r="I31" s="18" t="s">
@@ -2459,7 +2452,7 @@
       <c r="E32" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="F32" s="54" t="s">
+      <c r="F32" s="52" t="s">
         <v>117</v>
       </c>
       <c r="G32" s="17" t="s">
@@ -2485,13 +2478,13 @@
       <c r="C33" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="D33" s="57" t="s">
+      <c r="D33" s="55" t="s">
         <v>92</v>
       </c>
       <c r="E33" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="F33" s="54" t="s">
+      <c r="F33" s="52" t="s">
         <v>118</v>
       </c>
       <c r="G33" s="17" t="s">
@@ -2523,7 +2516,7 @@
       <c r="E34" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="F34" s="43" t="s">
+      <c r="F34" s="41" t="s">
         <v>119</v>
       </c>
       <c r="G34" s="17" t="s">
@@ -2555,7 +2548,7 @@
       <c r="E35" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="F35" s="54" t="s">
+      <c r="F35" s="52" t="s">
         <v>120</v>
       </c>
       <c r="G35" s="17" t="s">
@@ -2587,7 +2580,7 @@
       <c r="E36" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="F36" s="56" t="s">
+      <c r="F36" s="54" t="s">
         <v>121</v>
       </c>
       <c r="G36" s="17" t="s">
@@ -2605,7 +2598,7 @@
     </row>
     <row r="37" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>11</v>
@@ -2619,7 +2612,7 @@
       <c r="E37" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="F37" s="56" t="s">
+      <c r="F37" s="54" t="s">
         <v>122</v>
       </c>
       <c r="G37" s="17" t="s">
@@ -2637,7 +2630,7 @@
     </row>
     <row r="38" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>11</v>
@@ -2651,7 +2644,7 @@
       <c r="E38" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="F38" s="46" t="s">
+      <c r="F38" s="44" t="s">
         <v>123</v>
       </c>
       <c r="G38" s="17" t="s">
@@ -2669,7 +2662,7 @@
     </row>
     <row r="39" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>11</v>
@@ -2683,7 +2676,7 @@
       <c r="E39" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="F39" s="46" t="s">
+      <c r="F39" s="44" t="s">
         <v>123</v>
       </c>
       <c r="G39" s="17" t="s">
@@ -2699,28 +2692,30 @@
         <v>95</v>
       </c>
     </row>
-    <row r="40" spans="1:10" s="62" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="58"/>
-      <c r="B40" s="59" t="s">
-        <v>11</v>
-      </c>
-      <c r="C40" s="60" t="s">
+    <row r="40" spans="1:10" s="60" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>38</v>
+      </c>
+      <c r="B40" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="58" t="s">
         <v>166</v>
       </c>
       <c r="D40" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="E40" s="36" t="s">
+      <c r="E40" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="F40" s="44"/>
-      <c r="G40" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="H40" s="61" t="s">
-        <v>23</v>
-      </c>
-      <c r="I40" s="58" t="s">
+      <c r="F40" s="42"/>
+      <c r="G40" s="59" t="s">
+        <v>22</v>
+      </c>
+      <c r="H40" s="59" t="s">
+        <v>23</v>
+      </c>
+      <c r="I40" s="56" t="s">
         <v>26</v>
       </c>
       <c r="J40" t="s">
@@ -2728,7 +2723,9 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="27"/>
+      <c r="A41" s="6">
+        <v>39</v>
+      </c>
       <c r="B41" s="5" t="s">
         <v>11</v>
       </c>
@@ -2739,7 +2736,7 @@
         <v>59</v>
       </c>
       <c r="E41" s="28"/>
-      <c r="F41" s="47"/>
+      <c r="F41" s="45"/>
       <c r="G41" s="1" t="s">
         <v>24</v>
       </c>
@@ -2749,12 +2746,14 @@
       <c r="I41" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="J41" s="66" t="s">
+      <c r="J41" s="64" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="27"/>
+      <c r="A42" s="6">
+        <v>40</v>
+      </c>
       <c r="B42" s="5" t="s">
         <v>11</v>
       </c>
@@ -2764,8 +2763,10 @@
       <c r="D42" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E42" s="14"/>
-      <c r="F42" s="43" t="s">
+      <c r="E42" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F42" s="41" t="s">
         <v>124</v>
       </c>
       <c r="G42" s="1" t="s">
@@ -2782,7 +2783,9 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="27"/>
+      <c r="A43" s="6">
+        <v>41</v>
+      </c>
       <c r="B43" s="5" t="s">
         <v>11</v>
       </c>
@@ -2792,8 +2795,10 @@
       <c r="D43" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="E43" s="14"/>
-      <c r="F43" s="43" t="s">
+      <c r="E43" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F43" s="41" t="s">
         <v>125</v>
       </c>
       <c r="G43" s="1" t="s">
@@ -2810,7 +2815,9 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="27"/>
+      <c r="A44" s="6">
+        <v>42</v>
+      </c>
       <c r="B44" s="5" t="s">
         <v>11</v>
       </c>
@@ -2820,8 +2827,10 @@
       <c r="D44" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E44" s="1"/>
-      <c r="F44" s="43" t="s">
+      <c r="E44" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F44" s="41" t="s">
         <v>126</v>
       </c>
       <c r="G44" s="17" t="s">
@@ -2838,7 +2847,9 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="27"/>
+      <c r="A45" s="6">
+        <v>43</v>
+      </c>
       <c r="B45" s="5" t="s">
         <v>11</v>
       </c>
@@ -2848,8 +2859,10 @@
       <c r="D45" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="E45" s="14"/>
-      <c r="F45" s="43" t="s">
+      <c r="E45" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F45" s="41" t="s">
         <v>127</v>
       </c>
       <c r="G45" s="1" t="s">
@@ -2866,7 +2879,9 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="27"/>
+      <c r="A46" s="6">
+        <v>44</v>
+      </c>
       <c r="B46" s="5" t="s">
         <v>11</v>
       </c>
@@ -2876,8 +2891,10 @@
       <c r="D46" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E46" s="14"/>
-      <c r="F46" s="43" t="s">
+      <c r="E46" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F46" s="41" t="s">
         <v>119</v>
       </c>
       <c r="G46" s="1" t="s">
@@ -2894,7 +2911,9 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="27"/>
+      <c r="A47" s="6">
+        <v>45</v>
+      </c>
       <c r="B47" s="5" t="s">
         <v>11</v>
       </c>
@@ -2904,8 +2923,10 @@
       <c r="D47" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="E47" s="14"/>
-      <c r="F47" s="54" t="s">
+      <c r="E47" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F47" s="52" t="s">
         <v>120</v>
       </c>
       <c r="G47" s="1" t="s">
@@ -2922,7 +2943,9 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="27"/>
+      <c r="A48" s="6">
+        <v>46</v>
+      </c>
       <c r="B48" s="5" t="s">
         <v>11</v>
       </c>
@@ -2932,8 +2955,10 @@
       <c r="D48" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E48" s="29"/>
-      <c r="F48" s="48" t="s">
+      <c r="E48" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F48" s="46" t="s">
         <v>128</v>
       </c>
       <c r="G48" s="1" t="s">
@@ -2950,7 +2975,9 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="27"/>
+      <c r="A49" s="6">
+        <v>47</v>
+      </c>
       <c r="B49" s="5" t="s">
         <v>11</v>
       </c>
@@ -2960,8 +2987,10 @@
       <c r="D49" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="E49" s="29"/>
-      <c r="F49" s="48" t="s">
+      <c r="E49" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F49" s="46" t="s">
         <v>128</v>
       </c>
       <c r="G49" s="1" t="s">
@@ -2977,26 +3006,28 @@
         <v>95</v>
       </c>
     </row>
-    <row r="50" spans="1:10" s="62" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="58"/>
-      <c r="B50" s="59" t="s">
-        <v>11</v>
-      </c>
-      <c r="C50" s="60" t="s">
+    <row r="50" spans="1:10" s="60" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <v>48</v>
+      </c>
+      <c r="B50" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="C50" s="58" t="s">
         <v>176</v>
       </c>
       <c r="D50" s="24" t="s">
         <v>58</v>
       </c>
       <c r="E50" s="25"/>
-      <c r="F50" s="44"/>
-      <c r="G50" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="H50" s="61" t="s">
-        <v>23</v>
-      </c>
-      <c r="I50" s="58" t="s">
+      <c r="F50" s="42"/>
+      <c r="G50" s="59" t="s">
+        <v>22</v>
+      </c>
+      <c r="H50" s="59" t="s">
+        <v>23</v>
+      </c>
+      <c r="I50" s="56" t="s">
         <v>26</v>
       </c>
       <c r="J50" t="s">
@@ -3004,7 +3035,9 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="27"/>
+      <c r="A51" s="6">
+        <v>49</v>
+      </c>
       <c r="B51" s="5" t="s">
         <v>11</v>
       </c>
@@ -3015,7 +3048,7 @@
         <v>60</v>
       </c>
       <c r="E51" s="28"/>
-      <c r="F51" s="47"/>
+      <c r="F51" s="45"/>
       <c r="G51" s="2" t="s">
         <v>24</v>
       </c>
@@ -3025,12 +3058,14 @@
       <c r="I51" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="J51" s="66" t="s">
+      <c r="J51" s="64" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="27"/>
+      <c r="A52" s="6">
+        <v>50</v>
+      </c>
       <c r="B52" s="5" t="s">
         <v>11</v>
       </c>
@@ -3040,8 +3075,10 @@
       <c r="D52" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="E52" s="14"/>
-      <c r="F52" s="43" t="s">
+      <c r="E52" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F52" s="41" t="s">
         <v>112</v>
       </c>
       <c r="G52" s="1" t="s">
@@ -3058,7 +3095,9 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="27"/>
+      <c r="A53" s="6">
+        <v>51</v>
+      </c>
       <c r="B53" s="5" t="s">
         <v>11</v>
       </c>
@@ -3068,8 +3107,10 @@
       <c r="D53" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="E53" s="14"/>
-      <c r="F53" s="43" t="s">
+      <c r="E53" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F53" s="41" t="s">
         <v>113</v>
       </c>
       <c r="G53" s="1" t="s">
@@ -3086,7 +3127,9 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="27"/>
+      <c r="A54" s="6">
+        <v>52</v>
+      </c>
       <c r="B54" s="5" t="s">
         <v>11</v>
       </c>
@@ -3096,8 +3139,10 @@
       <c r="D54" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="E54" s="14"/>
-      <c r="F54" s="43" t="s">
+      <c r="E54" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F54" s="41" t="s">
         <v>114</v>
       </c>
       <c r="G54" s="1" t="s">
@@ -3114,7 +3159,9 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="27"/>
+      <c r="A55" s="6">
+        <v>53</v>
+      </c>
       <c r="B55" s="5" t="s">
         <v>11</v>
       </c>
@@ -3124,8 +3171,10 @@
       <c r="D55" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="E55" s="14"/>
-      <c r="F55" s="54" t="s">
+      <c r="E55" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F55" s="52" t="s">
         <v>115</v>
       </c>
       <c r="G55" s="1" t="s">
@@ -3142,7 +3191,9 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="27"/>
+      <c r="A56" s="6">
+        <v>54</v>
+      </c>
       <c r="B56" s="5" t="s">
         <v>11</v>
       </c>
@@ -3152,8 +3203,10 @@
       <c r="D56" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="E56" s="14"/>
-      <c r="F56" s="56" t="s">
+      <c r="E56" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F56" s="54" t="s">
         <v>116</v>
       </c>
       <c r="G56" s="1" t="s">
@@ -3170,7 +3223,9 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="27"/>
+      <c r="A57" s="6">
+        <v>55</v>
+      </c>
       <c r="B57" s="5" t="s">
         <v>11</v>
       </c>
@@ -3180,8 +3235,10 @@
       <c r="D57" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E57" s="14"/>
-      <c r="F57" s="54" t="s">
+      <c r="E57" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F57" s="52" t="s">
         <v>117</v>
       </c>
       <c r="G57" s="17" t="s">
@@ -3198,7 +3255,9 @@
       </c>
     </row>
     <row r="58" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="27"/>
+      <c r="A58" s="6">
+        <v>56</v>
+      </c>
       <c r="B58" s="5" t="s">
         <v>11</v>
       </c>
@@ -3208,8 +3267,10 @@
       <c r="D58" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="E58" s="14"/>
-      <c r="F58" s="54" t="s">
+      <c r="E58" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F58" s="52" t="s">
         <v>118</v>
       </c>
       <c r="G58" s="1" t="s">
@@ -3226,7 +3287,9 @@
       </c>
     </row>
     <row r="59" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A59" s="27"/>
+      <c r="A59" s="6">
+        <v>57</v>
+      </c>
       <c r="B59" s="5" t="s">
         <v>11</v>
       </c>
@@ -3237,7 +3300,7 @@
         <v>64</v>
       </c>
       <c r="E59" s="19"/>
-      <c r="F59" s="42"/>
+      <c r="F59" s="40"/>
       <c r="G59" s="1" t="s">
         <v>22</v>
       </c>
@@ -3252,7 +3315,9 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A60" s="27"/>
+      <c r="A60" s="6">
+        <v>58</v>
+      </c>
       <c r="B60" s="5" t="s">
         <v>11</v>
       </c>
@@ -3263,7 +3328,7 @@
         <v>65</v>
       </c>
       <c r="E60" s="19"/>
-      <c r="F60" s="42"/>
+      <c r="F60" s="40"/>
       <c r="G60" s="1" t="s">
         <v>22</v>
       </c>
@@ -3278,7 +3343,9 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="27"/>
+      <c r="A61" s="6">
+        <v>59</v>
+      </c>
       <c r="B61" s="5" t="s">
         <v>11</v>
       </c>
@@ -3288,8 +3355,10 @@
       <c r="D61" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="E61" s="14"/>
-      <c r="F61" s="43" t="s">
+      <c r="E61" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F61" s="41" t="s">
         <v>129</v>
       </c>
       <c r="G61" s="17" t="s">
@@ -3306,7 +3375,9 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="27"/>
+      <c r="A62" s="6">
+        <v>60</v>
+      </c>
       <c r="B62" s="5" t="s">
         <v>11</v>
       </c>
@@ -3316,8 +3387,10 @@
       <c r="D62" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E62" s="29"/>
-      <c r="F62" s="48" t="s">
+      <c r="E62" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F62" s="46" t="s">
         <v>128</v>
       </c>
       <c r="G62" s="1" t="s">
@@ -3334,7 +3407,9 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="27"/>
+      <c r="A63" s="6">
+        <v>61</v>
+      </c>
       <c r="B63" s="5" t="s">
         <v>11</v>
       </c>
@@ -3344,8 +3419,10 @@
       <c r="D63" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="E63" s="29"/>
-      <c r="F63" s="48" t="s">
+      <c r="E63" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F63" s="46" t="s">
         <v>128</v>
       </c>
       <c r="G63" s="1" t="s">
@@ -3361,26 +3438,28 @@
         <v>95</v>
       </c>
     </row>
-    <row r="64" spans="1:10" s="62" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A64" s="58"/>
-      <c r="B64" s="59" t="s">
-        <v>11</v>
-      </c>
-      <c r="C64" s="60" t="s">
+    <row r="64" spans="1:10" s="60" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A64" s="6">
+        <v>62</v>
+      </c>
+      <c r="B64" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" s="58" t="s">
         <v>190</v>
       </c>
       <c r="D64" s="24" t="s">
         <v>58</v>
       </c>
       <c r="E64" s="25"/>
-      <c r="F64" s="44"/>
-      <c r="G64" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="H64" s="61" t="s">
-        <v>23</v>
-      </c>
-      <c r="I64" s="58" t="s">
+      <c r="F64" s="42"/>
+      <c r="G64" s="59" t="s">
+        <v>22</v>
+      </c>
+      <c r="H64" s="59" t="s">
+        <v>23</v>
+      </c>
+      <c r="I64" s="56" t="s">
         <v>26</v>
       </c>
       <c r="J64" t="s">
@@ -3388,7 +3467,9 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="27"/>
+      <c r="A65" s="6">
+        <v>63</v>
+      </c>
       <c r="B65" s="5" t="s">
         <v>11</v>
       </c>
@@ -3399,7 +3480,7 @@
         <v>67</v>
       </c>
       <c r="E65" s="28"/>
-      <c r="F65" s="47"/>
+      <c r="F65" s="45"/>
       <c r="G65" s="2" t="s">
         <v>24</v>
       </c>
@@ -3409,12 +3490,14 @@
       <c r="I65" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="J65" s="66" t="s">
+      <c r="J65" s="64" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="27"/>
+      <c r="A66" s="6">
+        <v>64</v>
+      </c>
       <c r="B66" s="5" t="s">
         <v>11</v>
       </c>
@@ -3424,8 +3507,10 @@
       <c r="D66" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="E66" s="14"/>
-      <c r="F66" s="43" t="s">
+      <c r="E66" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F66" s="41" t="s">
         <v>130</v>
       </c>
       <c r="G66" s="1" t="s">
@@ -3442,7 +3527,9 @@
       </c>
     </row>
     <row r="67" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="27"/>
+      <c r="A67" s="6">
+        <v>65</v>
+      </c>
       <c r="B67" s="5" t="s">
         <v>11</v>
       </c>
@@ -3452,8 +3539,10 @@
       <c r="D67" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="E67" s="14"/>
-      <c r="F67" s="63" t="s">
+      <c r="E67" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F67" s="61" t="s">
         <v>130</v>
       </c>
       <c r="G67" s="1" t="s">
@@ -3470,7 +3559,9 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A68" s="27"/>
+      <c r="A68" s="6">
+        <v>66</v>
+      </c>
       <c r="B68" s="5" t="s">
         <v>11</v>
       </c>
@@ -3481,7 +3572,7 @@
         <v>70</v>
       </c>
       <c r="E68" s="14"/>
-      <c r="F68" s="63"/>
+      <c r="F68" s="61"/>
       <c r="G68" s="1" t="s">
         <v>22</v>
       </c>
@@ -3496,7 +3587,9 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="27"/>
+      <c r="A69" s="6">
+        <v>67</v>
+      </c>
       <c r="B69" s="5" t="s">
         <v>11</v>
       </c>
@@ -3507,7 +3600,7 @@
         <v>71</v>
       </c>
       <c r="E69" s="14"/>
-      <c r="F69" s="63"/>
+      <c r="F69" s="61"/>
       <c r="G69" s="1" t="s">
         <v>22</v>
       </c>
@@ -3522,18 +3615,20 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A70" s="27"/>
+      <c r="A70" s="6">
+        <v>68</v>
+      </c>
       <c r="B70" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="D70" s="30" t="s">
+      <c r="D70" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="E70" s="31"/>
-      <c r="F70" s="49"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="47"/>
       <c r="G70" s="2" t="s">
         <v>24</v>
       </c>
@@ -3543,12 +3638,14 @@
       <c r="I70" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="J70" s="66" t="s">
+      <c r="J70" s="64" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A71" s="27"/>
+      <c r="A71" s="6">
+        <v>69</v>
+      </c>
       <c r="B71" s="5" t="s">
         <v>11</v>
       </c>
@@ -3558,8 +3655,10 @@
       <c r="D71" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="E71" s="14"/>
-      <c r="F71" s="43" t="s">
+      <c r="E71" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F71" s="41" t="s">
         <v>131</v>
       </c>
       <c r="G71" s="1" t="s">
@@ -3575,26 +3674,28 @@
         <v>95</v>
       </c>
     </row>
-    <row r="72" spans="1:10" s="62" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A72" s="58"/>
-      <c r="B72" s="59" t="s">
-        <v>11</v>
-      </c>
-      <c r="C72" s="60" t="s">
+    <row r="72" spans="1:10" s="60" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
+        <v>70</v>
+      </c>
+      <c r="B72" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" s="58" t="s">
         <v>198</v>
       </c>
       <c r="D72" s="24" t="s">
         <v>74</v>
       </c>
       <c r="E72" s="25"/>
-      <c r="F72" s="44"/>
-      <c r="G72" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="H72" s="61" t="s">
-        <v>23</v>
-      </c>
-      <c r="I72" s="58" t="s">
+      <c r="F72" s="42"/>
+      <c r="G72" s="59" t="s">
+        <v>22</v>
+      </c>
+      <c r="H72" s="59" t="s">
+        <v>23</v>
+      </c>
+      <c r="I72" s="56" t="s">
         <v>26</v>
       </c>
       <c r="J72" t="s">
@@ -3602,7 +3703,9 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="27"/>
+      <c r="A73" s="6">
+        <v>71</v>
+      </c>
       <c r="B73" s="5" t="s">
         <v>11</v>
       </c>
@@ -3613,7 +3716,7 @@
         <v>75</v>
       </c>
       <c r="E73" s="28"/>
-      <c r="F73" s="47"/>
+      <c r="F73" s="45"/>
       <c r="G73" s="2" t="s">
         <v>24</v>
       </c>
@@ -3623,25 +3726,27 @@
       <c r="I73" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="J73" s="66" t="s">
+      <c r="J73" s="64" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A74" s="27"/>
+      <c r="A74" s="6">
+        <v>72</v>
+      </c>
       <c r="B74" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="D74" s="32" t="s">
+      <c r="D74" s="31" t="s">
         <v>76</v>
       </c>
       <c r="E74" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="F74" s="50" t="s">
+      <c r="F74" s="48" t="s">
         <v>132</v>
       </c>
       <c r="G74" s="17" t="s">
@@ -3658,7 +3763,9 @@
       </c>
     </row>
     <row r="75" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A75" s="27"/>
+      <c r="A75" s="6">
+        <v>73</v>
+      </c>
       <c r="B75" s="5" t="s">
         <v>11</v>
       </c>
@@ -3671,7 +3778,7 @@
       <c r="E75" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="F75" s="43" t="s">
+      <c r="F75" s="41" t="s">
         <v>133</v>
       </c>
       <c r="G75" s="17" t="s">
@@ -3688,7 +3795,9 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="27"/>
+      <c r="A76" s="6">
+        <v>74</v>
+      </c>
       <c r="B76" s="5" t="s">
         <v>11</v>
       </c>
@@ -3701,7 +3810,7 @@
       <c r="E76" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="F76" s="43" t="s">
+      <c r="F76" s="41" t="s">
         <v>134</v>
       </c>
       <c r="G76" s="17" t="s">
@@ -3718,7 +3827,9 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A77" s="27"/>
+      <c r="A77" s="6">
+        <v>75</v>
+      </c>
       <c r="B77" s="5" t="s">
         <v>11</v>
       </c>
@@ -3731,7 +3842,7 @@
       <c r="E77" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="F77" s="43" t="s">
+      <c r="F77" s="41" t="s">
         <v>135</v>
       </c>
       <c r="G77" s="17" t="s">
@@ -3748,7 +3859,9 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="27"/>
+      <c r="A78" s="6">
+        <v>76</v>
+      </c>
       <c r="B78" s="5" t="s">
         <v>11</v>
       </c>
@@ -3761,7 +3874,7 @@
       <c r="E78" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="F78" s="43" t="s">
+      <c r="F78" s="41" t="s">
         <v>136</v>
       </c>
       <c r="G78" s="17" t="s">
@@ -3778,21 +3891,23 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="27"/>
+      <c r="A79" s="6">
+        <v>77</v>
+      </c>
       <c r="B79" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="D79" s="33" t="s">
+      <c r="D79" s="32" t="s">
         <v>81</v>
       </c>
       <c r="E79" s="15"/>
-      <c r="F79" s="47" t="s">
+      <c r="F79" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="G79" s="65" t="s">
+      <c r="G79" s="63" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="17" t="s">
@@ -3806,7 +3921,9 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="27"/>
+      <c r="A80" s="6">
+        <v>78</v>
+      </c>
       <c r="B80" s="5" t="s">
         <v>11</v>
       </c>
@@ -3819,7 +3936,7 @@
       <c r="E80" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="F80" s="43"/>
+      <c r="F80" s="41"/>
       <c r="G80" s="1" t="s">
         <v>24</v>
       </c>
@@ -3829,12 +3946,14 @@
       <c r="I80" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="J80" s="66" t="s">
+      <c r="J80" s="64" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A81" s="27"/>
+      <c r="A81" s="6">
+        <v>79</v>
+      </c>
       <c r="B81" s="5" t="s">
         <v>11</v>
       </c>
@@ -3847,7 +3966,7 @@
       <c r="E81" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="F81" s="42" t="s">
+      <c r="F81" s="40" t="s">
         <v>137</v>
       </c>
       <c r="G81" s="17" t="s">
@@ -3864,7 +3983,9 @@
       </c>
     </row>
     <row r="82" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A82" s="27"/>
+      <c r="A82" s="6">
+        <v>80</v>
+      </c>
       <c r="B82" s="5" t="s">
         <v>11</v>
       </c>
@@ -3877,7 +3998,7 @@
       <c r="E82" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="F82" s="42" t="s">
+      <c r="F82" s="40" t="s">
         <v>138</v>
       </c>
       <c r="G82" s="17" t="s">
@@ -3894,21 +4015,23 @@
       </c>
     </row>
     <row r="83" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A83" s="27"/>
+      <c r="A83" s="6">
+        <v>81</v>
+      </c>
       <c r="B83" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C83" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="D83" s="33" t="s">
+      <c r="D83" s="32" t="s">
         <v>85</v>
       </c>
       <c r="E83" s="15"/>
-      <c r="F83" s="47" t="s">
+      <c r="F83" s="45" t="s">
         <v>139</v>
       </c>
-      <c r="G83" s="65" t="s">
+      <c r="G83" s="63" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="17" t="s">
@@ -3922,7 +4045,9 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A84" s="27"/>
+      <c r="A84" s="6">
+        <v>82</v>
+      </c>
       <c r="B84" s="5" t="s">
         <v>11</v>
       </c>
@@ -3935,7 +4060,9 @@
       <c r="E84" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="F84" s="43"/>
+      <c r="F84" s="41" t="s">
+        <v>221</v>
+      </c>
       <c r="G84" s="1" t="s">
         <v>24</v>
       </c>
@@ -3945,12 +4072,14 @@
       <c r="I84" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="J84" s="66" t="s">
+      <c r="J84" s="64" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A85" s="27"/>
+      <c r="A85" s="6">
+        <v>83</v>
+      </c>
       <c r="B85" s="5" t="s">
         <v>11</v>
       </c>
@@ -3963,7 +4092,7 @@
       <c r="E85" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="F85" s="43" t="s">
+      <c r="F85" s="41" t="s">
         <v>135</v>
       </c>
       <c r="G85" s="17" t="s">
@@ -3980,7 +4109,9 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A86" s="27"/>
+      <c r="A86" s="6">
+        <v>84</v>
+      </c>
       <c r="B86" s="5" t="s">
         <v>11</v>
       </c>
@@ -3993,7 +4124,7 @@
       <c r="E86" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="F86" s="43" t="s">
+      <c r="F86" s="41" t="s">
         <v>136</v>
       </c>
       <c r="G86" s="17" t="s">
@@ -4010,18 +4141,20 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A87" s="27"/>
+      <c r="A87" s="6">
+        <v>85</v>
+      </c>
       <c r="B87" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C87" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="D87" s="33" t="s">
+      <c r="D87" s="32" t="s">
         <v>88</v>
       </c>
       <c r="E87" s="15"/>
-      <c r="F87" s="47" t="s">
+      <c r="F87" s="45" t="s">
         <v>93</v>
       </c>
       <c r="G87" s="1" t="s">
@@ -4038,7 +4171,9 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A88" s="27"/>
+      <c r="A88" s="6">
+        <v>86</v>
+      </c>
       <c r="B88" s="5" t="s">
         <v>11</v>
       </c>
@@ -4051,7 +4186,7 @@
       <c r="E88" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="F88" s="45" t="s">
+      <c r="F88" s="43" t="s">
         <v>140</v>
       </c>
       <c r="G88" s="17" t="s">
@@ -4068,7 +4203,9 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A89" s="27"/>
+      <c r="A89" s="6">
+        <v>87</v>
+      </c>
       <c r="B89" s="5" t="s">
         <v>11</v>
       </c>
@@ -4081,7 +4218,7 @@
       <c r="E89" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="F89" s="43" t="s">
+      <c r="F89" s="41" t="s">
         <v>134</v>
       </c>
       <c r="G89" s="17" t="s">

--- a/mapping/field_mapping.xlsx
+++ b/mapping/field_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Water collectives\WHS Assessment\auto gen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845ADD18-9230-483A-B2D6-C2EA87031A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A965B154-67E4-4C25-BB15-86D5F20695CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B03A0D84-276C-499F-A511-71567CA886FB}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="222">
   <si>
     <t>Sl.No</t>
   </si>
@@ -3903,7 +3903,9 @@
       <c r="D79" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="E79" s="15"/>
+      <c r="E79" s="15" t="s">
+        <v>91</v>
+      </c>
       <c r="F79" s="45" t="s">
         <v>93</v>
       </c>
@@ -4027,7 +4029,9 @@
       <c r="D83" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="E83" s="15"/>
+      <c r="E83" s="15" t="s">
+        <v>91</v>
+      </c>
       <c r="F83" s="45" t="s">
         <v>139</v>
       </c>
@@ -4058,7 +4062,7 @@
         <v>78</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>91</v>
+        <v>24</v>
       </c>
       <c r="F84" s="41" t="s">
         <v>221</v>
@@ -4153,7 +4157,9 @@
       <c r="D87" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="E87" s="15"/>
+      <c r="E87" s="15" t="s">
+        <v>91</v>
+      </c>
       <c r="F87" s="45" t="s">
         <v>93</v>
       </c>

--- a/mapping/field_mapping.xlsx
+++ b/mapping/field_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Water collectives\WHS Assessment\auto gen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A965B154-67E4-4C25-BB15-86D5F20695CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C206738-87F6-48DA-BCA9-5CBF5DA3001A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B03A0D84-276C-499F-A511-71567CA886FB}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="223">
   <si>
     <t>Sl.No</t>
   </si>
@@ -335,9 +335,6 @@
     <t>Left side dam guide Wall</t>
   </si>
   <si>
-    <t>lead_metal_mamidipalli_km</t>
-  </si>
-  <si>
     <t>Calculation Type</t>
   </si>
   <si>
@@ -720,6 +717,12 @@
   </si>
   <si>
     <t>Mamidipalli</t>
+  </si>
+  <si>
+    <t>Kothavalasa</t>
+  </si>
+  <si>
+    <t>metal-lead_metal_mamidipalli_km</t>
   </si>
 </sst>
 </file>
@@ -1497,7 +1500,7 @@
         <v>6</v>
       </c>
       <c r="J1" s="62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1508,7 +1511,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D2" s="33" t="s">
         <v>8</v>
@@ -1517,7 +1520,7 @@
         <v>13</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>22</v>
@@ -1529,7 +1532,7 @@
         <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1540,7 +1543,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D3" s="33" t="s">
         <v>10</v>
@@ -1549,7 +1552,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>22</v>
@@ -1561,7 +1564,7 @@
         <v>9</v>
       </c>
       <c r="J3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1572,7 +1575,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>14</v>
@@ -1581,7 +1584,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>22</v>
@@ -1593,7 +1596,7 @@
         <v>9</v>
       </c>
       <c r="J4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1604,7 +1607,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>15</v>
@@ -1613,7 +1616,7 @@
         <v>13</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>22</v>
@@ -1625,7 +1628,7 @@
         <v>9</v>
       </c>
       <c r="J5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1636,7 +1639,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>16</v>
@@ -1645,7 +1648,7 @@
         <v>13</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>22</v>
@@ -1657,7 +1660,7 @@
         <v>12</v>
       </c>
       <c r="J6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1668,7 +1671,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D7" s="34" t="s">
         <v>17</v>
@@ -1677,7 +1680,7 @@
         <v>13</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>22</v>
@@ -1689,7 +1692,7 @@
         <v>12</v>
       </c>
       <c r="J7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1700,7 +1703,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>18</v>
@@ -1709,7 +1712,7 @@
         <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>22</v>
@@ -1721,7 +1724,7 @@
         <v>9</v>
       </c>
       <c r="J8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1732,7 +1735,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>19</v>
@@ -1749,7 +1752,7 @@
         <v>9</v>
       </c>
       <c r="J9" s="64" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1760,7 +1763,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>25</v>
@@ -1779,7 +1782,7 @@
         <v>9</v>
       </c>
       <c r="J10" s="64" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -1790,7 +1793,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>27</v>
@@ -1799,7 +1802,7 @@
         <v>13</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>22</v>
@@ -1811,7 +1814,7 @@
         <v>9</v>
       </c>
       <c r="J11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1822,7 +1825,7 @@
         <v>7</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>28</v>
@@ -1831,7 +1834,7 @@
         <v>13</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>22</v>
@@ -1843,7 +1846,7 @@
         <v>9</v>
       </c>
       <c r="J12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -1854,7 +1857,7 @@
         <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>29</v>
@@ -1873,7 +1876,7 @@
         <v>26</v>
       </c>
       <c r="J13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -1884,7 +1887,7 @@
         <v>7</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D14" s="16" t="s">
         <v>31</v>
@@ -1893,7 +1896,7 @@
         <v>13</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>22</v>
@@ -1905,7 +1908,7 @@
         <v>9</v>
       </c>
       <c r="J14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -1916,16 +1919,16 @@
         <v>7</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D15" s="65" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F15" s="66" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G15" s="17" t="s">
         <v>22</v>
@@ -1937,7 +1940,7 @@
         <v>9</v>
       </c>
       <c r="J15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -1948,16 +1951,16 @@
         <v>7</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D16" s="65" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F16" s="66" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G16" s="17" t="s">
         <v>22</v>
@@ -1969,7 +1972,7 @@
         <v>9</v>
       </c>
       <c r="J16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -1980,7 +1983,7 @@
         <v>11</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D17" s="19" t="s">
         <v>32</v>
@@ -1989,7 +1992,7 @@
         <v>33</v>
       </c>
       <c r="F17" s="37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G17" s="17" t="s">
         <v>22</v>
@@ -2001,7 +2004,7 @@
         <v>9</v>
       </c>
       <c r="J17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -2012,7 +2015,7 @@
         <v>11</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>34</v>
@@ -2021,7 +2024,7 @@
         <v>33</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G18" s="17" t="s">
         <v>22</v>
@@ -2033,7 +2036,7 @@
         <v>9</v>
       </c>
       <c r="J18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2044,7 +2047,7 @@
         <v>11</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>35</v>
@@ -2061,7 +2064,7 @@
         <v>26</v>
       </c>
       <c r="J19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2072,7 +2075,7 @@
         <v>11</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>36</v>
@@ -2089,7 +2092,7 @@
         <v>26</v>
       </c>
       <c r="J20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2100,7 +2103,7 @@
         <v>11</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D21" s="21" t="s">
         <v>38</v>
@@ -2109,7 +2112,7 @@
         <v>13</v>
       </c>
       <c r="F21" s="37" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G21" s="17" t="s">
         <v>22</v>
@@ -2121,7 +2124,7 @@
         <v>9</v>
       </c>
       <c r="J21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2132,7 +2135,7 @@
         <v>11</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D22" s="19" t="s">
         <v>39</v>
@@ -2141,7 +2144,7 @@
         <v>40</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G22" s="17" t="s">
         <v>22</v>
@@ -2153,7 +2156,7 @@
         <v>9</v>
       </c>
       <c r="J22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2164,7 +2167,7 @@
         <v>11</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D23" s="19" t="s">
         <v>41</v>
@@ -2173,7 +2176,7 @@
         <v>40</v>
       </c>
       <c r="F23" s="39" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G23" s="17" t="s">
         <v>22</v>
@@ -2185,7 +2188,7 @@
         <v>9</v>
       </c>
       <c r="J23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
@@ -2196,7 +2199,7 @@
         <v>11</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D24" s="23" t="s">
         <v>42</v>
@@ -2213,7 +2216,7 @@
         <v>9</v>
       </c>
       <c r="J24" s="64" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
@@ -2224,7 +2227,7 @@
         <v>11</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D25" s="19" t="s">
         <v>43</v>
@@ -2233,7 +2236,7 @@
         <v>33</v>
       </c>
       <c r="F25" s="40" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G25" s="17" t="s">
         <v>22</v>
@@ -2245,7 +2248,7 @@
         <v>9</v>
       </c>
       <c r="J25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
@@ -2256,7 +2259,7 @@
         <v>11</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D26" s="23" t="s">
         <v>44</v>
@@ -2273,7 +2276,7 @@
         <v>9</v>
       </c>
       <c r="J26" s="64" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2284,7 +2287,7 @@
         <v>11</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D27" s="19" t="s">
         <v>45</v>
@@ -2293,7 +2296,7 @@
         <v>33</v>
       </c>
       <c r="F27" s="41" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G27" s="17" t="s">
         <v>22</v>
@@ -2305,7 +2308,7 @@
         <v>9</v>
       </c>
       <c r="J27" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2316,7 +2319,7 @@
         <v>11</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D28" s="19" t="s">
         <v>46</v>
@@ -2325,7 +2328,7 @@
         <v>33</v>
       </c>
       <c r="F28" s="41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G28" s="17" t="s">
         <v>22</v>
@@ -2337,7 +2340,7 @@
         <v>9</v>
       </c>
       <c r="J28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2348,7 +2351,7 @@
         <v>11</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D29" s="50" t="s">
         <v>47</v>
@@ -2357,7 +2360,7 @@
         <v>33</v>
       </c>
       <c r="F29" s="41" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G29" s="17" t="s">
         <v>22</v>
@@ -2369,7 +2372,7 @@
         <v>9</v>
       </c>
       <c r="J29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2380,7 +2383,7 @@
         <v>11</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D30" s="50" t="s">
         <v>48</v>
@@ -2389,7 +2392,7 @@
         <v>33</v>
       </c>
       <c r="F30" s="52" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G30" s="53" t="s">
         <v>22</v>
@@ -2401,7 +2404,7 @@
         <v>9</v>
       </c>
       <c r="J30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2412,7 +2415,7 @@
         <v>11</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D31" s="50" t="s">
         <v>49</v>
@@ -2421,7 +2424,7 @@
         <v>33</v>
       </c>
       <c r="F31" s="54" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G31" s="53" t="s">
         <v>22</v>
@@ -2433,7 +2436,7 @@
         <v>9</v>
       </c>
       <c r="J31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2444,7 +2447,7 @@
         <v>11</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D32" s="19" t="s">
         <v>50</v>
@@ -2453,7 +2456,7 @@
         <v>33</v>
       </c>
       <c r="F32" s="52" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G32" s="17" t="s">
         <v>22</v>
@@ -2465,7 +2468,7 @@
         <v>9</v>
       </c>
       <c r="J32" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2476,7 +2479,7 @@
         <v>11</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D33" s="55" t="s">
         <v>92</v>
@@ -2485,7 +2488,7 @@
         <v>33</v>
       </c>
       <c r="F33" s="52" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G33" s="17" t="s">
         <v>22</v>
@@ -2497,7 +2500,7 @@
         <v>9</v>
       </c>
       <c r="J33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2508,7 +2511,7 @@
         <v>11</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D34" s="19" t="s">
         <v>52</v>
@@ -2517,7 +2520,7 @@
         <v>33</v>
       </c>
       <c r="F34" s="41" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G34" s="17" t="s">
         <v>22</v>
@@ -2529,7 +2532,7 @@
         <v>9</v>
       </c>
       <c r="J34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2540,7 +2543,7 @@
         <v>11</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D35" s="19" t="s">
         <v>53</v>
@@ -2549,7 +2552,7 @@
         <v>33</v>
       </c>
       <c r="F35" s="52" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G35" s="17" t="s">
         <v>22</v>
@@ -2561,7 +2564,7 @@
         <v>9</v>
       </c>
       <c r="J35" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -2572,7 +2575,7 @@
         <v>11</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D36" s="19" t="s">
         <v>54</v>
@@ -2581,7 +2584,7 @@
         <v>33</v>
       </c>
       <c r="F36" s="54" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G36" s="17" t="s">
         <v>22</v>
@@ -2593,7 +2596,7 @@
         <v>9</v>
       </c>
       <c r="J36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2604,7 +2607,7 @@
         <v>11</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D37" s="19" t="s">
         <v>55</v>
@@ -2613,7 +2616,7 @@
         <v>33</v>
       </c>
       <c r="F37" s="54" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G37" s="17" t="s">
         <v>22</v>
@@ -2625,7 +2628,7 @@
         <v>9</v>
       </c>
       <c r="J37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2636,7 +2639,7 @@
         <v>11</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D38" s="26" t="s">
         <v>56</v>
@@ -2645,7 +2648,7 @@
         <v>33</v>
       </c>
       <c r="F38" s="44" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G38" s="17" t="s">
         <v>22</v>
@@ -2657,7 +2660,7 @@
         <v>9</v>
       </c>
       <c r="J38" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2668,7 +2671,7 @@
         <v>11</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D39" s="26" t="s">
         <v>57</v>
@@ -2677,7 +2680,7 @@
         <v>33</v>
       </c>
       <c r="F39" s="44" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G39" s="17" t="s">
         <v>22</v>
@@ -2689,7 +2692,7 @@
         <v>9</v>
       </c>
       <c r="J39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="60" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -2700,7 +2703,7 @@
         <v>11</v>
       </c>
       <c r="C40" s="58" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D40" s="24" t="s">
         <v>58</v>
@@ -2719,7 +2722,7 @@
         <v>26</v>
       </c>
       <c r="J40" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
@@ -2730,7 +2733,7 @@
         <v>11</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D41" s="23" t="s">
         <v>59</v>
@@ -2747,7 +2750,7 @@
         <v>9</v>
       </c>
       <c r="J41" s="64" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2758,7 +2761,7 @@
         <v>11</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D42" s="19" t="s">
         <v>48</v>
@@ -2767,7 +2770,7 @@
         <v>33</v>
       </c>
       <c r="F42" s="41" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>22</v>
@@ -2779,7 +2782,7 @@
         <v>26</v>
       </c>
       <c r="J42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2790,7 +2793,7 @@
         <v>11</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D43" s="19" t="s">
         <v>49</v>
@@ -2799,7 +2802,7 @@
         <v>33</v>
       </c>
       <c r="F43" s="41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>22</v>
@@ -2811,7 +2814,7 @@
         <v>26</v>
       </c>
       <c r="J43" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2822,7 +2825,7 @@
         <v>11</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D44" s="19" t="s">
         <v>50</v>
@@ -2831,7 +2834,7 @@
         <v>33</v>
       </c>
       <c r="F44" s="41" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G44" s="17" t="s">
         <v>22</v>
@@ -2843,7 +2846,7 @@
         <v>9</v>
       </c>
       <c r="J44" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2854,7 +2857,7 @@
         <v>11</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D45" s="19" t="s">
         <v>51</v>
@@ -2863,7 +2866,7 @@
         <v>33</v>
       </c>
       <c r="F45" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>22</v>
@@ -2875,7 +2878,7 @@
         <v>26</v>
       </c>
       <c r="J45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2886,7 +2889,7 @@
         <v>11</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D46" s="19" t="s">
         <v>52</v>
@@ -2895,7 +2898,7 @@
         <v>33</v>
       </c>
       <c r="F46" s="41" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>22</v>
@@ -2907,7 +2910,7 @@
         <v>26</v>
       </c>
       <c r="J46" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2918,7 +2921,7 @@
         <v>11</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D47" s="19" t="s">
         <v>53</v>
@@ -2927,7 +2930,7 @@
         <v>33</v>
       </c>
       <c r="F47" s="52" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>22</v>
@@ -2939,7 +2942,7 @@
         <v>26</v>
       </c>
       <c r="J47" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2950,7 +2953,7 @@
         <v>11</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D48" s="26" t="s">
         <v>56</v>
@@ -2959,7 +2962,7 @@
         <v>33</v>
       </c>
       <c r="F48" s="46" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>22</v>
@@ -2971,7 +2974,7 @@
         <v>26</v>
       </c>
       <c r="J48" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2982,7 +2985,7 @@
         <v>11</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D49" s="26" t="s">
         <v>57</v>
@@ -2991,7 +2994,7 @@
         <v>33</v>
       </c>
       <c r="F49" s="46" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>22</v>
@@ -3003,7 +3006,7 @@
         <v>26</v>
       </c>
       <c r="J49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="60" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -3014,7 +3017,7 @@
         <v>11</v>
       </c>
       <c r="C50" s="58" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D50" s="24" t="s">
         <v>58</v>
@@ -3031,7 +3034,7 @@
         <v>26</v>
       </c>
       <c r="J50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
@@ -3042,7 +3045,7 @@
         <v>11</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D51" s="23" t="s">
         <v>60</v>
@@ -3059,7 +3062,7 @@
         <v>9</v>
       </c>
       <c r="J51" s="64" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3070,7 +3073,7 @@
         <v>11</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D52" s="19" t="s">
         <v>45</v>
@@ -3079,7 +3082,7 @@
         <v>33</v>
       </c>
       <c r="F52" s="41" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>22</v>
@@ -3091,7 +3094,7 @@
         <v>26</v>
       </c>
       <c r="J52" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3102,7 +3105,7 @@
         <v>11</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D53" s="19" t="s">
         <v>46</v>
@@ -3111,7 +3114,7 @@
         <v>33</v>
       </c>
       <c r="F53" s="41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>22</v>
@@ -3123,7 +3126,7 @@
         <v>26</v>
       </c>
       <c r="J53" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3134,7 +3137,7 @@
         <v>11</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D54" s="19" t="s">
         <v>47</v>
@@ -3143,7 +3146,7 @@
         <v>33</v>
       </c>
       <c r="F54" s="41" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>22</v>
@@ -3155,7 +3158,7 @@
         <v>26</v>
       </c>
       <c r="J54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3166,7 +3169,7 @@
         <v>11</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D55" s="19" t="s">
         <v>61</v>
@@ -3175,7 +3178,7 @@
         <v>33</v>
       </c>
       <c r="F55" s="52" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>22</v>
@@ -3187,7 +3190,7 @@
         <v>26</v>
       </c>
       <c r="J55" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3198,7 +3201,7 @@
         <v>11</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D56" s="19" t="s">
         <v>62</v>
@@ -3207,7 +3210,7 @@
         <v>33</v>
       </c>
       <c r="F56" s="54" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>22</v>
@@ -3219,7 +3222,7 @@
         <v>26</v>
       </c>
       <c r="J56" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3230,7 +3233,7 @@
         <v>11</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D57" s="19" t="s">
         <v>50</v>
@@ -3239,7 +3242,7 @@
         <v>33</v>
       </c>
       <c r="F57" s="52" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G57" s="17" t="s">
         <v>22</v>
@@ -3251,7 +3254,7 @@
         <v>9</v>
       </c>
       <c r="J57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3262,7 +3265,7 @@
         <v>11</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D58" s="19" t="s">
         <v>63</v>
@@ -3271,7 +3274,7 @@
         <v>33</v>
       </c>
       <c r="F58" s="52" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>22</v>
@@ -3283,7 +3286,7 @@
         <v>26</v>
       </c>
       <c r="J58" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
@@ -3294,7 +3297,7 @@
         <v>11</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D59" s="19" t="s">
         <v>64</v>
@@ -3311,7 +3314,7 @@
         <v>26</v>
       </c>
       <c r="J59" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
@@ -3322,7 +3325,7 @@
         <v>11</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D60" s="19" t="s">
         <v>65</v>
@@ -3339,7 +3342,7 @@
         <v>26</v>
       </c>
       <c r="J60" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3350,7 +3353,7 @@
         <v>11</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D61" s="19" t="s">
         <v>66</v>
@@ -3359,7 +3362,7 @@
         <v>33</v>
       </c>
       <c r="F61" s="41" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G61" s="17" t="s">
         <v>22</v>
@@ -3371,7 +3374,7 @@
         <v>9</v>
       </c>
       <c r="J61" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3382,7 +3385,7 @@
         <v>11</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D62" s="26" t="s">
         <v>56</v>
@@ -3391,7 +3394,7 @@
         <v>33</v>
       </c>
       <c r="F62" s="46" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>22</v>
@@ -3403,7 +3406,7 @@
         <v>26</v>
       </c>
       <c r="J62" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3414,7 +3417,7 @@
         <v>11</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D63" s="26" t="s">
         <v>57</v>
@@ -3423,7 +3426,7 @@
         <v>33</v>
       </c>
       <c r="F63" s="46" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>22</v>
@@ -3435,7 +3438,7 @@
         <v>26</v>
       </c>
       <c r="J63" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="64" spans="1:10" s="60" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -3446,7 +3449,7 @@
         <v>11</v>
       </c>
       <c r="C64" s="58" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D64" s="24" t="s">
         <v>58</v>
@@ -3463,7 +3466,7 @@
         <v>26</v>
       </c>
       <c r="J64" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
@@ -3474,7 +3477,7 @@
         <v>11</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D65" s="23" t="s">
         <v>67</v>
@@ -3491,7 +3494,7 @@
         <v>9</v>
       </c>
       <c r="J65" s="64" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3502,7 +3505,7 @@
         <v>11</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D66" s="19" t="s">
         <v>68</v>
@@ -3511,7 +3514,7 @@
         <v>33</v>
       </c>
       <c r="F66" s="41" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>22</v>
@@ -3523,7 +3526,7 @@
         <v>9</v>
       </c>
       <c r="J66" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3534,7 +3537,7 @@
         <v>11</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D67" s="19" t="s">
         <v>69</v>
@@ -3543,7 +3546,7 @@
         <v>33</v>
       </c>
       <c r="F67" s="61" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>22</v>
@@ -3555,7 +3558,7 @@
         <v>26</v>
       </c>
       <c r="J67" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -3566,7 +3569,7 @@
         <v>11</v>
       </c>
       <c r="C68" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D68" s="19" t="s">
         <v>70</v>
@@ -3583,7 +3586,7 @@
         <v>26</v>
       </c>
       <c r="J68" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -3594,7 +3597,7 @@
         <v>11</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D69" s="19" t="s">
         <v>71</v>
@@ -3611,7 +3614,7 @@
         <v>26</v>
       </c>
       <c r="J69" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
@@ -3622,7 +3625,7 @@
         <v>11</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D70" s="29" t="s">
         <v>72</v>
@@ -3639,7 +3642,7 @@
         <v>9</v>
       </c>
       <c r="J70" s="64" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3650,7 +3653,7 @@
         <v>11</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D71" s="19" t="s">
         <v>73</v>
@@ -3659,7 +3662,7 @@
         <v>33</v>
       </c>
       <c r="F71" s="41" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>22</v>
@@ -3671,7 +3674,7 @@
         <v>9</v>
       </c>
       <c r="J71" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="72" spans="1:10" s="60" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -3682,7 +3685,7 @@
         <v>11</v>
       </c>
       <c r="C72" s="58" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D72" s="24" t="s">
         <v>74</v>
@@ -3699,7 +3702,7 @@
         <v>26</v>
       </c>
       <c r="J72" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
@@ -3710,7 +3713,7 @@
         <v>11</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D73" s="23" t="s">
         <v>75</v>
@@ -3727,7 +3730,7 @@
         <v>9</v>
       </c>
       <c r="J73" s="64" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -3738,7 +3741,7 @@
         <v>11</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D74" s="31" t="s">
         <v>76</v>
@@ -3747,7 +3750,7 @@
         <v>91</v>
       </c>
       <c r="F74" s="48" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G74" s="17" t="s">
         <v>22</v>
@@ -3759,7 +3762,7 @@
         <v>9</v>
       </c>
       <c r="J74" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3770,7 +3773,7 @@
         <v>11</v>
       </c>
       <c r="C75" s="18" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D75" s="19" t="s">
         <v>77</v>
@@ -3779,7 +3782,7 @@
         <v>91</v>
       </c>
       <c r="F75" s="41" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G75" s="17" t="s">
         <v>22</v>
@@ -3791,7 +3794,7 @@
         <v>9</v>
       </c>
       <c r="J75" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3802,7 +3805,7 @@
         <v>11</v>
       </c>
       <c r="C76" s="18" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D76" s="19" t="s">
         <v>78</v>
@@ -3811,7 +3814,7 @@
         <v>91</v>
       </c>
       <c r="F76" s="41" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G76" s="17" t="s">
         <v>22</v>
@@ -3823,7 +3826,7 @@
         <v>9</v>
       </c>
       <c r="J76" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -3834,7 +3837,7 @@
         <v>11</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D77" s="19" t="s">
         <v>79</v>
@@ -3843,7 +3846,7 @@
         <v>91</v>
       </c>
       <c r="F77" s="41" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G77" s="17" t="s">
         <v>22</v>
@@ -3855,7 +3858,7 @@
         <v>9</v>
       </c>
       <c r="J77" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -3866,7 +3869,7 @@
         <v>11</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D78" s="19" t="s">
         <v>80</v>
@@ -3875,7 +3878,7 @@
         <v>91</v>
       </c>
       <c r="F78" s="41" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G78" s="17" t="s">
         <v>22</v>
@@ -3887,7 +3890,7 @@
         <v>9</v>
       </c>
       <c r="J78" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3898,7 +3901,7 @@
         <v>11</v>
       </c>
       <c r="C79" s="18" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D79" s="32" t="s">
         <v>81</v>
@@ -3907,7 +3910,7 @@
         <v>91</v>
       </c>
       <c r="F79" s="45" t="s">
-        <v>93</v>
+        <v>222</v>
       </c>
       <c r="G79" s="63" t="s">
         <v>22</v>
@@ -3919,7 +3922,7 @@
         <v>9</v>
       </c>
       <c r="J79" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3930,7 +3933,7 @@
         <v>11</v>
       </c>
       <c r="C80" s="18" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D80" s="19" t="s">
         <v>82</v>
@@ -3938,7 +3941,9 @@
       <c r="E80" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="F80" s="41"/>
+      <c r="F80" s="41" t="s">
+        <v>221</v>
+      </c>
       <c r="G80" s="1" t="s">
         <v>24</v>
       </c>
@@ -3949,7 +3954,7 @@
         <v>9</v>
       </c>
       <c r="J80" s="64" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3960,7 +3965,7 @@
         <v>11</v>
       </c>
       <c r="C81" s="18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D81" s="19" t="s">
         <v>83</v>
@@ -3969,7 +3974,7 @@
         <v>91</v>
       </c>
       <c r="F81" s="40" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G81" s="17" t="s">
         <v>22</v>
@@ -3981,7 +3986,7 @@
         <v>9</v>
       </c>
       <c r="J81" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3992,7 +3997,7 @@
         <v>11</v>
       </c>
       <c r="C82" s="18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D82" s="19" t="s">
         <v>84</v>
@@ -4001,7 +4006,7 @@
         <v>91</v>
       </c>
       <c r="F82" s="40" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G82" s="17" t="s">
         <v>22</v>
@@ -4013,7 +4018,7 @@
         <v>9</v>
       </c>
       <c r="J82" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -4024,7 +4029,7 @@
         <v>11</v>
       </c>
       <c r="C83" s="18" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D83" s="32" t="s">
         <v>85</v>
@@ -4033,7 +4038,7 @@
         <v>91</v>
       </c>
       <c r="F83" s="45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G83" s="63" t="s">
         <v>22</v>
@@ -4045,7 +4050,7 @@
         <v>9</v>
       </c>
       <c r="J83" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -4056,7 +4061,7 @@
         <v>11</v>
       </c>
       <c r="C84" s="18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D84" s="19" t="s">
         <v>78</v>
@@ -4065,7 +4070,7 @@
         <v>24</v>
       </c>
       <c r="F84" s="41" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>24</v>
@@ -4077,7 +4082,7 @@
         <v>9</v>
       </c>
       <c r="J84" s="64" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -4088,7 +4093,7 @@
         <v>11</v>
       </c>
       <c r="C85" s="18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D85" s="19" t="s">
         <v>86</v>
@@ -4097,7 +4102,7 @@
         <v>91</v>
       </c>
       <c r="F85" s="41" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G85" s="17" t="s">
         <v>22</v>
@@ -4109,7 +4114,7 @@
         <v>9</v>
       </c>
       <c r="J85" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -4120,7 +4125,7 @@
         <v>11</v>
       </c>
       <c r="C86" s="18" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D86" s="19" t="s">
         <v>87</v>
@@ -4129,7 +4134,7 @@
         <v>91</v>
       </c>
       <c r="F86" s="41" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G86" s="17" t="s">
         <v>22</v>
@@ -4141,7 +4146,7 @@
         <v>9</v>
       </c>
       <c r="J86" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -4152,7 +4157,7 @@
         <v>11</v>
       </c>
       <c r="C87" s="18" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D87" s="32" t="s">
         <v>88</v>
@@ -4161,7 +4166,7 @@
         <v>91</v>
       </c>
       <c r="F87" s="45" t="s">
-        <v>93</v>
+        <v>222</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>22</v>
@@ -4173,7 +4178,7 @@
         <v>9</v>
       </c>
       <c r="J87" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -4184,7 +4189,7 @@
         <v>11</v>
       </c>
       <c r="C88" s="18" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D88" s="19" t="s">
         <v>89</v>
@@ -4193,7 +4198,7 @@
         <v>91</v>
       </c>
       <c r="F88" s="43" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G88" s="17" t="s">
         <v>22</v>
@@ -4205,7 +4210,7 @@
         <v>9</v>
       </c>
       <c r="J88" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -4216,7 +4221,7 @@
         <v>11</v>
       </c>
       <c r="C89" s="18" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D89" s="19" t="s">
         <v>90</v>
@@ -4225,7 +4230,7 @@
         <v>91</v>
       </c>
       <c r="F89" s="41" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G89" s="17" t="s">
         <v>22</v>
@@ -4237,7 +4242,7 @@
         <v>9</v>
       </c>
       <c r="J89" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/mapping/field_mapping.xlsx
+++ b/mapping/field_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Water collectives\WHS Assessment\auto gen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C206738-87F6-48DA-BCA9-5CBF5DA3001A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27322F09-72F2-4B78-8FAA-608A25A6CFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B03A0D84-276C-499F-A511-71567CA886FB}"/>
   </bookViews>
@@ -2100,10 +2100,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="D21" s="21" t="s">
         <v>38</v>

--- a/mapping/field_mapping.xlsx
+++ b/mapping/field_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Water collectives\WHS Assessment\auto gen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27322F09-72F2-4B78-8FAA-608A25A6CFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A80E70F-1C2F-4B26-8910-6674047E9E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B03A0D84-276C-499F-A511-71567CA886FB}"/>
   </bookViews>
@@ -150,9 +150,6 @@
     <t>Water discharge (liters / sec)</t>
   </si>
   <si>
-    <t>1.1 Water Discharge</t>
-  </si>
-  <si>
     <t>Date of discharge measured</t>
   </si>
   <si>
@@ -165,6 +162,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Type of Bush Clearence (</t>
     </r>
@@ -174,6 +172,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Light</t>
     </r>
@@ -183,6 +182,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>/Medium/Juliflora)Max (L+10)*10</t>
     </r>
@@ -723,6 +723,9 @@
   </si>
   <si>
     <t>metal-lead_metal_mamidipalli_km</t>
+  </si>
+  <si>
+    <t>1.1 Discarge</t>
   </si>
 </sst>
 </file>
@@ -749,6 +752,7 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -761,6 +765,7 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -779,12 +784,14 @@
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -805,6 +812,7 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1500,7 +1508,7 @@
         <v>6</v>
       </c>
       <c r="J1" s="62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1511,7 +1519,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D2" s="33" t="s">
         <v>8</v>
@@ -1520,7 +1528,7 @@
         <v>13</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>22</v>
@@ -1532,7 +1540,7 @@
         <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1543,7 +1551,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D3" s="33" t="s">
         <v>10</v>
@@ -1552,7 +1560,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>22</v>
@@ -1564,7 +1572,7 @@
         <v>9</v>
       </c>
       <c r="J3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1575,7 +1583,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>14</v>
@@ -1584,7 +1592,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>22</v>
@@ -1596,7 +1604,7 @@
         <v>9</v>
       </c>
       <c r="J4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1607,7 +1615,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>15</v>
@@ -1616,7 +1624,7 @@
         <v>13</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>22</v>
@@ -1628,7 +1636,7 @@
         <v>9</v>
       </c>
       <c r="J5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1639,7 +1647,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>16</v>
@@ -1648,7 +1656,7 @@
         <v>13</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>22</v>
@@ -1660,7 +1668,7 @@
         <v>12</v>
       </c>
       <c r="J6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1671,7 +1679,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D7" s="34" t="s">
         <v>17</v>
@@ -1680,7 +1688,7 @@
         <v>13</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>22</v>
@@ -1692,7 +1700,7 @@
         <v>12</v>
       </c>
       <c r="J7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1703,7 +1711,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>18</v>
@@ -1712,7 +1720,7 @@
         <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>22</v>
@@ -1724,7 +1732,7 @@
         <v>9</v>
       </c>
       <c r="J8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1735,7 +1743,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>19</v>
@@ -1752,7 +1760,7 @@
         <v>9</v>
       </c>
       <c r="J9" s="64" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1763,7 +1771,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>25</v>
@@ -1782,7 +1790,7 @@
         <v>9</v>
       </c>
       <c r="J10" s="64" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -1793,7 +1801,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>27</v>
@@ -1802,7 +1810,7 @@
         <v>13</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>22</v>
@@ -1814,7 +1822,7 @@
         <v>9</v>
       </c>
       <c r="J11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1825,7 +1833,7 @@
         <v>7</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>28</v>
@@ -1834,7 +1842,7 @@
         <v>13</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>22</v>
@@ -1846,7 +1854,7 @@
         <v>9</v>
       </c>
       <c r="J12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -1857,7 +1865,7 @@
         <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>29</v>
@@ -1876,7 +1884,7 @@
         <v>26</v>
       </c>
       <c r="J13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -1887,7 +1895,7 @@
         <v>7</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D14" s="16" t="s">
         <v>31</v>
@@ -1896,7 +1904,7 @@
         <v>13</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>22</v>
@@ -1908,7 +1916,7 @@
         <v>9</v>
       </c>
       <c r="J14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -1919,16 +1927,16 @@
         <v>7</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D15" s="65" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F15" s="66" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G15" s="17" t="s">
         <v>22</v>
@@ -1940,7 +1948,7 @@
         <v>9</v>
       </c>
       <c r="J15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -1951,16 +1959,16 @@
         <v>7</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D16" s="65" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F16" s="66" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G16" s="17" t="s">
         <v>22</v>
@@ -1972,7 +1980,7 @@
         <v>9</v>
       </c>
       <c r="J16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -1983,7 +1991,7 @@
         <v>11</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D17" s="19" t="s">
         <v>32</v>
@@ -1992,7 +2000,7 @@
         <v>33</v>
       </c>
       <c r="F17" s="37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G17" s="17" t="s">
         <v>22</v>
@@ -2004,7 +2012,7 @@
         <v>9</v>
       </c>
       <c r="J17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -2015,7 +2023,7 @@
         <v>11</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>34</v>
@@ -2024,7 +2032,7 @@
         <v>33</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G18" s="17" t="s">
         <v>22</v>
@@ -2036,7 +2044,7 @@
         <v>9</v>
       </c>
       <c r="J18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2047,7 +2055,7 @@
         <v>11</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>35</v>
@@ -2064,7 +2072,7 @@
         <v>26</v>
       </c>
       <c r="J19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2075,7 +2083,7 @@
         <v>11</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>36</v>
@@ -2092,7 +2100,7 @@
         <v>26</v>
       </c>
       <c r="J20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2103,7 +2111,7 @@
         <v>7</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D21" s="21" t="s">
         <v>38</v>
@@ -2112,7 +2120,7 @@
         <v>13</v>
       </c>
       <c r="F21" s="37" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G21" s="17" t="s">
         <v>22</v>
@@ -2124,7 +2132,7 @@
         <v>9</v>
       </c>
       <c r="J21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2135,16 +2143,16 @@
         <v>11</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D22" s="19" t="s">
         <v>39</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>40</v>
+        <v>222</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G22" s="17" t="s">
         <v>22</v>
@@ -2156,7 +2164,7 @@
         <v>9</v>
       </c>
       <c r="J22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2167,16 +2175,16 @@
         <v>11</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>40</v>
+        <v>222</v>
       </c>
       <c r="F23" s="39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G23" s="17" t="s">
         <v>22</v>
@@ -2188,7 +2196,7 @@
         <v>9</v>
       </c>
       <c r="J23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
@@ -2199,10 +2207,10 @@
         <v>11</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E24" s="22"/>
       <c r="F24" s="39"/>
@@ -2216,7 +2224,7 @@
         <v>9</v>
       </c>
       <c r="J24" s="64" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
@@ -2227,16 +2235,16 @@
         <v>11</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E25" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F25" s="40" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G25" s="17" t="s">
         <v>22</v>
@@ -2248,7 +2256,7 @@
         <v>9</v>
       </c>
       <c r="J25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
@@ -2259,10 +2267,10 @@
         <v>11</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E26" s="22"/>
       <c r="F26" s="39"/>
@@ -2276,7 +2284,7 @@
         <v>9</v>
       </c>
       <c r="J26" s="64" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2287,16 +2295,16 @@
         <v>11</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E27" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F27" s="41" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G27" s="17" t="s">
         <v>22</v>
@@ -2308,7 +2316,7 @@
         <v>9</v>
       </c>
       <c r="J27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2319,16 +2327,16 @@
         <v>11</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E28" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="41" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G28" s="17" t="s">
         <v>22</v>
@@ -2340,7 +2348,7 @@
         <v>9</v>
       </c>
       <c r="J28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2351,16 +2359,16 @@
         <v>11</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D29" s="50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E29" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F29" s="41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G29" s="17" t="s">
         <v>22</v>
@@ -2372,7 +2380,7 @@
         <v>9</v>
       </c>
       <c r="J29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2383,16 +2391,16 @@
         <v>11</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D30" s="50" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E30" s="51" t="s">
         <v>33</v>
       </c>
       <c r="F30" s="52" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G30" s="53" t="s">
         <v>22</v>
@@ -2404,7 +2412,7 @@
         <v>9</v>
       </c>
       <c r="J30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2415,16 +2423,16 @@
         <v>11</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D31" s="50" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E31" s="51" t="s">
         <v>33</v>
       </c>
       <c r="F31" s="54" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G31" s="53" t="s">
         <v>22</v>
@@ -2436,7 +2444,7 @@
         <v>9</v>
       </c>
       <c r="J31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2447,16 +2455,16 @@
         <v>11</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E32" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F32" s="52" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G32" s="17" t="s">
         <v>22</v>
@@ -2468,7 +2476,7 @@
         <v>9</v>
       </c>
       <c r="J32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2479,16 +2487,16 @@
         <v>11</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D33" s="55" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E33" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F33" s="52" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G33" s="17" t="s">
         <v>22</v>
@@ -2500,7 +2508,7 @@
         <v>9</v>
       </c>
       <c r="J33" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2511,16 +2519,16 @@
         <v>11</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E34" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F34" s="41" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G34" s="17" t="s">
         <v>22</v>
@@ -2532,7 +2540,7 @@
         <v>9</v>
       </c>
       <c r="J34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2543,16 +2551,16 @@
         <v>11</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E35" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F35" s="52" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G35" s="17" t="s">
         <v>22</v>
@@ -2564,7 +2572,7 @@
         <v>9</v>
       </c>
       <c r="J35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -2575,16 +2583,16 @@
         <v>11</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E36" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F36" s="54" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G36" s="17" t="s">
         <v>22</v>
@@ -2596,7 +2604,7 @@
         <v>9</v>
       </c>
       <c r="J36" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2607,16 +2615,16 @@
         <v>11</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E37" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F37" s="54" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G37" s="17" t="s">
         <v>22</v>
@@ -2628,7 +2636,7 @@
         <v>9</v>
       </c>
       <c r="J37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2639,16 +2647,16 @@
         <v>11</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E38" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F38" s="44" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G38" s="17" t="s">
         <v>22</v>
@@ -2660,7 +2668,7 @@
         <v>9</v>
       </c>
       <c r="J38" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2671,16 +2679,16 @@
         <v>11</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E39" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F39" s="44" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G39" s="17" t="s">
         <v>22</v>
@@ -2692,7 +2700,7 @@
         <v>9</v>
       </c>
       <c r="J39" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="60" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -2703,10 +2711,10 @@
         <v>11</v>
       </c>
       <c r="C40" s="58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D40" s="24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E40" s="22" t="s">
         <v>33</v>
@@ -2722,7 +2730,7 @@
         <v>26</v>
       </c>
       <c r="J40" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
@@ -2733,10 +2741,10 @@
         <v>11</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E41" s="28"/>
       <c r="F41" s="45"/>
@@ -2750,7 +2758,7 @@
         <v>9</v>
       </c>
       <c r="J41" s="64" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2761,16 +2769,16 @@
         <v>11</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E42" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F42" s="41" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>22</v>
@@ -2782,7 +2790,7 @@
         <v>26</v>
       </c>
       <c r="J42" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2793,16 +2801,16 @@
         <v>11</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E43" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F43" s="41" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>22</v>
@@ -2814,7 +2822,7 @@
         <v>26</v>
       </c>
       <c r="J43" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2825,16 +2833,16 @@
         <v>11</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E44" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F44" s="41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G44" s="17" t="s">
         <v>22</v>
@@ -2846,7 +2854,7 @@
         <v>9</v>
       </c>
       <c r="J44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2857,16 +2865,16 @@
         <v>11</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E45" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F45" s="41" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>22</v>
@@ -2878,7 +2886,7 @@
         <v>26</v>
       </c>
       <c r="J45" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2889,16 +2897,16 @@
         <v>11</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E46" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F46" s="41" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>22</v>
@@ -2910,7 +2918,7 @@
         <v>26</v>
       </c>
       <c r="J46" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2921,16 +2929,16 @@
         <v>11</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E47" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F47" s="52" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>22</v>
@@ -2942,7 +2950,7 @@
         <v>26</v>
       </c>
       <c r="J47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2953,16 +2961,16 @@
         <v>11</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D48" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E48" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F48" s="46" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>22</v>
@@ -2974,7 +2982,7 @@
         <v>26</v>
       </c>
       <c r="J48" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -2985,16 +2993,16 @@
         <v>11</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E49" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F49" s="46" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>22</v>
@@ -3006,7 +3014,7 @@
         <v>26</v>
       </c>
       <c r="J49" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="60" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -3017,10 +3025,10 @@
         <v>11</v>
       </c>
       <c r="C50" s="58" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D50" s="24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E50" s="25"/>
       <c r="F50" s="42"/>
@@ -3034,7 +3042,7 @@
         <v>26</v>
       </c>
       <c r="J50" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
@@ -3045,10 +3053,10 @@
         <v>11</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D51" s="23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E51" s="28"/>
       <c r="F51" s="45"/>
@@ -3062,7 +3070,7 @@
         <v>9</v>
       </c>
       <c r="J51" s="64" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3073,16 +3081,16 @@
         <v>11</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E52" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F52" s="41" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>22</v>
@@ -3094,7 +3102,7 @@
         <v>26</v>
       </c>
       <c r="J52" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3105,16 +3113,16 @@
         <v>11</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E53" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F53" s="41" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>22</v>
@@ -3126,7 +3134,7 @@
         <v>26</v>
       </c>
       <c r="J53" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3137,16 +3145,16 @@
         <v>11</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D54" s="19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E54" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F54" s="41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>22</v>
@@ -3158,7 +3166,7 @@
         <v>26</v>
       </c>
       <c r="J54" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3169,16 +3177,16 @@
         <v>11</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E55" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F55" s="52" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>22</v>
@@ -3190,7 +3198,7 @@
         <v>26</v>
       </c>
       <c r="J55" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3201,16 +3209,16 @@
         <v>11</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E56" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F56" s="54" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>22</v>
@@ -3222,7 +3230,7 @@
         <v>26</v>
       </c>
       <c r="J56" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3233,16 +3241,16 @@
         <v>11</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E57" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F57" s="52" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G57" s="17" t="s">
         <v>22</v>
@@ -3254,7 +3262,7 @@
         <v>9</v>
       </c>
       <c r="J57" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3265,16 +3273,16 @@
         <v>11</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E58" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F58" s="52" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>22</v>
@@ -3286,7 +3294,7 @@
         <v>26</v>
       </c>
       <c r="J58" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
@@ -3297,10 +3305,10 @@
         <v>11</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E59" s="19"/>
       <c r="F59" s="40"/>
@@ -3314,7 +3322,7 @@
         <v>26</v>
       </c>
       <c r="J59" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
@@ -3325,10 +3333,10 @@
         <v>11</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E60" s="19"/>
       <c r="F60" s="40"/>
@@ -3342,7 +3350,7 @@
         <v>26</v>
       </c>
       <c r="J60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3353,16 +3361,16 @@
         <v>11</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E61" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F61" s="41" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G61" s="17" t="s">
         <v>22</v>
@@ -3374,7 +3382,7 @@
         <v>9</v>
       </c>
       <c r="J61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3385,16 +3393,16 @@
         <v>11</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D62" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E62" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F62" s="46" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>22</v>
@@ -3406,7 +3414,7 @@
         <v>26</v>
       </c>
       <c r="J62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3417,16 +3425,16 @@
         <v>11</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D63" s="26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E63" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F63" s="46" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>22</v>
@@ -3438,7 +3446,7 @@
         <v>26</v>
       </c>
       <c r="J63" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="64" spans="1:10" s="60" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -3449,10 +3457,10 @@
         <v>11</v>
       </c>
       <c r="C64" s="58" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D64" s="24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E64" s="25"/>
       <c r="F64" s="42"/>
@@ -3466,7 +3474,7 @@
         <v>26</v>
       </c>
       <c r="J64" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
@@ -3477,10 +3485,10 @@
         <v>11</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E65" s="28"/>
       <c r="F65" s="45"/>
@@ -3494,7 +3502,7 @@
         <v>9</v>
       </c>
       <c r="J65" s="64" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3505,16 +3513,16 @@
         <v>11</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E66" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F66" s="41" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>22</v>
@@ -3526,7 +3534,7 @@
         <v>9</v>
       </c>
       <c r="J66" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3537,16 +3545,16 @@
         <v>11</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E67" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F67" s="61" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>22</v>
@@ -3558,7 +3566,7 @@
         <v>26</v>
       </c>
       <c r="J67" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -3569,10 +3577,10 @@
         <v>11</v>
       </c>
       <c r="C68" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D68" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E68" s="14"/>
       <c r="F68" s="61"/>
@@ -3586,7 +3594,7 @@
         <v>26</v>
       </c>
       <c r="J68" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -3597,10 +3605,10 @@
         <v>11</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E69" s="14"/>
       <c r="F69" s="61"/>
@@ -3614,7 +3622,7 @@
         <v>26</v>
       </c>
       <c r="J69" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
@@ -3625,10 +3633,10 @@
         <v>11</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D70" s="29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E70" s="30"/>
       <c r="F70" s="47"/>
@@ -3642,7 +3650,7 @@
         <v>9</v>
       </c>
       <c r="J70" s="64" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3653,16 +3661,16 @@
         <v>11</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E71" s="22" t="s">
         <v>33</v>
       </c>
       <c r="F71" s="41" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>22</v>
@@ -3674,7 +3682,7 @@
         <v>9</v>
       </c>
       <c r="J71" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="72" spans="1:10" s="60" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -3685,10 +3693,10 @@
         <v>11</v>
       </c>
       <c r="C72" s="58" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D72" s="24" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E72" s="25"/>
       <c r="F72" s="42"/>
@@ -3702,7 +3710,7 @@
         <v>26</v>
       </c>
       <c r="J72" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
@@ -3713,10 +3721,10 @@
         <v>11</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D73" s="23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E73" s="28"/>
       <c r="F73" s="45"/>
@@ -3730,7 +3738,7 @@
         <v>9</v>
       </c>
       <c r="J73" s="64" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -3741,16 +3749,16 @@
         <v>11</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D74" s="31" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F74" s="48" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G74" s="17" t="s">
         <v>22</v>
@@ -3762,7 +3770,7 @@
         <v>9</v>
       </c>
       <c r="J74" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3773,16 +3781,16 @@
         <v>11</v>
       </c>
       <c r="C75" s="18" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F75" s="41" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G75" s="17" t="s">
         <v>22</v>
@@ -3794,7 +3802,7 @@
         <v>9</v>
       </c>
       <c r="J75" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3805,16 +3813,16 @@
         <v>11</v>
       </c>
       <c r="C76" s="18" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F76" s="41" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G76" s="17" t="s">
         <v>22</v>
@@ -3826,7 +3834,7 @@
         <v>9</v>
       </c>
       <c r="J76" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -3837,16 +3845,16 @@
         <v>11</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F77" s="41" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G77" s="17" t="s">
         <v>22</v>
@@ -3858,7 +3866,7 @@
         <v>9</v>
       </c>
       <c r="J77" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -3869,16 +3877,16 @@
         <v>11</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D78" s="19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F78" s="41" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G78" s="17" t="s">
         <v>22</v>
@@ -3890,7 +3898,7 @@
         <v>9</v>
       </c>
       <c r="J78" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3901,16 +3909,16 @@
         <v>11</v>
       </c>
       <c r="C79" s="18" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D79" s="32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F79" s="45" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G79" s="63" t="s">
         <v>22</v>
@@ -3922,7 +3930,7 @@
         <v>9</v>
       </c>
       <c r="J79" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3933,16 +3941,16 @@
         <v>11</v>
       </c>
       <c r="C80" s="18" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D80" s="19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F80" s="41" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>24</v>
@@ -3954,7 +3962,7 @@
         <v>9</v>
       </c>
       <c r="J80" s="64" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3965,16 +3973,16 @@
         <v>11</v>
       </c>
       <c r="C81" s="18" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F81" s="40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G81" s="17" t="s">
         <v>22</v>
@@ -3986,7 +3994,7 @@
         <v>9</v>
       </c>
       <c r="J81" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -3997,16 +4005,16 @@
         <v>11</v>
       </c>
       <c r="C82" s="18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D82" s="19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F82" s="40" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G82" s="17" t="s">
         <v>22</v>
@@ -4018,7 +4026,7 @@
         <v>9</v>
       </c>
       <c r="J82" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -4029,16 +4037,16 @@
         <v>11</v>
       </c>
       <c r="C83" s="18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D83" s="32" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F83" s="45" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G83" s="63" t="s">
         <v>22</v>
@@ -4050,7 +4058,7 @@
         <v>9</v>
       </c>
       <c r="J83" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -4061,16 +4069,16 @@
         <v>11</v>
       </c>
       <c r="C84" s="18" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D84" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E84" s="13" t="s">
         <v>24</v>
       </c>
       <c r="F84" s="41" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>24</v>
@@ -4082,7 +4090,7 @@
         <v>9</v>
       </c>
       <c r="J84" s="64" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -4093,16 +4101,16 @@
         <v>11</v>
       </c>
       <c r="C85" s="18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D85" s="19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F85" s="41" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G85" s="17" t="s">
         <v>22</v>
@@ -4114,7 +4122,7 @@
         <v>9</v>
       </c>
       <c r="J85" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
@@ -4125,16 +4133,16 @@
         <v>11</v>
       </c>
       <c r="C86" s="18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D86" s="19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F86" s="41" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G86" s="17" t="s">
         <v>22</v>
@@ -4146,7 +4154,7 @@
         <v>9</v>
       </c>
       <c r="J86" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -4157,16 +4165,16 @@
         <v>11</v>
       </c>
       <c r="C87" s="18" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D87" s="32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F87" s="45" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>22</v>
@@ -4178,7 +4186,7 @@
         <v>9</v>
       </c>
       <c r="J87" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -4189,16 +4197,16 @@
         <v>11</v>
       </c>
       <c r="C88" s="18" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D88" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F88" s="43" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G88" s="17" t="s">
         <v>22</v>
@@ -4210,7 +4218,7 @@
         <v>9</v>
       </c>
       <c r="J88" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -4221,16 +4229,16 @@
         <v>11</v>
       </c>
       <c r="C89" s="18" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D89" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="E89" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="E89" s="13" t="s">
-        <v>91</v>
-      </c>
       <c r="F89" s="41" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G89" s="17" t="s">
         <v>22</v>
@@ -4242,7 +4250,7 @@
         <v>9</v>
       </c>
       <c r="J89" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/mapping/field_mapping.xlsx
+++ b/mapping/field_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Water collectives\WHS Assessment\auto gen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A80E70F-1C2F-4B26-8910-6674047E9E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{444B1A81-FC0C-489F-879D-AA38985F7574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B03A0D84-276C-499F-A511-71567CA886FB}"/>
   </bookViews>
@@ -725,7 +725,7 @@
     <t>metal-lead_metal_mamidipalli_km</t>
   </si>
   <si>
-    <t>1.1 Discarge</t>
+    <t>1.1 Water Discharge</t>
   </si>
 </sst>
 </file>

--- a/mapping/field_mapping.xlsx
+++ b/mapping/field_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Water collectives\WHS Assessment\auto gen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE398C3D-FF42-488C-B480-366208CBF9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8A87B6-AE6E-46C1-AC65-55DB9FC0362D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{B03A0D84-276C-499F-A511-71567CA886FB}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Repeat Mapping" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Repeat Mapping'!$A$1:$M$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Repeat Mapping'!$A$1:$M$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1125" uniqueCount="325">
   <si>
     <t>Sl.No</t>
   </si>
@@ -886,15 +886,9 @@
     <t>Detail Column</t>
   </si>
   <si>
-    <t>E40/E41</t>
-  </si>
-  <si>
     <t>E</t>
   </si>
   <si>
-    <t>Right → E40; Left → E41</t>
-  </si>
-  <si>
     <t>Sum GWR length by side</t>
   </si>
   <si>
@@ -1031,6 +1025,15 @@
   </si>
   <si>
     <t>E19/E20</t>
+  </si>
+  <si>
+    <t>avg_length_gwl</t>
+  </si>
+  <si>
+    <t>Left → E41</t>
+  </si>
+  <si>
+    <t>Right → E40</t>
   </si>
 </sst>
 </file>
@@ -4029,7 +4032,7 @@
         <v>29</v>
       </c>
       <c r="F70" s="70" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>22</v>
@@ -4713,7 +4716,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14526625-C6E6-4A6B-94C7-2E3FA4EA86BF}">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
@@ -4780,37 +4783,37 @@
         <v>193</v>
       </c>
       <c r="C2" s="72" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D2" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F2" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G2" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H2" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I2" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K2" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="L2" s="72" t="s">
+        <v>277</v>
+      </c>
+      <c r="M2" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="E2" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F2" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G2" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H2" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="I2" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K2" s="32" t="s">
-        <v>285</v>
-      </c>
-      <c r="L2" s="72" t="s">
-        <v>279</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="30">
@@ -4821,10 +4824,10 @@
         <v>193</v>
       </c>
       <c r="C3" s="72" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E3" s="32" t="s">
         <v>187</v>
@@ -4845,13 +4848,13 @@
         <v>187</v>
       </c>
       <c r="K3" s="32" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="L3" s="72" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="8" customFormat="1">
@@ -4885,10 +4888,10 @@
       <c r="J4" s="73"/>
       <c r="K4" s="73"/>
       <c r="L4" s="75" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M4" s="79" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="8" customFormat="1">
@@ -4905,10 +4908,10 @@
         <v>189</v>
       </c>
       <c r="E5" s="75" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F5" s="73" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G5" s="75" t="s">
         <v>186</v>
@@ -4922,10 +4925,10 @@
       <c r="J5" s="73"/>
       <c r="K5" s="73"/>
       <c r="L5" s="75" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M5" s="79" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="30">
@@ -4945,7 +4948,7 @@
         <v>234</v>
       </c>
       <c r="F6" s="73" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G6" s="32" t="s">
         <v>190</v>
@@ -4962,7 +4965,7 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="26" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="30">
@@ -4973,37 +4976,37 @@
         <v>195</v>
       </c>
       <c r="C7" s="72" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D7" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="E7" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="F7" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="G7" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="H7" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="K7" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="L7" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="M7" s="26" t="s">
         <v>284</v>
-      </c>
-      <c r="E7" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="F7" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="G7" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="H7" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="I7" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="K7" s="32" t="s">
-        <v>285</v>
-      </c>
-      <c r="L7" s="32" t="s">
-        <v>279</v>
-      </c>
-      <c r="M7" s="26" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="30">
@@ -5014,10 +5017,10 @@
         <v>195</v>
       </c>
       <c r="C8" s="72" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E8" s="73" t="s">
         <v>187</v>
@@ -5038,13 +5041,13 @@
         <v>187</v>
       </c>
       <c r="K8" s="32" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="L8" s="32" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M8" s="26" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5061,10 +5064,10 @@
         <v>189</v>
       </c>
       <c r="E9" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="F9" s="32" t="s">
         <v>275</v>
-      </c>
-      <c r="F9" s="32" t="s">
-        <v>276</v>
       </c>
       <c r="G9" s="32" t="s">
         <v>186</v>
@@ -5076,19 +5079,19 @@
         <v>22</v>
       </c>
       <c r="J9" s="32" t="s">
+        <v>324</v>
+      </c>
+      <c r="K9" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="L9" s="32" t="s">
         <v>277</v>
       </c>
-      <c r="K9" s="32" t="s">
+      <c r="M9" s="80" t="s">
         <v>278</v>
       </c>
-      <c r="L9" s="32" t="s">
-        <v>279</v>
-      </c>
-      <c r="M9" s="80" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="30">
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="72" t="s">
         <v>268</v>
       </c>
@@ -5096,37 +5099,37 @@
         <v>269</v>
       </c>
       <c r="C10" s="72" t="s">
-        <v>281</v>
+        <v>322</v>
       </c>
       <c r="D10" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>233</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="G10" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E10" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F10" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G10" s="32" t="s">
-        <v>187</v>
-      </c>
       <c r="H10" s="32" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="I10" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>187</v>
+        <v>323</v>
       </c>
       <c r="K10" s="32" t="s">
-        <v>282</v>
-      </c>
-      <c r="L10" s="72" t="s">
-        <v>279</v>
-      </c>
-      <c r="M10" s="9" t="s">
         <v>276</v>
+      </c>
+      <c r="L10" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="M10" s="80" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="30">
@@ -5137,10 +5140,10 @@
         <v>269</v>
       </c>
       <c r="C11" s="72" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>284</v>
+        <v>186</v>
       </c>
       <c r="E11" s="32" t="s">
         <v>187</v>
@@ -5161,13 +5164,13 @@
         <v>187</v>
       </c>
       <c r="K11" s="32" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="L11" s="72" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="30">
@@ -5178,10 +5181,10 @@
         <v>269</v>
       </c>
       <c r="C12" s="72" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E12" s="32" t="s">
         <v>187</v>
@@ -5202,72 +5205,74 @@
         <v>187</v>
       </c>
       <c r="K12" s="32" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="L12" s="72" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="30">
       <c r="A13" s="72" t="s">
+        <v>268</v>
+      </c>
+      <c r="B13" s="72" t="s">
+        <v>269</v>
+      </c>
+      <c r="C13" s="72" t="s">
+        <v>285</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="E13" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G13" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H13" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I13" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K13" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="L13" s="72" t="s">
+        <v>277</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="30">
+      <c r="A14" s="72" t="s">
+        <v>294</v>
+      </c>
+      <c r="B14" s="72" t="s">
         <v>296</v>
       </c>
-      <c r="B13" s="72" t="s">
-        <v>298</v>
-      </c>
-      <c r="C13" s="72" t="s">
+      <c r="C14" s="72" t="s">
         <v>265</v>
       </c>
-      <c r="D13" s="32" t="s">
-        <v>293</v>
-      </c>
-      <c r="E13" s="71" t="s">
-        <v>241</v>
-      </c>
-      <c r="F13" s="32" t="s">
-        <v>276</v>
-      </c>
-      <c r="G13" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H13" s="71" t="s">
-        <v>178</v>
-      </c>
-      <c r="I13" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32" t="s">
-        <v>279</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="45">
-      <c r="A14" s="72" t="s">
-        <v>297</v>
-      </c>
-      <c r="B14" s="72" t="s">
-        <v>299</v>
-      </c>
-      <c r="C14" s="72" t="s">
-        <v>294</v>
-      </c>
       <c r="D14" s="32" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="E14" s="71" t="s">
         <v>241</v>
       </c>
       <c r="F14" s="32" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G14" s="32" t="s">
         <v>187</v>
@@ -5281,32 +5286,32 @@
       <c r="J14" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="K14" s="1"/>
+      <c r="K14" s="32"/>
       <c r="L14" s="32" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="30">
-      <c r="A15" s="77" t="s">
-        <v>300</v>
-      </c>
-      <c r="B15" s="77" t="s">
-        <v>301</v>
+        <v>278</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="45">
+      <c r="A15" s="72" t="s">
+        <v>295</v>
+      </c>
+      <c r="B15" s="72" t="s">
+        <v>297</v>
       </c>
       <c r="C15" s="72" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>189</v>
+        <v>293</v>
       </c>
       <c r="E15" s="71" t="s">
         <v>241</v>
       </c>
-      <c r="F15" s="71" t="s">
-        <v>276</v>
+      <c r="F15" s="32" t="s">
+        <v>275</v>
       </c>
       <c r="G15" s="32" t="s">
         <v>187</v>
@@ -5320,40 +5325,38 @@
       <c r="J15" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="K15" s="32" t="s">
-        <v>306</v>
-      </c>
+      <c r="K15" s="1"/>
       <c r="L15" s="32" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="30">
-      <c r="A16" s="72" t="s">
-        <v>297</v>
-      </c>
-      <c r="B16" s="72" t="s">
-        <v>311</v>
+      <c r="A16" s="77" t="s">
+        <v>298</v>
+      </c>
+      <c r="B16" s="77" t="s">
+        <v>299</v>
       </c>
       <c r="C16" s="72" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>284</v>
-      </c>
-      <c r="E16" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F16" s="32" t="s">
-        <v>187</v>
+        <v>189</v>
+      </c>
+      <c r="E16" s="71" t="s">
+        <v>241</v>
+      </c>
+      <c r="F16" s="71" t="s">
+        <v>275</v>
       </c>
       <c r="G16" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="H16" s="32" t="s">
-        <v>187</v>
+      <c r="H16" s="71" t="s">
+        <v>178</v>
       </c>
       <c r="I16" s="32" t="s">
         <v>22</v>
@@ -5362,27 +5365,27 @@
         <v>187</v>
       </c>
       <c r="K16" s="32" t="s">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="L16" s="32" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="30">
       <c r="A17" s="72" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B17" s="72" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C17" s="72" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E17" s="32" t="s">
         <v>187</v>
@@ -5403,27 +5406,27 @@
         <v>187</v>
       </c>
       <c r="K17" s="32" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="L17" s="32" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M17" s="9" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="30">
       <c r="A18" s="72" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B18" s="72" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C18" s="72" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E18" s="32" t="s">
         <v>187</v>
@@ -5444,68 +5447,68 @@
         <v>187</v>
       </c>
       <c r="K18" s="32" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="L18" s="32" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M18" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="30">
       <c r="A19" s="72" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B19" s="72" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C19" s="72" t="s">
+        <v>307</v>
+      </c>
+      <c r="D19" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="E19" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G19" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H19" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I19" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K19" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="L19" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="30">
+      <c r="A20" s="72" t="s">
+        <v>294</v>
+      </c>
+      <c r="B20" s="72" t="s">
         <v>310</v>
       </c>
-      <c r="D19" s="32" t="s">
-        <v>288</v>
-      </c>
-      <c r="E19" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F19" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G19" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H19" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="I19" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J19" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K19" s="32" t="s">
-        <v>285</v>
-      </c>
-      <c r="L19" s="32" t="s">
-        <v>279</v>
-      </c>
-      <c r="M19" s="9" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="30">
-      <c r="A20" s="77" t="s">
-        <v>300</v>
-      </c>
-      <c r="B20" s="77" t="s">
-        <v>302</v>
-      </c>
       <c r="C20" s="72" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E20" s="32" t="s">
         <v>187</v>
@@ -5526,68 +5529,68 @@
         <v>187</v>
       </c>
       <c r="K20" s="32" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="L20" s="32" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M20" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="30">
       <c r="A21" s="77" t="s">
+        <v>298</v>
+      </c>
+      <c r="B21" s="77" t="s">
         <v>300</v>
       </c>
-      <c r="B21" s="77" t="s">
+      <c r="C21" s="72" t="s">
+        <v>301</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="E21" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F21" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G21" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H21" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I21" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K21" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="L21" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="30">
+      <c r="A22" s="77" t="s">
+        <v>298</v>
+      </c>
+      <c r="B22" s="77" t="s">
+        <v>300</v>
+      </c>
+      <c r="C22" s="72" t="s">
         <v>302</v>
       </c>
-      <c r="C21" s="72" t="s">
-        <v>304</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>288</v>
-      </c>
-      <c r="E21" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F21" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G21" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H21" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="I21" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J21" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K21" s="32" t="s">
-        <v>285</v>
-      </c>
-      <c r="L21" s="32" t="s">
-        <v>279</v>
-      </c>
-      <c r="M21" s="9" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="30">
-      <c r="A22" s="72" t="s">
-        <v>321</v>
-      </c>
-      <c r="B22" s="72" t="s">
-        <v>322</v>
-      </c>
-      <c r="C22" s="72" t="s">
-        <v>315</v>
-      </c>
       <c r="D22" s="32" t="s">
-        <v>186</v>
+        <v>286</v>
       </c>
       <c r="E22" s="32" t="s">
         <v>187</v>
@@ -5608,27 +5611,27 @@
         <v>187</v>
       </c>
       <c r="K22" s="32" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L22" s="32" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M22" s="9" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="30">
       <c r="A23" s="72" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B23" s="72" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C23" s="72" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D23" s="32" t="s">
-        <v>284</v>
+        <v>186</v>
       </c>
       <c r="E23" s="32" t="s">
         <v>187</v>
@@ -5649,99 +5652,140 @@
         <v>187</v>
       </c>
       <c r="K23" s="32" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="L23" s="32" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M23" s="9" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="30">
       <c r="A24" s="72" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B24" s="72" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C24" s="72" t="s">
+        <v>314</v>
+      </c>
+      <c r="D24" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="E24" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F24" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G24" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H24" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I24" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K24" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="L24" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="M24" s="9" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="30">
+      <c r="A25" s="72" t="s">
+        <v>319</v>
+      </c>
+      <c r="B25" s="72" t="s">
+        <v>320</v>
+      </c>
+      <c r="C25" s="72" t="s">
+        <v>315</v>
+      </c>
+      <c r="D25" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="E25" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F25" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G25" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H25" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I25" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K25" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="L25" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="72" t="s">
+        <v>319</v>
+      </c>
+      <c r="B26" s="72" t="s">
+        <v>320</v>
+      </c>
+      <c r="C26" s="72" t="s">
+        <v>316</v>
+      </c>
+      <c r="D26" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="E26" s="71" t="s">
+        <v>242</v>
+      </c>
+      <c r="F26" s="71" t="s">
+        <v>275</v>
+      </c>
+      <c r="G26" s="71" t="s">
+        <v>186</v>
+      </c>
+      <c r="H26" s="71" t="s">
+        <v>178</v>
+      </c>
+      <c r="I26" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" s="32" t="s">
         <v>317</v>
       </c>
-      <c r="D24" s="32" t="s">
-        <v>288</v>
-      </c>
-      <c r="E24" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F24" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G24" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H24" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="I24" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J24" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K24" s="32" t="s">
-        <v>285</v>
-      </c>
-      <c r="L24" s="32" t="s">
-        <v>279</v>
-      </c>
-      <c r="M24" s="9" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="72" t="s">
-        <v>321</v>
-      </c>
-      <c r="B25" s="72" t="s">
-        <v>322</v>
-      </c>
-      <c r="C25" s="72" t="s">
+      <c r="K26" s="32" t="s">
         <v>318</v>
       </c>
-      <c r="D25" s="32" t="s">
-        <v>189</v>
-      </c>
-      <c r="E25" s="71" t="s">
-        <v>242</v>
-      </c>
-      <c r="F25" s="71" t="s">
-        <v>276</v>
-      </c>
-      <c r="G25" s="71" t="s">
-        <v>186</v>
-      </c>
-      <c r="H25" s="71" t="s">
-        <v>178</v>
-      </c>
-      <c r="I25" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J25" s="32" t="s">
-        <v>319</v>
-      </c>
-      <c r="K25" s="32" t="s">
-        <v>320</v>
-      </c>
-      <c r="L25" s="32" t="s">
-        <v>279</v>
-      </c>
-      <c r="M25" s="9" t="s">
-        <v>280</v>
+      <c r="L26" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="M26" s="9" t="s">
+        <v>278</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M25" xr:uid="{14526625-C6E6-4A6B-94C7-2E3FA4EA86BF}"/>
+  <autoFilter ref="A1:M26" xr:uid="{14526625-C6E6-4A6B-94C7-2E3FA4EA86BF}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/mapping/field_mapping.xlsx
+++ b/mapping/field_mapping.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Water collectives\WHS Assessment\auto gen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8A87B6-AE6E-46C1-AC65-55DB9FC0362D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{840EA080-84ED-4D09-B28E-9E0F334193B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{B03A0D84-276C-499F-A511-71567CA886FB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B03A0D84-276C-499F-A511-71567CA886FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Repeat Mapping" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Repeat Mapping'!$A$1:$M$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Repeat Mapping'!$A$1:$M$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1125" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="323">
   <si>
     <t>Sl.No</t>
   </si>
@@ -625,9 +625,6 @@
     <t>—</t>
   </si>
   <si>
-    <t>length_ncg</t>
-  </si>
-  <si>
     <t>Length</t>
   </si>
   <si>
@@ -1022,9 +1019,6 @@
   </si>
   <si>
     <t>nboe/nboe_</t>
-  </si>
-  <si>
-    <t>E19/E20</t>
   </si>
   <si>
     <t>avg_length_gwl</t>
@@ -2521,7 +2515,7 @@
         <v>11</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D22" s="18" t="s">
         <v>31</v>
@@ -2553,7 +2547,7 @@
         <v>11</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D23" s="18" t="s">
         <v>32</v>
@@ -2611,7 +2605,7 @@
         <v>11</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D25" s="66" t="s">
         <v>148</v>
@@ -2673,7 +2667,7 @@
         <v>11</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D27" s="18" t="s">
         <v>34</v>
@@ -2733,7 +2727,7 @@
         <v>11</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D29" s="18" t="s">
         <v>154</v>
@@ -2765,7 +2759,7 @@
         <v>11</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D30" s="18" t="s">
         <v>157</v>
@@ -2797,7 +2791,7 @@
         <v>11</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D31" s="47" t="s">
         <v>158</v>
@@ -2829,7 +2823,7 @@
         <v>11</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D32" s="47" t="s">
         <v>162</v>
@@ -2861,7 +2855,7 @@
         <v>11</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D33" s="47" t="s">
         <v>163</v>
@@ -2893,7 +2887,7 @@
         <v>11</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D34" s="18" t="s">
         <v>39</v>
@@ -2925,7 +2919,7 @@
         <v>11</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D35" s="52" t="s">
         <v>81</v>
@@ -2957,7 +2951,7 @@
         <v>11</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D36" s="18" t="s">
         <v>41</v>
@@ -2989,7 +2983,7 @@
         <v>11</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D37" s="18" t="s">
         <v>42</v>
@@ -3021,7 +3015,7 @@
         <v>11</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D38" s="18" t="s">
         <v>43</v>
@@ -3053,7 +3047,7 @@
         <v>11</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D39" s="18" t="s">
         <v>44</v>
@@ -3085,7 +3079,7 @@
         <v>11</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D40" s="25" t="s">
         <v>170</v>
@@ -3094,7 +3088,7 @@
         <v>29</v>
       </c>
       <c r="F40" s="69" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>22</v>
@@ -3117,7 +3111,7 @@
         <v>11</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D41" s="25" t="s">
         <v>171</v>
@@ -3126,7 +3120,7 @@
         <v>29</v>
       </c>
       <c r="F41" s="69" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G41" s="16" t="s">
         <v>22</v>
@@ -3149,7 +3143,7 @@
         <v>11</v>
       </c>
       <c r="C42" s="55" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D42" s="23" t="s">
         <v>47</v>
@@ -3179,7 +3173,7 @@
         <v>11</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D43" s="22" t="s">
         <v>48</v>
@@ -3207,7 +3201,7 @@
         <v>11</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D44" s="18" t="s">
         <v>162</v>
@@ -3239,7 +3233,7 @@
         <v>11</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D45" s="18" t="s">
         <v>163</v>
@@ -3271,7 +3265,7 @@
         <v>11</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D46" s="18" t="s">
         <v>39</v>
@@ -3303,7 +3297,7 @@
         <v>11</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D47" s="18" t="s">
         <v>40</v>
@@ -3335,7 +3329,7 @@
         <v>11</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D48" s="18" t="s">
         <v>41</v>
@@ -3367,7 +3361,7 @@
         <v>11</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D49" s="18" t="s">
         <v>42</v>
@@ -3399,7 +3393,7 @@
         <v>11</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D50" s="25" t="s">
         <v>45</v>
@@ -3408,7 +3402,7 @@
         <v>29</v>
       </c>
       <c r="F50" s="69" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>22</v>
@@ -3431,7 +3425,7 @@
         <v>11</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D51" s="25" t="s">
         <v>46</v>
@@ -3440,7 +3434,7 @@
         <v>29</v>
       </c>
       <c r="F51" s="69" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>22</v>
@@ -3463,7 +3457,7 @@
         <v>11</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D52" s="23" t="s">
         <v>47</v>
@@ -3491,7 +3485,7 @@
         <v>11</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D53" s="22" t="s">
         <v>49</v>
@@ -3519,7 +3513,7 @@
         <v>11</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D54" s="18" t="s">
         <v>36</v>
@@ -3551,7 +3545,7 @@
         <v>11</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D55" s="18" t="s">
         <v>37</v>
@@ -3583,7 +3577,7 @@
         <v>11</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D56" s="18" t="s">
         <v>38</v>
@@ -3615,7 +3609,7 @@
         <v>11</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D57" s="18" t="s">
         <v>50</v>
@@ -3647,7 +3641,7 @@
         <v>11</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D58" s="18" t="s">
         <v>51</v>
@@ -3679,7 +3673,7 @@
         <v>11</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D59" s="18" t="s">
         <v>39</v>
@@ -3711,7 +3705,7 @@
         <v>11</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D60" s="18" t="s">
         <v>52</v>
@@ -3743,7 +3737,7 @@
         <v>11</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D61" s="18" t="s">
         <v>53</v>
@@ -3752,7 +3746,7 @@
         <v>29</v>
       </c>
       <c r="F61" s="70" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>22</v>
@@ -3775,7 +3769,7 @@
         <v>11</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D62" s="18" t="s">
         <v>54</v>
@@ -3784,7 +3778,7 @@
         <v>29</v>
       </c>
       <c r="F62" s="70" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>22</v>
@@ -3807,7 +3801,7 @@
         <v>11</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D63" s="18" t="s">
         <v>55</v>
@@ -3839,7 +3833,7 @@
         <v>11</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D64" s="25" t="s">
         <v>45</v>
@@ -3848,7 +3842,7 @@
         <v>29</v>
       </c>
       <c r="F64" s="69" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>22</v>
@@ -3871,7 +3865,7 @@
         <v>11</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D65" s="25" t="s">
         <v>46</v>
@@ -3880,7 +3874,7 @@
         <v>29</v>
       </c>
       <c r="F65" s="69" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>22</v>
@@ -3903,7 +3897,7 @@
         <v>11</v>
       </c>
       <c r="C66" s="17" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D66" s="23" t="s">
         <v>47</v>
@@ -3931,7 +3925,7 @@
         <v>11</v>
       </c>
       <c r="C67" s="17" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D67" s="22" t="s">
         <v>56</v>
@@ -3959,7 +3953,7 @@
         <v>11</v>
       </c>
       <c r="C68" s="17" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D68" s="18" t="s">
         <v>57</v>
@@ -3991,7 +3985,7 @@
         <v>11</v>
       </c>
       <c r="C69" s="17" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D69" s="18" t="s">
         <v>58</v>
@@ -4023,7 +4017,7 @@
         <v>11</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D70" s="18" t="s">
         <v>59</v>
@@ -4032,7 +4026,7 @@
         <v>29</v>
       </c>
       <c r="F70" s="70" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>22</v>
@@ -4055,7 +4049,7 @@
         <v>11</v>
       </c>
       <c r="C71" s="17" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D71" s="18" t="s">
         <v>60</v>
@@ -4064,7 +4058,7 @@
         <v>29</v>
       </c>
       <c r="F71" s="58" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>22</v>
@@ -4087,7 +4081,7 @@
         <v>11</v>
       </c>
       <c r="C72" s="17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D72" s="28" t="s">
         <v>61</v>
@@ -4115,7 +4109,7 @@
         <v>11</v>
       </c>
       <c r="C73" s="17" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D73" s="18" t="s">
         <v>62</v>
@@ -4147,7 +4141,7 @@
         <v>11</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D74" s="23" t="s">
         <v>63</v>
@@ -4175,7 +4169,7 @@
         <v>11</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D75" s="22" t="s">
         <v>64</v>
@@ -4203,7 +4197,7 @@
         <v>11</v>
       </c>
       <c r="C76" s="17" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D76" s="30" t="s">
         <v>65</v>
@@ -4235,7 +4229,7 @@
         <v>11</v>
       </c>
       <c r="C77" s="17" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D77" s="18" t="s">
         <v>66</v>
@@ -4267,7 +4261,7 @@
         <v>11</v>
       </c>
       <c r="C78" s="17" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D78" s="18" t="s">
         <v>67</v>
@@ -4299,7 +4293,7 @@
         <v>11</v>
       </c>
       <c r="C79" s="17" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D79" s="18" t="s">
         <v>68</v>
@@ -4331,7 +4325,7 @@
         <v>11</v>
       </c>
       <c r="C80" s="17" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D80" s="18" t="s">
         <v>69</v>
@@ -4363,7 +4357,7 @@
         <v>11</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D81" s="31" t="s">
         <v>70</v>
@@ -4395,7 +4389,7 @@
         <v>11</v>
       </c>
       <c r="C82" s="17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D82" s="18" t="s">
         <v>71</v>
@@ -4427,7 +4421,7 @@
         <v>11</v>
       </c>
       <c r="C83" s="17" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D83" s="18" t="s">
         <v>72</v>
@@ -4459,7 +4453,7 @@
         <v>11</v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D84" s="18" t="s">
         <v>73</v>
@@ -4491,7 +4485,7 @@
         <v>11</v>
       </c>
       <c r="C85" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D85" s="31" t="s">
         <v>74</v>
@@ -4523,7 +4517,7 @@
         <v>11</v>
       </c>
       <c r="C86" s="17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D86" s="18" t="s">
         <v>67</v>
@@ -4555,7 +4549,7 @@
         <v>11</v>
       </c>
       <c r="C87" s="17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D87" s="18" t="s">
         <v>75</v>
@@ -4587,7 +4581,7 @@
         <v>11</v>
       </c>
       <c r="C88" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D88" s="18" t="s">
         <v>76</v>
@@ -4619,7 +4613,7 @@
         <v>11</v>
       </c>
       <c r="C89" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D89" s="31" t="s">
         <v>77</v>
@@ -4651,7 +4645,7 @@
         <v>11</v>
       </c>
       <c r="C90" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D90" s="18" t="s">
         <v>78</v>
@@ -4683,7 +4677,7 @@
         <v>11</v>
       </c>
       <c r="C91" s="17" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D91" s="18" t="s">
         <v>79</v>
@@ -4716,14 +4710,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14526625-C6E6-4A6B-94C7-2E3FA4EA86BF}">
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
     <col min="2" max="2" width="46.42578125" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="45.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -4739,7 +4733,7 @@
         <v>174</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>5</v>
@@ -4769,10 +4763,10 @@
         <v>177</v>
       </c>
       <c r="L1" s="71" t="s">
+        <v>272</v>
+      </c>
+      <c r="M1" s="9" t="s">
         <v>273</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="30">
@@ -4780,40 +4774,40 @@
         <v>184</v>
       </c>
       <c r="B2" s="72" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C2" s="72" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D2" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F2" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G2" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H2" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I2" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K2" s="32" t="s">
         <v>282</v>
       </c>
-      <c r="E2" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F2" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G2" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H2" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="I2" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K2" s="32" t="s">
+      <c r="L2" s="72" t="s">
+        <v>276</v>
+      </c>
+      <c r="M2" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="L2" s="72" t="s">
-        <v>277</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="30">
@@ -4821,40 +4815,40 @@
         <v>184</v>
       </c>
       <c r="B3" s="72" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C3" s="72" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D3" s="32" t="s">
+        <v>285</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H3" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I3" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K3" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="L3" s="72" t="s">
+        <v>276</v>
+      </c>
+      <c r="M3" s="9" t="s">
         <v>286</v>
-      </c>
-      <c r="E3" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F3" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G3" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H3" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="I3" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K3" s="32" t="s">
-        <v>283</v>
-      </c>
-      <c r="L3" s="72" t="s">
-        <v>277</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="8" customFormat="1">
@@ -4862,7 +4856,7 @@
         <v>184</v>
       </c>
       <c r="B4" s="78" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C4" s="74" t="s">
         <v>185</v>
@@ -4888,10 +4882,10 @@
       <c r="J4" s="73"/>
       <c r="K4" s="73"/>
       <c r="L4" s="75" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="M4" s="79" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="8" customFormat="1">
@@ -4899,19 +4893,19 @@
         <v>184</v>
       </c>
       <c r="B5" s="78" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C5" s="74" t="s">
+        <v>262</v>
+      </c>
+      <c r="D5" s="75" t="s">
         <v>188</v>
       </c>
-      <c r="D5" s="75" t="s">
-        <v>189</v>
-      </c>
       <c r="E5" s="75" t="s">
-        <v>321</v>
+        <v>211</v>
       </c>
       <c r="F5" s="73" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G5" s="75" t="s">
         <v>186</v>
@@ -4925,190 +4919,186 @@
       <c r="J5" s="73"/>
       <c r="K5" s="73"/>
       <c r="L5" s="75" t="s">
+        <v>276</v>
+      </c>
+      <c r="M5" s="79" t="s">
         <v>277</v>
       </c>
-      <c r="M5" s="79" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="30">
-      <c r="A6" s="32" t="s">
-        <v>194</v>
-      </c>
-      <c r="B6" s="32" t="s">
-        <v>195</v>
-      </c>
-      <c r="C6" s="72" t="s">
-        <v>191</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>189</v>
-      </c>
-      <c r="E6" s="32" t="s">
-        <v>234</v>
+    </row>
+    <row r="6" spans="1:13" s="8" customFormat="1">
+      <c r="A6" s="73" t="s">
+        <v>184</v>
+      </c>
+      <c r="B6" s="78" t="s">
+        <v>192</v>
+      </c>
+      <c r="C6" s="74" t="s">
+        <v>263</v>
+      </c>
+      <c r="D6" s="75" t="s">
+        <v>188</v>
+      </c>
+      <c r="E6" s="75" t="s">
+        <v>210</v>
       </c>
       <c r="F6" s="73" t="s">
-        <v>275</v>
-      </c>
-      <c r="G6" s="32" t="s">
-        <v>190</v>
-      </c>
-      <c r="H6" s="32" t="s">
+        <v>274</v>
+      </c>
+      <c r="G6" s="75" t="s">
+        <v>186</v>
+      </c>
+      <c r="H6" s="75" t="s">
         <v>178</v>
       </c>
-      <c r="I6" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="32" t="s">
-        <v>267</v>
-      </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="26" t="s">
-        <v>278</v>
+      <c r="I6" s="73" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="73"/>
+      <c r="K6" s="73"/>
+      <c r="L6" s="75" t="s">
+        <v>276</v>
+      </c>
+      <c r="M6" s="79" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="30">
       <c r="A7" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="B7" s="32" t="s">
         <v>194</v>
       </c>
-      <c r="B7" s="32" t="s">
-        <v>195</v>
-      </c>
       <c r="C7" s="72" t="s">
-        <v>311</v>
+        <v>190</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>282</v>
-      </c>
-      <c r="E7" s="73" t="s">
-        <v>187</v>
+        <v>188</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>233</v>
       </c>
       <c r="F7" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="G7" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="H7" s="73" t="s">
-        <v>187</v>
+        <v>274</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>178</v>
       </c>
       <c r="I7" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="K7" s="32" t="s">
-        <v>283</v>
-      </c>
-      <c r="L7" s="32" t="s">
+      <c r="J7" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="26" t="s">
         <v>277</v>
-      </c>
-      <c r="M7" s="26" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="30">
       <c r="A8" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="B8" s="32" t="s">
         <v>194</v>
       </c>
-      <c r="B8" s="32" t="s">
-        <v>195</v>
-      </c>
       <c r="C8" s="72" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D8" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="E8" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="F8" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="G8" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="H8" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="I8" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="K8" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="L8" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="M8" s="26" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="30">
+      <c r="A9" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="C9" s="72" t="s">
+        <v>311</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>285</v>
+      </c>
+      <c r="E9" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="F9" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="G9" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="H9" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="I9" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="K9" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="L9" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="M9" s="26" t="s">
         <v>286</v>
-      </c>
-      <c r="E8" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="F8" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="G8" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="H8" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="I8" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="K8" s="32" t="s">
-        <v>283</v>
-      </c>
-      <c r="L8" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="M8" s="26" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="72" t="s">
-        <v>268</v>
-      </c>
-      <c r="B9" s="72" t="s">
-        <v>269</v>
-      </c>
-      <c r="C9" s="72" t="s">
-        <v>270</v>
-      </c>
-      <c r="D9" s="32" t="s">
-        <v>189</v>
-      </c>
-      <c r="E9" s="32" t="s">
-        <v>232</v>
-      </c>
-      <c r="F9" s="32" t="s">
-        <v>275</v>
-      </c>
-      <c r="G9" s="32" t="s">
-        <v>186</v>
-      </c>
-      <c r="H9" s="32" t="s">
-        <v>178</v>
-      </c>
-      <c r="I9" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="32" t="s">
-        <v>324</v>
-      </c>
-      <c r="K9" s="32" t="s">
-        <v>276</v>
-      </c>
-      <c r="L9" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="M9" s="80" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="72" t="s">
+        <v>267</v>
+      </c>
+      <c r="B10" s="72" t="s">
         <v>268</v>
       </c>
-      <c r="B10" s="72" t="s">
+      <c r="C10" s="72" t="s">
         <v>269</v>
       </c>
-      <c r="C10" s="72" t="s">
-        <v>322</v>
-      </c>
       <c r="D10" s="32" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F10" s="32" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G10" s="32" t="s">
         <v>186</v>
@@ -5120,71 +5110,71 @@
         <v>22</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="K10" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="L10" s="32" t="s">
         <v>276</v>
       </c>
-      <c r="L10" s="32" t="s">
+      <c r="M10" s="80" t="s">
         <v>277</v>
       </c>
-      <c r="M10" s="80" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="30">
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="72" t="s">
+        <v>267</v>
+      </c>
+      <c r="B11" s="72" t="s">
         <v>268</v>
       </c>
-      <c r="B11" s="72" t="s">
-        <v>269</v>
-      </c>
       <c r="C11" s="72" t="s">
-        <v>279</v>
+        <v>320</v>
       </c>
       <c r="D11" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>274</v>
+      </c>
+      <c r="G11" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E11" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F11" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G11" s="32" t="s">
-        <v>187</v>
-      </c>
       <c r="H11" s="32" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="I11" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J11" s="32" t="s">
-        <v>187</v>
+        <v>321</v>
       </c>
       <c r="K11" s="32" t="s">
-        <v>280</v>
-      </c>
-      <c r="L11" s="72" t="s">
+        <v>275</v>
+      </c>
+      <c r="L11" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="M11" s="80" t="s">
         <v>277</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="30">
       <c r="A12" s="72" t="s">
+        <v>267</v>
+      </c>
+      <c r="B12" s="72" t="s">
         <v>268</v>
       </c>
-      <c r="B12" s="72" t="s">
-        <v>269</v>
-      </c>
       <c r="C12" s="72" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>282</v>
+        <v>186</v>
       </c>
       <c r="E12" s="32" t="s">
         <v>187</v>
@@ -5205,27 +5195,27 @@
         <v>187</v>
       </c>
       <c r="K12" s="32" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="L12" s="72" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="30">
       <c r="A13" s="72" t="s">
+        <v>267</v>
+      </c>
+      <c r="B13" s="72" t="s">
         <v>268</v>
       </c>
-      <c r="B13" s="72" t="s">
-        <v>269</v>
-      </c>
       <c r="C13" s="72" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="E13" s="32" t="s">
         <v>187</v>
@@ -5246,39 +5236,39 @@
         <v>187</v>
       </c>
       <c r="K13" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="L13" s="72" t="s">
+        <v>276</v>
+      </c>
+      <c r="M13" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="L13" s="72" t="s">
-        <v>277</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="30">
       <c r="A14" s="72" t="s">
-        <v>294</v>
+        <v>267</v>
       </c>
       <c r="B14" s="72" t="s">
-        <v>296</v>
+        <v>268</v>
       </c>
       <c r="C14" s="72" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>291</v>
-      </c>
-      <c r="E14" s="71" t="s">
-        <v>241</v>
+        <v>285</v>
+      </c>
+      <c r="E14" s="32" t="s">
+        <v>187</v>
       </c>
       <c r="F14" s="32" t="s">
-        <v>275</v>
+        <v>187</v>
       </c>
       <c r="G14" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="H14" s="71" t="s">
-        <v>178</v>
+      <c r="H14" s="32" t="s">
+        <v>187</v>
       </c>
       <c r="I14" s="32" t="s">
         <v>22</v>
@@ -5286,32 +5276,34 @@
       <c r="J14" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="K14" s="32"/>
-      <c r="L14" s="32" t="s">
-        <v>277</v>
+      <c r="K14" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="L14" s="72" t="s">
+        <v>276</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="45">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="30">
       <c r="A15" s="72" t="s">
+        <v>293</v>
+      </c>
+      <c r="B15" s="72" t="s">
         <v>295</v>
       </c>
-      <c r="B15" s="72" t="s">
-        <v>297</v>
-      </c>
       <c r="C15" s="72" t="s">
-        <v>292</v>
+        <v>264</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E15" s="71" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G15" s="32" t="s">
         <v>187</v>
@@ -5325,32 +5317,32 @@
       <c r="J15" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="K15" s="1"/>
+      <c r="K15" s="32"/>
       <c r="L15" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="M15" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="M15" s="9" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="30">
-      <c r="A16" s="77" t="s">
-        <v>298</v>
-      </c>
-      <c r="B16" s="77" t="s">
-        <v>299</v>
+    </row>
+    <row r="16" spans="1:13" ht="45">
+      <c r="A16" s="72" t="s">
+        <v>294</v>
+      </c>
+      <c r="B16" s="72" t="s">
+        <v>296</v>
       </c>
       <c r="C16" s="72" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>189</v>
+        <v>292</v>
       </c>
       <c r="E16" s="71" t="s">
-        <v>241</v>
-      </c>
-      <c r="F16" s="71" t="s">
-        <v>275</v>
+        <v>240</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>274</v>
       </c>
       <c r="G16" s="32" t="s">
         <v>187</v>
@@ -5364,40 +5356,38 @@
       <c r="J16" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="K16" s="32" t="s">
-        <v>304</v>
-      </c>
+      <c r="K16" s="1"/>
       <c r="L16" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="M16" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="M16" s="9" t="s">
-        <v>278</v>
-      </c>
     </row>
     <row r="17" spans="1:13" ht="30">
-      <c r="A17" s="72" t="s">
-        <v>295</v>
-      </c>
-      <c r="B17" s="72" t="s">
-        <v>309</v>
+      <c r="A17" s="77" t="s">
+        <v>297</v>
+      </c>
+      <c r="B17" s="77" t="s">
+        <v>298</v>
       </c>
       <c r="C17" s="72" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>282</v>
-      </c>
-      <c r="E17" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F17" s="32" t="s">
-        <v>187</v>
+        <v>188</v>
+      </c>
+      <c r="E17" s="71" t="s">
+        <v>240</v>
+      </c>
+      <c r="F17" s="71" t="s">
+        <v>274</v>
       </c>
       <c r="G17" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="H17" s="32" t="s">
-        <v>187</v>
+      <c r="H17" s="71" t="s">
+        <v>178</v>
       </c>
       <c r="I17" s="32" t="s">
         <v>22</v>
@@ -5406,27 +5396,27 @@
         <v>187</v>
       </c>
       <c r="K17" s="32" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="L17" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="M17" s="9" t="s">
         <v>277</v>
-      </c>
-      <c r="M17" s="9" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="30">
       <c r="A18" s="72" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B18" s="72" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C18" s="72" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="E18" s="32" t="s">
         <v>187</v>
@@ -5447,13 +5437,13 @@
         <v>187</v>
       </c>
       <c r="K18" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="L18" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="M18" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="L18" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="M18" s="9" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="30">
@@ -5461,218 +5451,218 @@
         <v>294</v>
       </c>
       <c r="B19" s="72" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C19" s="72" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D19" s="32" t="s">
+        <v>285</v>
+      </c>
+      <c r="E19" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G19" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H19" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I19" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K19" s="32" t="s">
         <v>282</v>
       </c>
-      <c r="E19" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F19" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G19" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H19" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="I19" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J19" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K19" s="32" t="s">
-        <v>283</v>
-      </c>
       <c r="L19" s="32" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="M19" s="9" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="30">
       <c r="A20" s="72" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B20" s="72" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C20" s="72" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D20" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="E20" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G20" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H20" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I20" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K20" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="L20" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="30">
+      <c r="A21" s="72" t="s">
+        <v>293</v>
+      </c>
+      <c r="B21" s="72" t="s">
+        <v>309</v>
+      </c>
+      <c r="C21" s="72" t="s">
+        <v>307</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>285</v>
+      </c>
+      <c r="E21" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F21" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G21" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H21" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I21" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K21" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="L21" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="M21" s="9" t="s">
         <v>286</v>
-      </c>
-      <c r="E20" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F20" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G20" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H20" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="I20" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J20" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K20" s="32" t="s">
-        <v>283</v>
-      </c>
-      <c r="L20" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="M20" s="9" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="30">
-      <c r="A21" s="77" t="s">
-        <v>298</v>
-      </c>
-      <c r="B21" s="77" t="s">
-        <v>300</v>
-      </c>
-      <c r="C21" s="72" t="s">
-        <v>301</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>282</v>
-      </c>
-      <c r="E21" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F21" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G21" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H21" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="I21" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J21" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K21" s="32" t="s">
-        <v>283</v>
-      </c>
-      <c r="L21" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="M21" s="9" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="30">
       <c r="A22" s="77" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B22" s="77" t="s">
+        <v>299</v>
+      </c>
+      <c r="C22" s="72" t="s">
         <v>300</v>
       </c>
-      <c r="C22" s="72" t="s">
-        <v>302</v>
-      </c>
       <c r="D22" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="E22" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F22" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G22" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H22" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I22" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K22" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="L22" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="30">
+      <c r="A23" s="77" t="s">
+        <v>297</v>
+      </c>
+      <c r="B23" s="77" t="s">
+        <v>299</v>
+      </c>
+      <c r="C23" s="72" t="s">
+        <v>301</v>
+      </c>
+      <c r="D23" s="32" t="s">
+        <v>285</v>
+      </c>
+      <c r="E23" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F23" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G23" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H23" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I23" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K23" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="L23" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="M23" s="9" t="s">
         <v>286</v>
-      </c>
-      <c r="E22" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F22" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G22" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H22" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="I22" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J22" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K22" s="32" t="s">
-        <v>283</v>
-      </c>
-      <c r="L22" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="M22" s="9" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="30">
-      <c r="A23" s="72" t="s">
-        <v>319</v>
-      </c>
-      <c r="B23" s="72" t="s">
-        <v>320</v>
-      </c>
-      <c r="C23" s="72" t="s">
-        <v>313</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>186</v>
-      </c>
-      <c r="E23" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F23" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G23" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H23" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="I23" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J23" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K23" s="32" t="s">
-        <v>280</v>
-      </c>
-      <c r="L23" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="M23" s="9" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="30">
       <c r="A24" s="72" t="s">
+        <v>318</v>
+      </c>
+      <c r="B24" s="72" t="s">
         <v>319</v>
       </c>
-      <c r="B24" s="72" t="s">
-        <v>320</v>
-      </c>
       <c r="C24" s="72" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D24" s="32" t="s">
-        <v>282</v>
+        <v>186</v>
       </c>
       <c r="E24" s="32" t="s">
         <v>187</v>
@@ -5693,99 +5683,140 @@
         <v>187</v>
       </c>
       <c r="K24" s="32" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="L24" s="32" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="M24" s="9" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="30">
       <c r="A25" s="72" t="s">
+        <v>318</v>
+      </c>
+      <c r="B25" s="72" t="s">
         <v>319</v>
       </c>
-      <c r="B25" s="72" t="s">
-        <v>320</v>
-      </c>
       <c r="C25" s="72" t="s">
+        <v>313</v>
+      </c>
+      <c r="D25" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="E25" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F25" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G25" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H25" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I25" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K25" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="L25" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="30">
+      <c r="A26" s="72" t="s">
+        <v>318</v>
+      </c>
+      <c r="B26" s="72" t="s">
+        <v>319</v>
+      </c>
+      <c r="C26" s="72" t="s">
+        <v>314</v>
+      </c>
+      <c r="D26" s="32" t="s">
+        <v>285</v>
+      </c>
+      <c r="E26" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F26" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G26" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H26" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I26" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K26" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="L26" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="M26" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="72" t="s">
+        <v>318</v>
+      </c>
+      <c r="B27" s="72" t="s">
+        <v>319</v>
+      </c>
+      <c r="C27" s="72" t="s">
         <v>315</v>
       </c>
-      <c r="D25" s="32" t="s">
-        <v>286</v>
-      </c>
-      <c r="E25" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F25" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G25" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H25" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="I25" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J25" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K25" s="32" t="s">
-        <v>283</v>
-      </c>
-      <c r="L25" s="32" t="s">
+      <c r="D27" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="E27" s="71" t="s">
+        <v>241</v>
+      </c>
+      <c r="F27" s="71" t="s">
+        <v>274</v>
+      </c>
+      <c r="G27" s="71" t="s">
+        <v>186</v>
+      </c>
+      <c r="H27" s="71" t="s">
+        <v>178</v>
+      </c>
+      <c r="I27" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" s="32" t="s">
+        <v>316</v>
+      </c>
+      <c r="K27" s="32" t="s">
+        <v>317</v>
+      </c>
+      <c r="L27" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="M27" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="M25" s="9" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="72" t="s">
-        <v>319</v>
-      </c>
-      <c r="B26" s="72" t="s">
-        <v>320</v>
-      </c>
-      <c r="C26" s="72" t="s">
-        <v>316</v>
-      </c>
-      <c r="D26" s="32" t="s">
-        <v>189</v>
-      </c>
-      <c r="E26" s="71" t="s">
-        <v>242</v>
-      </c>
-      <c r="F26" s="71" t="s">
-        <v>275</v>
-      </c>
-      <c r="G26" s="71" t="s">
-        <v>186</v>
-      </c>
-      <c r="H26" s="71" t="s">
-        <v>178</v>
-      </c>
-      <c r="I26" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J26" s="32" t="s">
-        <v>317</v>
-      </c>
-      <c r="K26" s="32" t="s">
-        <v>318</v>
-      </c>
-      <c r="L26" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="M26" s="9" t="s">
-        <v>278</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M26" xr:uid="{14526625-C6E6-4A6B-94C7-2E3FA4EA86BF}"/>
+  <autoFilter ref="A1:M27" xr:uid="{14526625-C6E6-4A6B-94C7-2E3FA4EA86BF}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/mapping/field_mapping.xlsx
+++ b/mapping/field_mapping.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Water collectives\WHS Assessment\auto gen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{840EA080-84ED-4D09-B28E-9E0F334193B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{862DD315-4053-4314-8CB1-521F1BA14AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B03A0D84-276C-499F-A511-71567CA886FB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{B03A0D84-276C-499F-A511-71567CA886FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Repeat Mapping" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Repeat Mapping'!$A$1:$M$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Repeat Mapping'!$A$1:$M$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="325">
   <si>
     <t>Sl.No</t>
   </si>
@@ -631,9 +631,6 @@
     <t>None</t>
   </si>
   <si>
-    <t>length_canal_guidewall_height_increase</t>
-  </si>
-  <si>
     <t>Repeat Path</t>
   </si>
   <si>
@@ -1028,6 +1025,15 @@
   </si>
   <si>
     <t>Right → E40</t>
+  </si>
+  <si>
+    <t>canal_guidewall_height_increase_side</t>
+  </si>
+  <si>
+    <t>length_canal_guidewall_height_increase_right</t>
+  </si>
+  <si>
+    <t>length_canal_guidewall_height_increase_left</t>
   </si>
 </sst>
 </file>
@@ -2515,7 +2521,7 @@
         <v>11</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D22" s="18" t="s">
         <v>31</v>
@@ -2547,7 +2553,7 @@
         <v>11</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D23" s="18" t="s">
         <v>32</v>
@@ -2605,7 +2611,7 @@
         <v>11</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D25" s="66" t="s">
         <v>148</v>
@@ -2667,7 +2673,7 @@
         <v>11</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D27" s="18" t="s">
         <v>34</v>
@@ -2727,7 +2733,7 @@
         <v>11</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D29" s="18" t="s">
         <v>154</v>
@@ -2759,7 +2765,7 @@
         <v>11</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D30" s="18" t="s">
         <v>157</v>
@@ -2791,7 +2797,7 @@
         <v>11</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D31" s="47" t="s">
         <v>158</v>
@@ -2823,7 +2829,7 @@
         <v>11</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D32" s="47" t="s">
         <v>162</v>
@@ -2855,7 +2861,7 @@
         <v>11</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D33" s="47" t="s">
         <v>163</v>
@@ -2887,7 +2893,7 @@
         <v>11</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D34" s="18" t="s">
         <v>39</v>
@@ -2919,7 +2925,7 @@
         <v>11</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D35" s="52" t="s">
         <v>81</v>
@@ -2951,7 +2957,7 @@
         <v>11</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D36" s="18" t="s">
         <v>41</v>
@@ -2983,7 +2989,7 @@
         <v>11</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D37" s="18" t="s">
         <v>42</v>
@@ -3015,7 +3021,7 @@
         <v>11</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D38" s="18" t="s">
         <v>43</v>
@@ -3047,7 +3053,7 @@
         <v>11</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D39" s="18" t="s">
         <v>44</v>
@@ -3079,7 +3085,7 @@
         <v>11</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D40" s="25" t="s">
         <v>170</v>
@@ -3088,7 +3094,7 @@
         <v>29</v>
       </c>
       <c r="F40" s="69" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>22</v>
@@ -3111,7 +3117,7 @@
         <v>11</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D41" s="25" t="s">
         <v>171</v>
@@ -3120,7 +3126,7 @@
         <v>29</v>
       </c>
       <c r="F41" s="69" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G41" s="16" t="s">
         <v>22</v>
@@ -3143,7 +3149,7 @@
         <v>11</v>
       </c>
       <c r="C42" s="55" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D42" s="23" t="s">
         <v>47</v>
@@ -3173,7 +3179,7 @@
         <v>11</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D43" s="22" t="s">
         <v>48</v>
@@ -3201,7 +3207,7 @@
         <v>11</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D44" s="18" t="s">
         <v>162</v>
@@ -3233,7 +3239,7 @@
         <v>11</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D45" s="18" t="s">
         <v>163</v>
@@ -3265,7 +3271,7 @@
         <v>11</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D46" s="18" t="s">
         <v>39</v>
@@ -3297,7 +3303,7 @@
         <v>11</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D47" s="18" t="s">
         <v>40</v>
@@ -3329,7 +3335,7 @@
         <v>11</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D48" s="18" t="s">
         <v>41</v>
@@ -3361,7 +3367,7 @@
         <v>11</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D49" s="18" t="s">
         <v>42</v>
@@ -3393,7 +3399,7 @@
         <v>11</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D50" s="25" t="s">
         <v>45</v>
@@ -3402,7 +3408,7 @@
         <v>29</v>
       </c>
       <c r="F50" s="69" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>22</v>
@@ -3425,7 +3431,7 @@
         <v>11</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D51" s="25" t="s">
         <v>46</v>
@@ -3434,7 +3440,7 @@
         <v>29</v>
       </c>
       <c r="F51" s="69" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>22</v>
@@ -3457,7 +3463,7 @@
         <v>11</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D52" s="23" t="s">
         <v>47</v>
@@ -3485,7 +3491,7 @@
         <v>11</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D53" s="22" t="s">
         <v>49</v>
@@ -3513,7 +3519,7 @@
         <v>11</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D54" s="18" t="s">
         <v>36</v>
@@ -3545,7 +3551,7 @@
         <v>11</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D55" s="18" t="s">
         <v>37</v>
@@ -3577,7 +3583,7 @@
         <v>11</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D56" s="18" t="s">
         <v>38</v>
@@ -3609,7 +3615,7 @@
         <v>11</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D57" s="18" t="s">
         <v>50</v>
@@ -3641,7 +3647,7 @@
         <v>11</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D58" s="18" t="s">
         <v>51</v>
@@ -3673,7 +3679,7 @@
         <v>11</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D59" s="18" t="s">
         <v>39</v>
@@ -3705,7 +3711,7 @@
         <v>11</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D60" s="18" t="s">
         <v>52</v>
@@ -3737,7 +3743,7 @@
         <v>11</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D61" s="18" t="s">
         <v>53</v>
@@ -3746,7 +3752,7 @@
         <v>29</v>
       </c>
       <c r="F61" s="70" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>22</v>
@@ -3769,7 +3775,7 @@
         <v>11</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D62" s="18" t="s">
         <v>54</v>
@@ -3778,7 +3784,7 @@
         <v>29</v>
       </c>
       <c r="F62" s="70" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>22</v>
@@ -3801,7 +3807,7 @@
         <v>11</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D63" s="18" t="s">
         <v>55</v>
@@ -3833,7 +3839,7 @@
         <v>11</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D64" s="25" t="s">
         <v>45</v>
@@ -3842,7 +3848,7 @@
         <v>29</v>
       </c>
       <c r="F64" s="69" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>22</v>
@@ -3865,7 +3871,7 @@
         <v>11</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D65" s="25" t="s">
         <v>46</v>
@@ -3874,7 +3880,7 @@
         <v>29</v>
       </c>
       <c r="F65" s="69" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>22</v>
@@ -3897,7 +3903,7 @@
         <v>11</v>
       </c>
       <c r="C66" s="17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D66" s="23" t="s">
         <v>47</v>
@@ -3925,7 +3931,7 @@
         <v>11</v>
       </c>
       <c r="C67" s="17" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D67" s="22" t="s">
         <v>56</v>
@@ -3953,7 +3959,7 @@
         <v>11</v>
       </c>
       <c r="C68" s="17" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D68" s="18" t="s">
         <v>57</v>
@@ -3985,7 +3991,7 @@
         <v>11</v>
       </c>
       <c r="C69" s="17" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D69" s="18" t="s">
         <v>58</v>
@@ -4017,7 +4023,7 @@
         <v>11</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D70" s="18" t="s">
         <v>59</v>
@@ -4026,7 +4032,7 @@
         <v>29</v>
       </c>
       <c r="F70" s="70" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>22</v>
@@ -4049,7 +4055,7 @@
         <v>11</v>
       </c>
       <c r="C71" s="17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D71" s="18" t="s">
         <v>60</v>
@@ -4058,7 +4064,7 @@
         <v>29</v>
       </c>
       <c r="F71" s="58" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>22</v>
@@ -4081,7 +4087,7 @@
         <v>11</v>
       </c>
       <c r="C72" s="17" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D72" s="28" t="s">
         <v>61</v>
@@ -4109,7 +4115,7 @@
         <v>11</v>
       </c>
       <c r="C73" s="17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D73" s="18" t="s">
         <v>62</v>
@@ -4141,7 +4147,7 @@
         <v>11</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D74" s="23" t="s">
         <v>63</v>
@@ -4169,7 +4175,7 @@
         <v>11</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D75" s="22" t="s">
         <v>64</v>
@@ -4197,7 +4203,7 @@
         <v>11</v>
       </c>
       <c r="C76" s="17" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D76" s="30" t="s">
         <v>65</v>
@@ -4229,7 +4235,7 @@
         <v>11</v>
       </c>
       <c r="C77" s="17" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D77" s="18" t="s">
         <v>66</v>
@@ -4261,7 +4267,7 @@
         <v>11</v>
       </c>
       <c r="C78" s="17" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D78" s="18" t="s">
         <v>67</v>
@@ -4293,7 +4299,7 @@
         <v>11</v>
       </c>
       <c r="C79" s="17" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D79" s="18" t="s">
         <v>68</v>
@@ -4325,7 +4331,7 @@
         <v>11</v>
       </c>
       <c r="C80" s="17" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D80" s="18" t="s">
         <v>69</v>
@@ -4357,7 +4363,7 @@
         <v>11</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D81" s="31" t="s">
         <v>70</v>
@@ -4389,7 +4395,7 @@
         <v>11</v>
       </c>
       <c r="C82" s="17" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D82" s="18" t="s">
         <v>71</v>
@@ -4421,7 +4427,7 @@
         <v>11</v>
       </c>
       <c r="C83" s="17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D83" s="18" t="s">
         <v>72</v>
@@ -4453,7 +4459,7 @@
         <v>11</v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D84" s="18" t="s">
         <v>73</v>
@@ -4485,7 +4491,7 @@
         <v>11</v>
       </c>
       <c r="C85" s="17" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D85" s="31" t="s">
         <v>74</v>
@@ -4517,7 +4523,7 @@
         <v>11</v>
       </c>
       <c r="C86" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D86" s="18" t="s">
         <v>67</v>
@@ -4549,7 +4555,7 @@
         <v>11</v>
       </c>
       <c r="C87" s="17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D87" s="18" t="s">
         <v>75</v>
@@ -4581,7 +4587,7 @@
         <v>11</v>
       </c>
       <c r="C88" s="17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D88" s="18" t="s">
         <v>76</v>
@@ -4613,7 +4619,7 @@
         <v>11</v>
       </c>
       <c r="C89" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D89" s="31" t="s">
         <v>77</v>
@@ -4645,7 +4651,7 @@
         <v>11</v>
       </c>
       <c r="C90" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D90" s="18" t="s">
         <v>78</v>
@@ -4677,7 +4683,7 @@
         <v>11</v>
       </c>
       <c r="C91" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D91" s="18" t="s">
         <v>79</v>
@@ -4710,7 +4716,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14526625-C6E6-4A6B-94C7-2E3FA4EA86BF}">
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
@@ -4733,7 +4739,7 @@
         <v>174</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>5</v>
@@ -4763,10 +4769,10 @@
         <v>177</v>
       </c>
       <c r="L1" s="71" t="s">
+        <v>271</v>
+      </c>
+      <c r="M1" s="9" t="s">
         <v>272</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="30">
@@ -4774,40 +4780,40 @@
         <v>184</v>
       </c>
       <c r="B2" s="72" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C2" s="72" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D2" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F2" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G2" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H2" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I2" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K2" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="E2" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F2" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G2" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H2" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="I2" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K2" s="32" t="s">
+      <c r="L2" s="72" t="s">
+        <v>275</v>
+      </c>
+      <c r="M2" s="9" t="s">
         <v>282</v>
-      </c>
-      <c r="L2" s="72" t="s">
-        <v>276</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="30">
@@ -4815,40 +4821,40 @@
         <v>184</v>
       </c>
       <c r="B3" s="72" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C3" s="72" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D3" s="32" t="s">
+        <v>284</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H3" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I3" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K3" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="L3" s="72" t="s">
+        <v>275</v>
+      </c>
+      <c r="M3" s="9" t="s">
         <v>285</v>
-      </c>
-      <c r="E3" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F3" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G3" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H3" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="I3" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K3" s="32" t="s">
-        <v>282</v>
-      </c>
-      <c r="L3" s="72" t="s">
-        <v>276</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="8" customFormat="1">
@@ -4856,7 +4862,7 @@
         <v>184</v>
       </c>
       <c r="B4" s="78" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C4" s="74" t="s">
         <v>185</v>
@@ -4882,10 +4888,10 @@
       <c r="J4" s="73"/>
       <c r="K4" s="73"/>
       <c r="L4" s="75" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M4" s="79" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="8" customFormat="1">
@@ -4893,19 +4899,19 @@
         <v>184</v>
       </c>
       <c r="B5" s="78" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C5" s="74" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D5" s="75" t="s">
         <v>188</v>
       </c>
       <c r="E5" s="75" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F5" s="73" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G5" s="75" t="s">
         <v>186</v>
@@ -4919,10 +4925,10 @@
       <c r="J5" s="73"/>
       <c r="K5" s="73"/>
       <c r="L5" s="75" t="s">
+        <v>275</v>
+      </c>
+      <c r="M5" s="79" t="s">
         <v>276</v>
-      </c>
-      <c r="M5" s="79" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="8" customFormat="1">
@@ -4930,19 +4936,19 @@
         <v>184</v>
       </c>
       <c r="B6" s="78" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C6" s="74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D6" s="75" t="s">
         <v>188</v>
       </c>
       <c r="E6" s="75" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F6" s="73" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G6" s="75" t="s">
         <v>186</v>
@@ -4956,307 +4962,303 @@
       <c r="J6" s="73"/>
       <c r="K6" s="73"/>
       <c r="L6" s="75" t="s">
+        <v>275</v>
+      </c>
+      <c r="M6" s="79" t="s">
         <v>276</v>
       </c>
-      <c r="M6" s="79" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="30">
+    </row>
+    <row r="7" spans="1:13" s="8" customFormat="1" ht="30">
       <c r="A7" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="B7" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="B7" s="32" t="s">
-        <v>194</v>
-      </c>
-      <c r="C7" s="72" t="s">
-        <v>190</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>188</v>
+      <c r="C7" s="74" t="s">
+        <v>322</v>
+      </c>
+      <c r="D7" s="75" t="s">
+        <v>186</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>233</v>
-      </c>
-      <c r="F7" s="73" t="s">
-        <v>274</v>
+        <v>187</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>187</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="I7" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J7" s="32" t="s">
-        <v>266</v>
-      </c>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="26" t="s">
-        <v>277</v>
+        <v>187</v>
+      </c>
+      <c r="K7" s="32" t="s">
+        <v>278</v>
+      </c>
+      <c r="L7" s="72" t="s">
+        <v>275</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="30">
       <c r="A8" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="B8" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="B8" s="32" t="s">
-        <v>194</v>
-      </c>
       <c r="C8" s="72" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>281</v>
-      </c>
-      <c r="E8" s="73" t="s">
-        <v>187</v>
+        <v>188</v>
+      </c>
+      <c r="E8" s="32" t="s">
+        <v>232</v>
       </c>
       <c r="F8" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="G8" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="H8" s="73" t="s">
-        <v>187</v>
+        <v>273</v>
+      </c>
+      <c r="G8" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="H8" s="32" t="s">
+        <v>178</v>
       </c>
       <c r="I8" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="J8" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="K8" s="32" t="s">
-        <v>282</v>
-      </c>
-      <c r="L8" s="32" t="s">
+      <c r="J8" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="26" t="s">
         <v>276</v>
-      </c>
-      <c r="M8" s="26" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="30">
       <c r="A9" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="B9" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="B9" s="32" t="s">
-        <v>194</v>
-      </c>
       <c r="C9" s="72" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="D9" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="E9" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="F9" s="73" t="s">
+        <v>273</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="H9" s="32" t="s">
+        <v>178</v>
+      </c>
+      <c r="I9" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="26" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="30">
+      <c r="A10" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C10" s="72" t="s">
+        <v>309</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="E10" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="F10" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="G10" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="H10" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="I10" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="K10" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="L10" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="M10" s="26" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="30">
+      <c r="A11" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="C11" s="72" t="s">
+        <v>310</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>284</v>
+      </c>
+      <c r="E11" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="F11" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="G11" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="H11" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="I11" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="K11" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="L11" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="M11" s="26" t="s">
         <v>285</v>
       </c>
-      <c r="E9" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="F9" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="G9" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="H9" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="I9" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="K9" s="32" t="s">
-        <v>282</v>
-      </c>
-      <c r="L9" s="32" t="s">
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="72" t="s">
+        <v>266</v>
+      </c>
+      <c r="B12" s="72" t="s">
+        <v>267</v>
+      </c>
+      <c r="C12" s="72" t="s">
+        <v>268</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="G12" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="H12" s="32" t="s">
+        <v>178</v>
+      </c>
+      <c r="I12" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="32" t="s">
+        <v>321</v>
+      </c>
+      <c r="K12" s="32" t="s">
+        <v>274</v>
+      </c>
+      <c r="L12" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="M12" s="80" t="s">
         <v>276</v>
       </c>
-      <c r="M9" s="26" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="72" t="s">
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="72" t="s">
+        <v>266</v>
+      </c>
+      <c r="B13" s="72" t="s">
         <v>267</v>
       </c>
-      <c r="B10" s="72" t="s">
-        <v>268</v>
-      </c>
-      <c r="C10" s="72" t="s">
-        <v>269</v>
-      </c>
-      <c r="D10" s="32" t="s">
+      <c r="C13" s="72" t="s">
+        <v>319</v>
+      </c>
+      <c r="D13" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E13" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F13" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="G13" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="H13" s="32" t="s">
+        <v>178</v>
+      </c>
+      <c r="I13" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="32" t="s">
+        <v>320</v>
+      </c>
+      <c r="K13" s="32" t="s">
         <v>274</v>
       </c>
-      <c r="G10" s="32" t="s">
-        <v>186</v>
-      </c>
-      <c r="H10" s="32" t="s">
-        <v>178</v>
-      </c>
-      <c r="I10" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="32" t="s">
-        <v>322</v>
-      </c>
-      <c r="K10" s="32" t="s">
+      <c r="L13" s="32" t="s">
         <v>275</v>
       </c>
-      <c r="L10" s="32" t="s">
+      <c r="M13" s="80" t="s">
         <v>276</v>
-      </c>
-      <c r="M10" s="80" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="72" t="s">
-        <v>267</v>
-      </c>
-      <c r="B11" s="72" t="s">
-        <v>268</v>
-      </c>
-      <c r="C11" s="72" t="s">
-        <v>320</v>
-      </c>
-      <c r="D11" s="32" t="s">
-        <v>188</v>
-      </c>
-      <c r="E11" s="32" t="s">
-        <v>232</v>
-      </c>
-      <c r="F11" s="32" t="s">
-        <v>274</v>
-      </c>
-      <c r="G11" s="32" t="s">
-        <v>186</v>
-      </c>
-      <c r="H11" s="32" t="s">
-        <v>178</v>
-      </c>
-      <c r="I11" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="32" t="s">
-        <v>321</v>
-      </c>
-      <c r="K11" s="32" t="s">
-        <v>275</v>
-      </c>
-      <c r="L11" s="32" t="s">
-        <v>276</v>
-      </c>
-      <c r="M11" s="80" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="30">
-      <c r="A12" s="72" t="s">
-        <v>267</v>
-      </c>
-      <c r="B12" s="72" t="s">
-        <v>268</v>
-      </c>
-      <c r="C12" s="72" t="s">
-        <v>278</v>
-      </c>
-      <c r="D12" s="32" t="s">
-        <v>186</v>
-      </c>
-      <c r="E12" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F12" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G12" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H12" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="I12" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K12" s="32" t="s">
-        <v>279</v>
-      </c>
-      <c r="L12" s="72" t="s">
-        <v>276</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="30">
-      <c r="A13" s="72" t="s">
-        <v>267</v>
-      </c>
-      <c r="B13" s="72" t="s">
-        <v>268</v>
-      </c>
-      <c r="C13" s="72" t="s">
-        <v>280</v>
-      </c>
-      <c r="D13" s="32" t="s">
-        <v>281</v>
-      </c>
-      <c r="E13" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F13" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G13" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H13" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="I13" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K13" s="32" t="s">
-        <v>282</v>
-      </c>
-      <c r="L13" s="72" t="s">
-        <v>276</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="30">
       <c r="A14" s="72" t="s">
+        <v>266</v>
+      </c>
+      <c r="B14" s="72" t="s">
         <v>267</v>
       </c>
-      <c r="B14" s="72" t="s">
-        <v>268</v>
-      </c>
       <c r="C14" s="72" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>285</v>
+        <v>186</v>
       </c>
       <c r="E14" s="32" t="s">
         <v>187</v>
@@ -5277,39 +5279,39 @@
         <v>187</v>
       </c>
       <c r="K14" s="32" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="L14" s="72" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="30">
       <c r="A15" s="72" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="B15" s="72" t="s">
-        <v>295</v>
+        <v>267</v>
       </c>
       <c r="C15" s="72" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>290</v>
-      </c>
-      <c r="E15" s="71" t="s">
-        <v>240</v>
+        <v>280</v>
+      </c>
+      <c r="E15" s="32" t="s">
+        <v>187</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>274</v>
+        <v>187</v>
       </c>
       <c r="G15" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="H15" s="71" t="s">
-        <v>178</v>
+      <c r="H15" s="32" t="s">
+        <v>187</v>
       </c>
       <c r="I15" s="32" t="s">
         <v>22</v>
@@ -5317,71 +5319,75 @@
       <c r="J15" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="K15" s="32"/>
-      <c r="L15" s="32" t="s">
-        <v>276</v>
+      <c r="K15" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="L15" s="72" t="s">
+        <v>275</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="45">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="30">
       <c r="A16" s="72" t="s">
+        <v>266</v>
+      </c>
+      <c r="B16" s="72" t="s">
+        <v>267</v>
+      </c>
+      <c r="C16" s="72" t="s">
+        <v>283</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>284</v>
+      </c>
+      <c r="E16" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G16" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H16" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I16" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K16" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="L16" s="72" t="s">
+        <v>275</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="30">
+      <c r="A17" s="72" t="s">
+        <v>292</v>
+      </c>
+      <c r="B17" s="72" t="s">
         <v>294</v>
       </c>
-      <c r="B16" s="72" t="s">
-        <v>296</v>
-      </c>
-      <c r="C16" s="72" t="s">
-        <v>291</v>
-      </c>
-      <c r="D16" s="32" t="s">
-        <v>292</v>
-      </c>
-      <c r="E16" s="71" t="s">
-        <v>240</v>
-      </c>
-      <c r="F16" s="32" t="s">
-        <v>274</v>
-      </c>
-      <c r="G16" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H16" s="71" t="s">
-        <v>178</v>
-      </c>
-      <c r="I16" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J16" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K16" s="1"/>
-      <c r="L16" s="32" t="s">
-        <v>276</v>
-      </c>
-      <c r="M16" s="9" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="30">
-      <c r="A17" s="77" t="s">
-        <v>297</v>
-      </c>
-      <c r="B17" s="77" t="s">
-        <v>298</v>
-      </c>
       <c r="C17" s="72" t="s">
-        <v>302</v>
+        <v>263</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>188</v>
+        <v>289</v>
       </c>
       <c r="E17" s="71" t="s">
-        <v>240</v>
-      </c>
-      <c r="F17" s="71" t="s">
-        <v>274</v>
+        <v>239</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>273</v>
       </c>
       <c r="G17" s="32" t="s">
         <v>187</v>
@@ -5395,40 +5401,38 @@
       <c r="J17" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="K17" s="32" t="s">
-        <v>303</v>
-      </c>
+      <c r="K17" s="32"/>
       <c r="L17" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="M17" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="M17" s="9" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="30">
+    </row>
+    <row r="18" spans="1:13" ht="45">
       <c r="A18" s="72" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B18" s="72" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="C18" s="72" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>281</v>
-      </c>
-      <c r="E18" s="32" t="s">
-        <v>187</v>
+        <v>291</v>
+      </c>
+      <c r="E18" s="71" t="s">
+        <v>239</v>
       </c>
       <c r="F18" s="32" t="s">
-        <v>187</v>
+        <v>273</v>
       </c>
       <c r="G18" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="H18" s="32" t="s">
-        <v>187</v>
+      <c r="H18" s="71" t="s">
+        <v>178</v>
       </c>
       <c r="I18" s="32" t="s">
         <v>22</v>
@@ -5436,40 +5440,38 @@
       <c r="J18" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="K18" s="32" t="s">
-        <v>282</v>
-      </c>
+      <c r="K18" s="1"/>
       <c r="L18" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="M18" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="M18" s="9" t="s">
-        <v>283</v>
-      </c>
     </row>
     <row r="19" spans="1:13" ht="30">
-      <c r="A19" s="72" t="s">
-        <v>294</v>
-      </c>
-      <c r="B19" s="72" t="s">
-        <v>308</v>
+      <c r="A19" s="77" t="s">
+        <v>296</v>
+      </c>
+      <c r="B19" s="77" t="s">
+        <v>297</v>
       </c>
       <c r="C19" s="72" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>285</v>
-      </c>
-      <c r="E19" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F19" s="32" t="s">
-        <v>187</v>
+        <v>188</v>
+      </c>
+      <c r="E19" s="71" t="s">
+        <v>239</v>
+      </c>
+      <c r="F19" s="71" t="s">
+        <v>273</v>
       </c>
       <c r="G19" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="H19" s="32" t="s">
-        <v>187</v>
+      <c r="H19" s="71" t="s">
+        <v>178</v>
       </c>
       <c r="I19" s="32" t="s">
         <v>22</v>
@@ -5478,13 +5480,13 @@
         <v>187</v>
       </c>
       <c r="K19" s="32" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="L19" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="M19" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="M19" s="9" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="30">
@@ -5492,40 +5494,40 @@
         <v>293</v>
       </c>
       <c r="B20" s="72" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C20" s="72" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D20" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="E20" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G20" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H20" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I20" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K20" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="E20" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F20" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G20" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H20" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="I20" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J20" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K20" s="32" t="s">
+      <c r="L20" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="M20" s="9" t="s">
         <v>282</v>
-      </c>
-      <c r="L20" s="32" t="s">
-        <v>276</v>
-      </c>
-      <c r="M20" s="9" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="30">
@@ -5533,290 +5535,372 @@
         <v>293</v>
       </c>
       <c r="B21" s="72" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C21" s="72" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D21" s="32" t="s">
+        <v>284</v>
+      </c>
+      <c r="E21" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F21" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G21" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H21" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I21" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K21" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="L21" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="M21" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="E21" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F21" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G21" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H21" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="I21" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J21" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K21" s="32" t="s">
+    </row>
+    <row r="22" spans="1:13" ht="30">
+      <c r="A22" s="72" t="s">
+        <v>292</v>
+      </c>
+      <c r="B22" s="72" t="s">
+        <v>308</v>
+      </c>
+      <c r="C22" s="72" t="s">
+        <v>305</v>
+      </c>
+      <c r="D22" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="E22" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F22" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G22" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H22" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I22" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K22" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="L22" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="M22" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="L21" s="32" t="s">
-        <v>276</v>
-      </c>
-      <c r="M21" s="9" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="30">
-      <c r="A22" s="77" t="s">
-        <v>297</v>
-      </c>
-      <c r="B22" s="77" t="s">
+    </row>
+    <row r="23" spans="1:13" ht="30">
+      <c r="A23" s="72" t="s">
+        <v>292</v>
+      </c>
+      <c r="B23" s="72" t="s">
+        <v>308</v>
+      </c>
+      <c r="C23" s="72" t="s">
+        <v>306</v>
+      </c>
+      <c r="D23" s="32" t="s">
+        <v>284</v>
+      </c>
+      <c r="E23" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F23" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G23" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H23" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I23" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K23" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="L23" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="M23" s="9" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="30">
+      <c r="A24" s="77" t="s">
+        <v>296</v>
+      </c>
+      <c r="B24" s="77" t="s">
+        <v>298</v>
+      </c>
+      <c r="C24" s="72" t="s">
         <v>299</v>
       </c>
-      <c r="C22" s="72" t="s">
+      <c r="D24" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="E24" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F24" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G24" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H24" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I24" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K24" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="L24" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="M24" s="9" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="30">
+      <c r="A25" s="77" t="s">
+        <v>296</v>
+      </c>
+      <c r="B25" s="77" t="s">
+        <v>298</v>
+      </c>
+      <c r="C25" s="72" t="s">
         <v>300</v>
       </c>
-      <c r="D22" s="32" t="s">
+      <c r="D25" s="32" t="s">
+        <v>284</v>
+      </c>
+      <c r="E25" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F25" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G25" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H25" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I25" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K25" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="E22" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F22" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G22" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H22" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="I22" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J22" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K22" s="32" t="s">
-        <v>282</v>
-      </c>
-      <c r="L22" s="32" t="s">
-        <v>276</v>
-      </c>
-      <c r="M22" s="9" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="30">
-      <c r="A23" s="77" t="s">
-        <v>297</v>
-      </c>
-      <c r="B23" s="77" t="s">
-        <v>299</v>
-      </c>
-      <c r="C23" s="72" t="s">
-        <v>301</v>
-      </c>
-      <c r="D23" s="32" t="s">
+      <c r="L25" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="M25" s="9" t="s">
         <v>285</v>
-      </c>
-      <c r="E23" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F23" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G23" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H23" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="I23" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J23" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K23" s="32" t="s">
-        <v>282</v>
-      </c>
-      <c r="L23" s="32" t="s">
-        <v>276</v>
-      </c>
-      <c r="M23" s="9" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="30">
-      <c r="A24" s="72" t="s">
-        <v>318</v>
-      </c>
-      <c r="B24" s="72" t="s">
-        <v>319</v>
-      </c>
-      <c r="C24" s="72" t="s">
-        <v>312</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>186</v>
-      </c>
-      <c r="E24" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F24" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G24" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H24" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="I24" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J24" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K24" s="32" t="s">
-        <v>279</v>
-      </c>
-      <c r="L24" s="32" t="s">
-        <v>276</v>
-      </c>
-      <c r="M24" s="9" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="30">
-      <c r="A25" s="72" t="s">
-        <v>318</v>
-      </c>
-      <c r="B25" s="72" t="s">
-        <v>319</v>
-      </c>
-      <c r="C25" s="72" t="s">
-        <v>313</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>281</v>
-      </c>
-      <c r="E25" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F25" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G25" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H25" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="I25" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J25" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K25" s="32" t="s">
-        <v>282</v>
-      </c>
-      <c r="L25" s="32" t="s">
-        <v>276</v>
-      </c>
-      <c r="M25" s="9" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="30">
       <c r="A26" s="72" t="s">
+        <v>317</v>
+      </c>
+      <c r="B26" s="72" t="s">
         <v>318</v>
       </c>
-      <c r="B26" s="72" t="s">
-        <v>319</v>
-      </c>
       <c r="C26" s="72" t="s">
+        <v>311</v>
+      </c>
+      <c r="D26" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="E26" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F26" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G26" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H26" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I26" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K26" s="32" t="s">
+        <v>278</v>
+      </c>
+      <c r="L26" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="M26" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="30">
+      <c r="A27" s="72" t="s">
+        <v>317</v>
+      </c>
+      <c r="B27" s="72" t="s">
+        <v>318</v>
+      </c>
+      <c r="C27" s="72" t="s">
+        <v>312</v>
+      </c>
+      <c r="D27" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="E27" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F27" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G27" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H27" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I27" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K27" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="L27" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="M27" s="9" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="30">
+      <c r="A28" s="72" t="s">
+        <v>317</v>
+      </c>
+      <c r="B28" s="72" t="s">
+        <v>318</v>
+      </c>
+      <c r="C28" s="72" t="s">
+        <v>313</v>
+      </c>
+      <c r="D28" s="32" t="s">
+        <v>284</v>
+      </c>
+      <c r="E28" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="F28" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="G28" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="H28" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="I28" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J28" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K28" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="L28" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="M28" s="9" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="72" t="s">
+        <v>317</v>
+      </c>
+      <c r="B29" s="72" t="s">
+        <v>318</v>
+      </c>
+      <c r="C29" s="72" t="s">
         <v>314</v>
       </c>
-      <c r="D26" s="32" t="s">
-        <v>285</v>
-      </c>
-      <c r="E26" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F26" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G26" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H26" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="I26" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J26" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K26" s="32" t="s">
-        <v>282</v>
-      </c>
-      <c r="L26" s="32" t="s">
+      <c r="D29" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="E29" s="71" t="s">
+        <v>240</v>
+      </c>
+      <c r="F29" s="71" t="s">
+        <v>273</v>
+      </c>
+      <c r="G29" s="71" t="s">
+        <v>186</v>
+      </c>
+      <c r="H29" s="71" t="s">
+        <v>178</v>
+      </c>
+      <c r="I29" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" s="32" t="s">
+        <v>315</v>
+      </c>
+      <c r="K29" s="32" t="s">
+        <v>316</v>
+      </c>
+      <c r="L29" s="32" t="s">
+        <v>275</v>
+      </c>
+      <c r="M29" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="M26" s="9" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="72" t="s">
-        <v>318</v>
-      </c>
-      <c r="B27" s="72" t="s">
-        <v>319</v>
-      </c>
-      <c r="C27" s="72" t="s">
-        <v>315</v>
-      </c>
-      <c r="D27" s="32" t="s">
-        <v>188</v>
-      </c>
-      <c r="E27" s="71" t="s">
-        <v>241</v>
-      </c>
-      <c r="F27" s="71" t="s">
-        <v>274</v>
-      </c>
-      <c r="G27" s="71" t="s">
-        <v>186</v>
-      </c>
-      <c r="H27" s="71" t="s">
-        <v>178</v>
-      </c>
-      <c r="I27" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J27" s="32" t="s">
-        <v>316</v>
-      </c>
-      <c r="K27" s="32" t="s">
-        <v>317</v>
-      </c>
-      <c r="L27" s="32" t="s">
-        <v>276</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>277</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M27" xr:uid="{14526625-C6E6-4A6B-94C7-2E3FA4EA86BF}"/>
+  <autoFilter ref="A1:M29" xr:uid="{14526625-C6E6-4A6B-94C7-2E3FA4EA86BF}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/mapping/field_mapping.xlsx
+++ b/mapping/field_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Water collectives\WHS Assessment\auto gen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{862DD315-4053-4314-8CB1-521F1BA14AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5ADBF90-792D-4CC4-9454-C30D6377E569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{B03A0D84-276C-499F-A511-71567CA886FB}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Repeat Mapping'!$A$1:$M$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$92</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="326">
   <si>
     <t>Sl.No</t>
   </si>
@@ -217,18 +217,12 @@
     <t>Left side Abutment wall</t>
   </si>
   <si>
-    <t>Left side dam gudie wall</t>
-  </si>
-  <si>
     <t>Right side Diverson Canal guide walls over the existing bed CC after removing damaged guide walls</t>
   </si>
   <si>
     <t>Left side Diverson Canal guide walls over the existing bed CC after removing damaged guide walls</t>
   </si>
   <si>
-    <t>Increasing height of the guide wall</t>
-  </si>
-  <si>
     <t>CC(1:2:4) for</t>
   </si>
   <si>
@@ -577,9 +571,6 @@
     <t>For R/S New canal-L</t>
   </si>
   <si>
-    <t>cbagw-length_canalbed_guidewall_tobe_replaced</t>
-  </si>
-  <si>
     <t>tr-avg_length_tp</t>
   </si>
   <si>
@@ -1034,6 +1025,18 @@
   </si>
   <si>
     <t>length_canal_guidewall_height_increase_left</t>
+  </si>
+  <si>
+    <t>Left side dam guide wall</t>
+  </si>
+  <si>
+    <t>Increasing height of the guide wall-Right</t>
+  </si>
+  <si>
+    <t>Increasing height of the guide wall-Left</t>
+  </si>
+  <si>
+    <t>H71</t>
   </si>
 </sst>
 </file>
@@ -1280,7 +1283,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1303,11 +1306,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1526,6 +1542,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1841,7 +1878,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BD40E3A-47FB-49F4-898A-F101DAF5E071}">
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:J92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -1884,7 +1921,7 @@
         <v>6</v>
       </c>
       <c r="J1" s="59" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15.75">
@@ -1895,7 +1932,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>8</v>
@@ -1904,7 +1941,7 @@
         <v>13</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>22</v>
@@ -1916,7 +1953,7 @@
         <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.75">
@@ -1927,7 +1964,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D3" s="32" t="s">
         <v>10</v>
@@ -1936,7 +1973,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>22</v>
@@ -1948,7 +1985,7 @@
         <v>9</v>
       </c>
       <c r="J3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75">
@@ -1959,7 +1996,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>14</v>
@@ -1968,7 +2005,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>22</v>
@@ -1980,7 +2017,7 @@
         <v>9</v>
       </c>
       <c r="J4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75">
@@ -1991,7 +2028,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>15</v>
@@ -2000,7 +2037,7 @@
         <v>13</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>22</v>
@@ -2012,7 +2049,7 @@
         <v>9</v>
       </c>
       <c r="J5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.75">
@@ -2023,7 +2060,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>16</v>
@@ -2032,7 +2069,7 @@
         <v>13</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>22</v>
@@ -2044,7 +2081,7 @@
         <v>12</v>
       </c>
       <c r="J6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.75">
@@ -2055,7 +2092,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D7" s="33" t="s">
         <v>17</v>
@@ -2064,7 +2101,7 @@
         <v>13</v>
       </c>
       <c r="F7" s="36" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>22</v>
@@ -2076,7 +2113,7 @@
         <v>12</v>
       </c>
       <c r="J7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.75">
@@ -2087,7 +2124,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>18</v>
@@ -2096,7 +2133,7 @@
         <v>13</v>
       </c>
       <c r="F8" s="76" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>22</v>
@@ -2108,7 +2145,7 @@
         <v>9</v>
       </c>
       <c r="J8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.75">
@@ -2119,7 +2156,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>19</v>
@@ -2136,7 +2173,7 @@
         <v>9</v>
       </c>
       <c r="J9" s="61" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.75">
@@ -2147,16 +2184,16 @@
         <v>7</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E10" s="19" t="s">
         <v>29</v>
       </c>
       <c r="F10" s="65" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>22</v>
@@ -2168,7 +2205,7 @@
         <v>9</v>
       </c>
       <c r="J10" s="61" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15.75">
@@ -2179,7 +2216,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>25</v>
@@ -2198,7 +2235,7 @@
         <v>9</v>
       </c>
       <c r="J11" s="61" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.75">
@@ -2207,16 +2244,16 @@
         <v>7</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F12" s="65" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>22</v>
@@ -2228,7 +2265,7 @@
         <v>9</v>
       </c>
       <c r="J12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15.75">
@@ -2239,7 +2276,7 @@
         <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>27</v>
@@ -2248,7 +2285,7 @@
         <v>13</v>
       </c>
       <c r="F13" s="37" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>22</v>
@@ -2260,7 +2297,7 @@
         <v>9</v>
       </c>
       <c r="J13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15.75">
@@ -2271,16 +2308,16 @@
         <v>7</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F14" s="64" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>22</v>
@@ -2292,7 +2329,7 @@
         <v>9</v>
       </c>
       <c r="J14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15.75">
@@ -2301,16 +2338,16 @@
         <v>7</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F15" s="64" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>22</v>
@@ -2322,7 +2359,7 @@
         <v>9</v>
       </c>
       <c r="J15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="31.5">
@@ -2333,16 +2370,16 @@
         <v>7</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F16" s="64" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>22</v>
@@ -2354,23 +2391,23 @@
         <v>9</v>
       </c>
       <c r="J16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="31.5">
       <c r="A17" s="6"/>
       <c r="B17" s="5"/>
       <c r="C17" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F17" s="64" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>22</v>
@@ -2382,7 +2419,7 @@
         <v>9</v>
       </c>
       <c r="J17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15.75">
@@ -2393,7 +2430,7 @@
         <v>7</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>28</v>
@@ -2402,7 +2439,7 @@
         <v>13</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>22</v>
@@ -2414,7 +2451,7 @@
         <v>9</v>
       </c>
       <c r="J18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="8" customFormat="1" ht="15.75">
@@ -2425,16 +2462,16 @@
         <v>7</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D19" s="62" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F19" s="63" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G19" s="16" t="s">
         <v>22</v>
@@ -2446,7 +2483,7 @@
         <v>9</v>
       </c>
       <c r="J19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="8" customFormat="1" ht="15.75">
@@ -2457,16 +2494,16 @@
         <v>7</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D20" s="62" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F20" s="63" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G20" s="16" t="s">
         <v>22</v>
@@ -2478,7 +2515,7 @@
         <v>9</v>
       </c>
       <c r="J20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15.75">
@@ -2489,7 +2526,7 @@
         <v>7</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D21" s="20" t="s">
         <v>30</v>
@@ -2498,7 +2535,7 @@
         <v>13</v>
       </c>
       <c r="F21" s="36" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G21" s="16" t="s">
         <v>22</v>
@@ -2510,7 +2547,7 @@
         <v>9</v>
       </c>
       <c r="J21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15.75">
@@ -2521,16 +2558,16 @@
         <v>11</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D22" s="18" t="s">
         <v>31</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G22" s="16" t="s">
         <v>22</v>
@@ -2542,7 +2579,7 @@
         <v>9</v>
       </c>
       <c r="J22" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="15.75">
@@ -2553,16 +2590,16 @@
         <v>11</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D23" s="18" t="s">
         <v>32</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F23" s="38" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G23" s="16" t="s">
         <v>22</v>
@@ -2574,7 +2611,7 @@
         <v>9</v>
       </c>
       <c r="J23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="18.75">
@@ -2585,7 +2622,7 @@
         <v>11</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D24" s="22" t="s">
         <v>33</v>
@@ -2602,7 +2639,7 @@
         <v>9</v>
       </c>
       <c r="J24" s="61" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="15.75">
@@ -2611,16 +2648,16 @@
         <v>11</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D25" s="66" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E25" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F25" s="38" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G25" s="16" t="s">
         <v>22</v>
@@ -2632,7 +2669,7 @@
         <v>9</v>
       </c>
       <c r="J25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15.75">
@@ -2641,16 +2678,16 @@
         <v>11</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D26" s="66" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E26" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F26" s="61" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G26" s="16" t="s">
         <v>22</v>
@@ -2662,7 +2699,7 @@
         <v>9</v>
       </c>
       <c r="J26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="31.5">
@@ -2673,7 +2710,7 @@
         <v>11</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D27" s="18" t="s">
         <v>34</v>
@@ -2682,7 +2719,7 @@
         <v>29</v>
       </c>
       <c r="F27" s="39" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G27" s="16" t="s">
         <v>22</v>
@@ -2694,7 +2731,7 @@
         <v>9</v>
       </c>
       <c r="J27" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="18.75">
@@ -2705,7 +2742,7 @@
         <v>11</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D28" s="22" t="s">
         <v>35</v>
@@ -2722,7 +2759,7 @@
         <v>9</v>
       </c>
       <c r="J28" s="61" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="15.75">
@@ -2733,16 +2770,16 @@
         <v>11</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E29" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F29" s="40" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G29" s="16" t="s">
         <v>22</v>
@@ -2754,7 +2791,7 @@
         <v>9</v>
       </c>
       <c r="J29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="15.75">
@@ -2765,16 +2802,16 @@
         <v>11</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E30" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F30" s="40" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G30" s="16" t="s">
         <v>22</v>
@@ -2786,7 +2823,7 @@
         <v>9</v>
       </c>
       <c r="J30" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="15.75">
@@ -2797,16 +2834,16 @@
         <v>11</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D31" s="47" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E31" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F31" s="40" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G31" s="16" t="s">
         <v>22</v>
@@ -2818,7 +2855,7 @@
         <v>9</v>
       </c>
       <c r="J31" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="15.75">
@@ -2829,16 +2866,16 @@
         <v>11</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D32" s="47" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E32" s="48" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="49" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G32" s="50" t="s">
         <v>22</v>
@@ -2850,7 +2887,7 @@
         <v>9</v>
       </c>
       <c r="J32" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="15.75">
@@ -2861,16 +2898,16 @@
         <v>11</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D33" s="47" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E33" s="48" t="s">
         <v>29</v>
       </c>
       <c r="F33" s="67" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G33" s="50" t="s">
         <v>22</v>
@@ -2882,7 +2919,7 @@
         <v>9</v>
       </c>
       <c r="J33" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="15.75">
@@ -2893,7 +2930,7 @@
         <v>11</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D34" s="18" t="s">
         <v>39</v>
@@ -2902,7 +2939,7 @@
         <v>29</v>
       </c>
       <c r="F34" s="49" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G34" s="16" t="s">
         <v>22</v>
@@ -2914,7 +2951,7 @@
         <v>9</v>
       </c>
       <c r="J34" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="15.75">
@@ -2925,16 +2962,16 @@
         <v>11</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D35" s="52" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E35" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F35" s="49" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G35" s="16" t="s">
         <v>22</v>
@@ -2946,7 +2983,7 @@
         <v>9</v>
       </c>
       <c r="J35" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="15.75">
@@ -2957,7 +2994,7 @@
         <v>11</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D36" s="18" t="s">
         <v>41</v>
@@ -2966,7 +3003,7 @@
         <v>29</v>
       </c>
       <c r="F36" s="40" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G36" s="16" t="s">
         <v>22</v>
@@ -2978,7 +3015,7 @@
         <v>9</v>
       </c>
       <c r="J36" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="15.75">
@@ -2989,7 +3026,7 @@
         <v>11</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D37" s="18" t="s">
         <v>42</v>
@@ -2998,7 +3035,7 @@
         <v>29</v>
       </c>
       <c r="F37" s="49" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G37" s="16" t="s">
         <v>22</v>
@@ -3010,7 +3047,7 @@
         <v>9</v>
       </c>
       <c r="J37" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="15.75">
@@ -3021,7 +3058,7 @@
         <v>11</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D38" s="18" t="s">
         <v>43</v>
@@ -3030,7 +3067,7 @@
         <v>29</v>
       </c>
       <c r="F38" s="51" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G38" s="16" t="s">
         <v>22</v>
@@ -3042,7 +3079,7 @@
         <v>9</v>
       </c>
       <c r="J38" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="15.75">
@@ -3053,7 +3090,7 @@
         <v>11</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D39" s="18" t="s">
         <v>44</v>
@@ -3062,7 +3099,7 @@
         <v>29</v>
       </c>
       <c r="F39" s="51" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G39" s="16" t="s">
         <v>22</v>
@@ -3074,7 +3111,7 @@
         <v>9</v>
       </c>
       <c r="J39" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="15.75">
@@ -3085,16 +3122,16 @@
         <v>11</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E40" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F40" s="69" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>22</v>
@@ -3106,7 +3143,7 @@
         <v>9</v>
       </c>
       <c r="J40" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="15.75">
@@ -3117,16 +3154,16 @@
         <v>11</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E41" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F41" s="69" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="G41" s="16" t="s">
         <v>22</v>
@@ -3138,7 +3175,7 @@
         <v>9</v>
       </c>
       <c r="J41" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="57" customFormat="1" ht="15.75">
@@ -3149,7 +3186,7 @@
         <v>11</v>
       </c>
       <c r="C42" s="55" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D42" s="23" t="s">
         <v>47</v>
@@ -3168,7 +3205,7 @@
         <v>26</v>
       </c>
       <c r="J42" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="18.75">
@@ -3179,7 +3216,7 @@
         <v>11</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D43" s="22" t="s">
         <v>48</v>
@@ -3196,7 +3233,7 @@
         <v>9</v>
       </c>
       <c r="J43" s="61" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="15.75">
@@ -3207,16 +3244,16 @@
         <v>11</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D44" s="18" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E44" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F44" s="49" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>22</v>
@@ -3228,7 +3265,7 @@
         <v>26</v>
       </c>
       <c r="J44" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="15.75">
@@ -3239,16 +3276,16 @@
         <v>11</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E45" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F45" s="67" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>22</v>
@@ -3260,7 +3297,7 @@
         <v>26</v>
       </c>
       <c r="J45" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="15.75">
@@ -3271,7 +3308,7 @@
         <v>11</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D46" s="18" t="s">
         <v>39</v>
@@ -3280,7 +3317,7 @@
         <v>29</v>
       </c>
       <c r="F46" s="49" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G46" s="16" t="s">
         <v>22</v>
@@ -3292,7 +3329,7 @@
         <v>9</v>
       </c>
       <c r="J46" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="15.75">
@@ -3303,7 +3340,7 @@
         <v>11</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D47" s="18" t="s">
         <v>40</v>
@@ -3312,7 +3349,7 @@
         <v>29</v>
       </c>
       <c r="F47" s="49" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>22</v>
@@ -3324,7 +3361,7 @@
         <v>26</v>
       </c>
       <c r="J47" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="15.75">
@@ -3335,7 +3372,7 @@
         <v>11</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D48" s="18" t="s">
         <v>41</v>
@@ -3344,7 +3381,7 @@
         <v>29</v>
       </c>
       <c r="F48" s="40" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>22</v>
@@ -3356,7 +3393,7 @@
         <v>26</v>
       </c>
       <c r="J48" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="15.75">
@@ -3367,7 +3404,7 @@
         <v>11</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D49" s="18" t="s">
         <v>42</v>
@@ -3376,7 +3413,7 @@
         <v>29</v>
       </c>
       <c r="F49" s="49" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>22</v>
@@ -3388,7 +3425,7 @@
         <v>26</v>
       </c>
       <c r="J49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="15.75">
@@ -3399,7 +3436,7 @@
         <v>11</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D50" s="25" t="s">
         <v>45</v>
@@ -3408,7 +3445,7 @@
         <v>29</v>
       </c>
       <c r="F50" s="69" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>22</v>
@@ -3420,7 +3457,7 @@
         <v>26</v>
       </c>
       <c r="J50" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="15.75">
@@ -3431,7 +3468,7 @@
         <v>11</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D51" s="25" t="s">
         <v>46</v>
@@ -3440,7 +3477,7 @@
         <v>29</v>
       </c>
       <c r="F51" s="69" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>22</v>
@@ -3452,7 +3489,7 @@
         <v>26</v>
       </c>
       <c r="J51" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" spans="1:10" s="57" customFormat="1" ht="15.75">
@@ -3463,7 +3500,7 @@
         <v>11</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D52" s="23" t="s">
         <v>47</v>
@@ -3480,7 +3517,7 @@
         <v>26</v>
       </c>
       <c r="J52" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="18.75">
@@ -3491,7 +3528,7 @@
         <v>11</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D53" s="22" t="s">
         <v>49</v>
@@ -3508,7 +3545,7 @@
         <v>9</v>
       </c>
       <c r="J53" s="61" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="15.75">
@@ -3519,7 +3556,7 @@
         <v>11</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D54" s="18" t="s">
         <v>36</v>
@@ -3528,7 +3565,7 @@
         <v>29</v>
       </c>
       <c r="F54" s="40" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>22</v>
@@ -3540,7 +3577,7 @@
         <v>26</v>
       </c>
       <c r="J54" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="15.75">
@@ -3551,7 +3588,7 @@
         <v>11</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D55" s="18" t="s">
         <v>37</v>
@@ -3560,7 +3597,7 @@
         <v>29</v>
       </c>
       <c r="F55" s="40" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>22</v>
@@ -3572,7 +3609,7 @@
         <v>26</v>
       </c>
       <c r="J55" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="15.75">
@@ -3583,7 +3620,7 @@
         <v>11</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D56" s="18" t="s">
         <v>38</v>
@@ -3592,7 +3629,7 @@
         <v>29</v>
       </c>
       <c r="F56" s="40" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>22</v>
@@ -3604,7 +3641,7 @@
         <v>26</v>
       </c>
       <c r="J56" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="15.75">
@@ -3615,7 +3652,7 @@
         <v>11</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D57" s="18" t="s">
         <v>50</v>
@@ -3624,7 +3661,7 @@
         <v>29</v>
       </c>
       <c r="F57" s="49" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>22</v>
@@ -3636,7 +3673,7 @@
         <v>26</v>
       </c>
       <c r="J57" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="15.75">
@@ -3647,7 +3684,7 @@
         <v>11</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D58" s="18" t="s">
         <v>51</v>
@@ -3656,7 +3693,7 @@
         <v>29</v>
       </c>
       <c r="F58" s="67" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>22</v>
@@ -3668,7 +3705,7 @@
         <v>26</v>
       </c>
       <c r="J58" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="15.75">
@@ -3679,7 +3716,7 @@
         <v>11</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D59" s="18" t="s">
         <v>39</v>
@@ -3688,7 +3725,7 @@
         <v>29</v>
       </c>
       <c r="F59" s="49" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G59" s="16" t="s">
         <v>22</v>
@@ -3700,7 +3737,7 @@
         <v>9</v>
       </c>
       <c r="J59" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="15.75">
@@ -3711,16 +3748,16 @@
         <v>11</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>52</v>
+        <v>322</v>
       </c>
       <c r="E60" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F60" s="49" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>22</v>
@@ -3732,7 +3769,7 @@
         <v>26</v>
       </c>
       <c r="J60" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="54" customHeight="1">
@@ -3743,16 +3780,16 @@
         <v>11</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E61" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F61" s="70" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>22</v>
@@ -3764,7 +3801,7 @@
         <v>26</v>
       </c>
       <c r="J61" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="51" customHeight="1">
@@ -3775,16 +3812,16 @@
         <v>11</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E62" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F62" s="70" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>22</v>
@@ -3796,7 +3833,7 @@
         <v>26</v>
       </c>
       <c r="J62" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="15.75">
@@ -3807,16 +3844,16 @@
         <v>11</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>55</v>
+        <v>323</v>
       </c>
       <c r="E63" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F63" s="40" t="s">
-        <v>172</v>
+        <v>320</v>
       </c>
       <c r="G63" s="16" t="s">
         <v>22</v>
@@ -3828,59 +3865,59 @@
         <v>9</v>
       </c>
       <c r="J63" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="15.75">
       <c r="A64" s="6">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="D64" s="25" t="s">
-        <v>45</v>
+        <v>230</v>
+      </c>
+      <c r="D64" s="18" t="s">
+        <v>324</v>
       </c>
       <c r="E64" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F64" s="69" t="s">
-        <v>262</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I64" s="26" t="s">
-        <v>26</v>
+      <c r="F64" s="72" t="s">
+        <v>321</v>
+      </c>
+      <c r="G64" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H64" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I64" s="17" t="s">
+        <v>9</v>
       </c>
       <c r="J64" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="15.75">
       <c r="A65" s="6">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D65" s="25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E65" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F65" s="69" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>22</v>
@@ -3892,115 +3929,115 @@
         <v>26</v>
       </c>
       <c r="J65" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" s="57" customFormat="1" ht="15.75">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="15.75">
       <c r="A66" s="6">
+        <v>61</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="D66" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="E66" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="F66" s="69" t="s">
+        <v>258</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I66" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J66" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" s="57" customFormat="1" ht="15.75">
+      <c r="A67" s="6">
         <v>62</v>
       </c>
-      <c r="B66" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="C66" s="17" t="s">
-        <v>235</v>
-      </c>
-      <c r="D66" s="23" t="s">
+      <c r="B67" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="D67" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="E66" s="24"/>
-      <c r="F66" s="41"/>
-      <c r="G66" s="56" t="s">
-        <v>22</v>
-      </c>
-      <c r="H66" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="I66" s="53" t="s">
+      <c r="E67" s="24"/>
+      <c r="F67" s="41"/>
+      <c r="G67" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="H67" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="I67" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="J66" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="18.75">
-      <c r="A67" s="6">
+      <c r="J67" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="18.75">
+      <c r="A68" s="6">
         <v>63</v>
       </c>
-      <c r="B67" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C67" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="D67" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="E67" s="27"/>
-      <c r="F67" s="43"/>
-      <c r="G67" s="2" t="s">
+      <c r="B68" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="D68" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="E68" s="27"/>
+      <c r="F68" s="43"/>
+      <c r="G68" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H67" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I67" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="J67" s="61" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="15.75">
-      <c r="A68" s="6">
-        <v>64</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C68" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="D68" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="E68" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="F68" s="40" t="s">
-        <v>166</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I68" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="J68" t="s">
-        <v>83</v>
+      <c r="H68" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I68" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J68" s="61" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="15.75">
       <c r="A69" s="6">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="17" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D69" s="18" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E69" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F69" s="49" t="s">
-        <v>167</v>
+      <c r="F69" s="40" t="s">
+        <v>164</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>22</v>
@@ -4009,30 +4046,30 @@
         <v>23</v>
       </c>
       <c r="I69" s="26" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J69" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" ht="31.5">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="15.75">
       <c r="A70" s="6">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D70" s="18" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E70" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F70" s="70" t="s">
-        <v>288</v>
+      <c r="F70" s="49" t="s">
+        <v>165</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>22</v>
@@ -4044,27 +4081,27 @@
         <v>26</v>
       </c>
       <c r="J70" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="31.5">
       <c r="A71" s="6">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="17" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D71" s="18" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E71" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F71" s="58" t="s">
-        <v>264</v>
+      <c r="F71" s="70" t="s">
+        <v>285</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>22</v>
@@ -4076,175 +4113,175 @@
         <v>26</v>
       </c>
       <c r="J71" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" ht="37.5">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="31.5">
       <c r="A72" s="6">
+        <v>67</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="D72" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="E72" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="F72" s="58" t="s">
+        <v>261</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I72" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J72" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="37.5">
+      <c r="A73" s="6">
         <v>68</v>
       </c>
-      <c r="B72" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C72" s="17" t="s">
+      <c r="B73" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="D73" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="E73" s="29"/>
+      <c r="F73" s="44"/>
+      <c r="G73" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H73" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I73" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J73" s="61" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="15.75">
+      <c r="A74" s="6">
+        <v>69</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="D74" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E74" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="F74" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I74" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="J74" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" s="57" customFormat="1" ht="15.75">
+      <c r="A75" s="6">
+        <v>70</v>
+      </c>
+      <c r="B75" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="D72" s="28" t="s">
+      <c r="D75" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="E72" s="29"/>
-      <c r="F72" s="44"/>
-      <c r="G72" s="2" t="s">
+      <c r="E75" s="24"/>
+      <c r="F75" s="41"/>
+      <c r="G75" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="H75" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="I75" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="J75" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="18.75">
+      <c r="A76" s="6">
+        <v>71</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="D76" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="E76" s="27"/>
+      <c r="F76" s="43"/>
+      <c r="G76" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H72" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I72" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="J72" s="61" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" ht="15.75">
-      <c r="A73" s="6">
-        <v>69</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C73" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="D73" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="E73" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="F73" s="40" t="s">
-        <v>173</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H73" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I73" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="J73" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" s="57" customFormat="1" ht="15.75">
-      <c r="A74" s="6">
-        <v>70</v>
-      </c>
-      <c r="B74" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="C74" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="D74" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="E74" s="24"/>
-      <c r="F74" s="41"/>
-      <c r="G74" s="56" t="s">
-        <v>22</v>
-      </c>
-      <c r="H74" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="I74" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="J74" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" ht="18.75">
-      <c r="A75" s="6">
-        <v>71</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C75" s="17" t="s">
-        <v>244</v>
-      </c>
-      <c r="D75" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="E75" s="27"/>
-      <c r="F75" s="43"/>
-      <c r="G75" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H75" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I75" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="J75" s="61" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" ht="15.75">
-      <c r="A76" s="6">
-        <v>72</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C76" s="17" t="s">
-        <v>245</v>
-      </c>
-      <c r="D76" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="E76" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="F76" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="G76" s="16" t="s">
-        <v>22</v>
-      </c>
       <c r="H76" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I76" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="J76" t="s">
-        <v>83</v>
+      <c r="J76" s="61" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="15.75">
       <c r="A77" s="6">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="D77" s="18" t="s">
-        <v>66</v>
+        <v>243</v>
+      </c>
+      <c r="D77" s="30" t="s">
+        <v>63</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="F77" s="40" t="s">
-        <v>98</v>
+        <v>78</v>
+      </c>
+      <c r="F77" s="45" t="s">
+        <v>95</v>
       </c>
       <c r="G77" s="16" t="s">
         <v>22</v>
@@ -4256,27 +4293,27 @@
         <v>9</v>
       </c>
       <c r="J77" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="15.75">
       <c r="A78" s="6">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="17" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D78" s="18" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F78" s="40" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G78" s="16" t="s">
         <v>22</v>
@@ -4288,93 +4325,93 @@
         <v>9</v>
       </c>
       <c r="J78" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="15.75">
       <c r="A79" s="6">
+        <v>74</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="D79" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="E79" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F79" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="G79" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H79" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I79" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J79" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="15.75">
+      <c r="A80" s="6">
         <v>75</v>
       </c>
-      <c r="B79" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C79" s="17" t="s">
-        <v>248</v>
-      </c>
-      <c r="D79" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="E79" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="F79" s="40" t="s">
-        <v>100</v>
-      </c>
-      <c r="G79" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H79" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I79" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="J79" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" ht="31.5">
-      <c r="A80" s="6">
+      <c r="B80" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C80" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="D80" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E80" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F80" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="G80" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H80" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I80" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J80" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="31.5">
+      <c r="A81" s="6">
         <v>76</v>
       </c>
-      <c r="B80" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C80" s="17" t="s">
-        <v>249</v>
-      </c>
-      <c r="D80" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="E80" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="F80" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G80" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H80" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I80" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="J80" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" ht="15.75">
-      <c r="A81" s="6">
-        <v>77</v>
-      </c>
       <c r="B81" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>250</v>
-      </c>
-      <c r="D81" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="E81" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="F81" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="G81" s="60" t="s">
+        <v>247</v>
+      </c>
+      <c r="D81" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E81" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F81" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="G81" s="16" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="16" t="s">
@@ -4384,91 +4421,91 @@
         <v>9</v>
       </c>
       <c r="J81" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="15.75">
       <c r="A82" s="6">
+        <v>77</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="D82" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E82" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="B82" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C82" s="17" t="s">
-        <v>251</v>
-      </c>
-      <c r="D82" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="E82" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="F82" s="40" t="s">
-        <v>133</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I82" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="J82" s="61" t="s">
-        <v>84</v>
+      <c r="F82" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="G82" s="60" t="s">
+        <v>22</v>
+      </c>
+      <c r="H82" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I82" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J82" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="15.75">
       <c r="A83" s="6">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C83" s="17" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D83" s="18" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="F83" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="G83" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H83" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I83" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="J83" t="s">
-        <v>83</v>
+        <v>78</v>
+      </c>
+      <c r="F83" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I83" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="J83" s="61" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="15.75">
       <c r="A84" s="6">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D84" s="18" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F84" s="39" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G84" s="16" t="s">
         <v>22</v>
@@ -4480,29 +4517,29 @@
         <v>9</v>
       </c>
       <c r="J84" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="15.75">
       <c r="A85" s="6">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C85" s="17" t="s">
-        <v>254</v>
-      </c>
-      <c r="D85" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="E85" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="F85" s="43" t="s">
-        <v>104</v>
-      </c>
-      <c r="G85" s="60" t="s">
+        <v>251</v>
+      </c>
+      <c r="D85" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E85" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F85" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="G85" s="16" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="16" t="s">
@@ -4512,199 +4549,231 @@
         <v>9</v>
       </c>
       <c r="J85" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="15.75">
       <c r="A86" s="6">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C86" s="17" t="s">
-        <v>255</v>
-      </c>
-      <c r="D86" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="E86" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F86" s="40" t="s">
-        <v>132</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I86" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="J86" s="61" t="s">
-        <v>84</v>
+        <v>252</v>
+      </c>
+      <c r="D86" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="E86" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F86" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="G86" s="60" t="s">
+        <v>22</v>
+      </c>
+      <c r="H86" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I86" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J86" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="15.75">
       <c r="A87" s="6">
+        <v>82</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="D87" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="E87" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F87" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I87" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="J87" s="61" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="15.75">
+      <c r="A88" s="81">
         <v>83</v>
       </c>
-      <c r="B87" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C87" s="17" t="s">
-        <v>256</v>
-      </c>
-      <c r="D87" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="E87" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="F87" s="40" t="s">
-        <v>100</v>
-      </c>
-      <c r="G87" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H87" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I87" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="J87" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" ht="15.75">
-      <c r="A88" s="6">
-        <v>84</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C88" s="17" t="s">
-        <v>257</v>
-      </c>
-      <c r="D88" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="E88" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="F88" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G88" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H88" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I88" s="17" t="s">
+      <c r="B88" s="82" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88" s="83" t="s">
+        <v>254</v>
+      </c>
+      <c r="D88" s="84" t="s">
+        <v>73</v>
+      </c>
+      <c r="E88" s="85" t="s">
+        <v>78</v>
+      </c>
+      <c r="F88" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="G88" s="87" t="s">
+        <v>22</v>
+      </c>
+      <c r="H88" s="87" t="s">
+        <v>23</v>
+      </c>
+      <c r="I88" s="83" t="s">
         <v>9</v>
       </c>
       <c r="J88" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="15.75">
       <c r="A89" s="6">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C89" s="17" t="s">
-        <v>258</v>
-      </c>
-      <c r="D89" s="31" t="s">
-        <v>77</v>
-      </c>
-      <c r="E89" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="F89" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H89" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I89" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="J89" t="s">
-        <v>83</v>
+        <v>255</v>
+      </c>
+      <c r="D89" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E89" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F89" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="G89" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H89" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I89" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="15.75">
       <c r="A90" s="6">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C90" s="17" t="s">
-        <v>259</v>
-      </c>
-      <c r="D90" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="D90" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="E90" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="E90" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="F90" s="42" t="s">
-        <v>105</v>
-      </c>
-      <c r="G90" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H90" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I90" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="J90" t="s">
-        <v>83</v>
+      <c r="F90" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I90" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="15.75">
       <c r="A91" s="6">
+        <v>86</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C91" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="D91" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F91" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="G91" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H91" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I91" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="15.75">
+      <c r="A92" s="6">
         <v>87</v>
       </c>
-      <c r="B91" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C91" s="17" t="s">
-        <v>260</v>
-      </c>
-      <c r="D91" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="E91" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="F91" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="G91" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H91" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I91" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="J91" t="s">
-        <v>83</v>
+      <c r="B92" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C92" s="26" t="s">
+        <v>325</v>
+      </c>
+      <c r="D92" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="E92" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F92" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="G92" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H92" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I92" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -4736,151 +4805,151 @@
   <sheetData>
     <row r="1" spans="1:13" s="68" customFormat="1" ht="30">
       <c r="A1" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>5</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E1" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="G1" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>183</v>
-      </c>
       <c r="K1" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L1" s="71" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="30">
       <c r="A2" s="72" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B2" s="72" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C2" s="72" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G2" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I2" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J2" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K2" s="32" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L2" s="72" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="30">
       <c r="A3" s="72" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B3" s="72" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C3" s="72" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G3" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H3" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I3" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J3" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K3" s="32" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L3" s="72" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="8" customFormat="1">
       <c r="A4" s="73" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B4" s="78" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C4" s="74" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D4" s="75" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E4" s="75" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F4" s="75" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G4" s="75" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H4" s="75" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I4" s="73" t="s">
         <v>22</v>
@@ -4888,36 +4957,36 @@
       <c r="J4" s="73"/>
       <c r="K4" s="73"/>
       <c r="L4" s="75" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M4" s="79" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="8" customFormat="1">
       <c r="A5" s="73" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B5" s="78" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C5" s="74" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D5" s="75" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E5" s="75" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F5" s="73" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G5" s="75" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="H5" s="75" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I5" s="73" t="s">
         <v>22</v>
@@ -4925,36 +4994,36 @@
       <c r="J5" s="73"/>
       <c r="K5" s="73"/>
       <c r="L5" s="75" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M5" s="79" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="8" customFormat="1">
       <c r="A6" s="73" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B6" s="78" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C6" s="74" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D6" s="75" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E6" s="75" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F6" s="73" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G6" s="75" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="H6" s="75" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I6" s="73" t="s">
         <v>22</v>
@@ -4962,941 +5031,941 @@
       <c r="J6" s="73"/>
       <c r="K6" s="73"/>
       <c r="L6" s="75" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M6" s="79" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="8" customFormat="1" ht="30">
       <c r="A7" s="32" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C7" s="74" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D7" s="75" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F7" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I7" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J7" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K7" s="32" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="L7" s="72" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="30">
       <c r="A8" s="32" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C8" s="72" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F8" s="73" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G8" s="32" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H8" s="32" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I8" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="26" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="30">
       <c r="A9" s="32" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C9" s="72" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F9" s="73" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G9" s="32" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H9" s="32" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I9" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="26" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="30">
       <c r="A10" s="32" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C10" s="72" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E10" s="73" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F10" s="73" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G10" s="73" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H10" s="73" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I10" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J10" s="73" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K10" s="32" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L10" s="32" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M10" s="26" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="30">
       <c r="A11" s="32" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C11" s="72" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E11" s="73" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F11" s="73" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G11" s="73" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H11" s="73" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I11" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J11" s="73" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K11" s="32" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L11" s="32" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M11" s="26" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="72" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B12" s="72" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C12" s="72" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F12" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="G12" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="H12" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="I12" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="32" t="s">
+        <v>318</v>
+      </c>
+      <c r="K12" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="L12" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="M12" s="80" t="s">
         <v>273</v>
-      </c>
-      <c r="G12" s="32" t="s">
-        <v>186</v>
-      </c>
-      <c r="H12" s="32" t="s">
-        <v>178</v>
-      </c>
-      <c r="I12" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" s="32" t="s">
-        <v>321</v>
-      </c>
-      <c r="K12" s="32" t="s">
-        <v>274</v>
-      </c>
-      <c r="L12" s="32" t="s">
-        <v>275</v>
-      </c>
-      <c r="M12" s="80" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="72" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B13" s="72" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C13" s="72" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F13" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="G13" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="H13" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="I13" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="32" t="s">
+        <v>317</v>
+      </c>
+      <c r="K13" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="L13" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="M13" s="80" t="s">
         <v>273</v>
-      </c>
-      <c r="G13" s="32" t="s">
-        <v>186</v>
-      </c>
-      <c r="H13" s="32" t="s">
-        <v>178</v>
-      </c>
-      <c r="I13" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="32" t="s">
-        <v>320</v>
-      </c>
-      <c r="K13" s="32" t="s">
-        <v>274</v>
-      </c>
-      <c r="L13" s="32" t="s">
-        <v>275</v>
-      </c>
-      <c r="M13" s="80" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="30">
       <c r="A14" s="72" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B14" s="72" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C14" s="72" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F14" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G14" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H14" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I14" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J14" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K14" s="32" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="L14" s="72" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="30">
       <c r="A15" s="72" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B15" s="72" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C15" s="72" t="s">
+        <v>276</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="E15" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="G15" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="H15" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="I15" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="K15" s="32" t="s">
+        <v>278</v>
+      </c>
+      <c r="L15" s="72" t="s">
+        <v>272</v>
+      </c>
+      <c r="M15" s="9" t="s">
         <v>279</v>
-      </c>
-      <c r="D15" s="32" t="s">
-        <v>280</v>
-      </c>
-      <c r="E15" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="F15" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="G15" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H15" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="I15" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K15" s="32" t="s">
-        <v>281</v>
-      </c>
-      <c r="L15" s="72" t="s">
-        <v>275</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="30">
       <c r="A16" s="72" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B16" s="72" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C16" s="72" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F16" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G16" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H16" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I16" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J16" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K16" s="32" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L16" s="72" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="30">
       <c r="A17" s="72" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B17" s="72" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C17" s="72" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E17" s="71" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F17" s="32" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G17" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H17" s="71" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I17" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J17" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K17" s="32"/>
       <c r="L17" s="32" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M17" s="9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="45">
       <c r="A18" s="72" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B18" s="72" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C18" s="72" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E18" s="71" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F18" s="32" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G18" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H18" s="71" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I18" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J18" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="32" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M18" s="9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="30">
       <c r="A19" s="77" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B19" s="77" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C19" s="72" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E19" s="71" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F19" s="71" t="s">
+        <v>270</v>
+      </c>
+      <c r="G19" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="H19" s="71" t="s">
+        <v>175</v>
+      </c>
+      <c r="I19" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="K19" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="L19" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="M19" s="9" t="s">
         <v>273</v>
-      </c>
-      <c r="G19" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="H19" s="71" t="s">
-        <v>178</v>
-      </c>
-      <c r="I19" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J19" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K19" s="32" t="s">
-        <v>302</v>
-      </c>
-      <c r="L19" s="32" t="s">
-        <v>275</v>
-      </c>
-      <c r="M19" s="9" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="30">
       <c r="A20" s="72" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B20" s="72" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C20" s="72" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F20" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G20" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H20" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I20" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J20" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K20" s="32" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L20" s="32" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M20" s="9" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="30">
       <c r="A21" s="72" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B21" s="72" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C21" s="72" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D21" s="32" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E21" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F21" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G21" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H21" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I21" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J21" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K21" s="32" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L21" s="32" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="30">
       <c r="A22" s="72" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B22" s="72" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C22" s="72" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D22" s="32" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E22" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F22" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G22" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H22" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I22" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J22" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K22" s="32" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L22" s="32" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M22" s="9" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="30">
       <c r="A23" s="72" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B23" s="72" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C23" s="72" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D23" s="32" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E23" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F23" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G23" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H23" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I23" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J23" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K23" s="32" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L23" s="32" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M23" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="30">
       <c r="A24" s="77" t="s">
+        <v>293</v>
+      </c>
+      <c r="B24" s="77" t="s">
+        <v>295</v>
+      </c>
+      <c r="C24" s="72" t="s">
         <v>296</v>
       </c>
-      <c r="B24" s="77" t="s">
-        <v>298</v>
-      </c>
-      <c r="C24" s="72" t="s">
-        <v>299</v>
-      </c>
       <c r="D24" s="32" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E24" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F24" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G24" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H24" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I24" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J24" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K24" s="32" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L24" s="32" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M24" s="9" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="30">
       <c r="A25" s="77" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B25" s="77" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C25" s="72" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D25" s="32" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F25" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G25" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H25" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I25" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J25" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K25" s="32" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L25" s="32" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M25" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="30">
       <c r="A26" s="72" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B26" s="72" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C26" s="72" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D26" s="32" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F26" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G26" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H26" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I26" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J26" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K26" s="32" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="L26" s="32" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M26" s="9" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="30">
       <c r="A27" s="72" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B27" s="72" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C27" s="72" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D27" s="32" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E27" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F27" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G27" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H27" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I27" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J27" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K27" s="32" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L27" s="32" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M27" s="9" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="30">
       <c r="A28" s="72" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B28" s="72" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C28" s="72" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D28" s="32" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E28" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F28" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G28" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H28" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I28" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J28" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="K28" s="32" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L28" s="32" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M28" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="72" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B29" s="72" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C29" s="72" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E29" s="71" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F29" s="71" t="s">
+        <v>270</v>
+      </c>
+      <c r="G29" s="71" t="s">
+        <v>183</v>
+      </c>
+      <c r="H29" s="71" t="s">
+        <v>175</v>
+      </c>
+      <c r="I29" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" s="32" t="s">
+        <v>312</v>
+      </c>
+      <c r="K29" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="L29" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="M29" s="9" t="s">
         <v>273</v>
-      </c>
-      <c r="G29" s="71" t="s">
-        <v>186</v>
-      </c>
-      <c r="H29" s="71" t="s">
-        <v>178</v>
-      </c>
-      <c r="I29" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J29" s="32" t="s">
-        <v>315</v>
-      </c>
-      <c r="K29" s="32" t="s">
-        <v>316</v>
-      </c>
-      <c r="L29" s="32" t="s">
-        <v>275</v>
-      </c>
-      <c r="M29" s="9" t="s">
-        <v>276</v>
       </c>
     </row>
   </sheetData>

--- a/mapping/field_mapping.xlsx
+++ b/mapping/field_mapping.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Water collectives\WHS Assessment\auto gen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5ADBF90-792D-4CC4-9454-C30D6377E569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD61CA2E-BF4A-4EA4-914C-67029B8245D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{B03A0D84-276C-499F-A511-71567CA886FB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B03A0D84-276C-499F-A511-71567CA886FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Repeat Mapping" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Repeat Mapping'!$A$1:$M$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Repeat Mapping'!$A$1:$M$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$94</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="323">
   <si>
     <t>Sl.No</t>
   </si>
@@ -232,9 +232,6 @@
     <t>Wearing coat over Apron-II</t>
   </si>
   <si>
-    <t>Hunch to arrest the leakages through bed and guidewall joint</t>
-  </si>
-  <si>
     <t>Left side Canal - new bed over the exising bed</t>
   </si>
   <si>
@@ -787,12 +784,6 @@
     <t>E54</t>
   </si>
   <si>
-    <t>H55</t>
-  </si>
-  <si>
-    <t>H56</t>
-  </si>
-  <si>
     <t>H57</t>
   </si>
   <si>
@@ -844,9 +835,6 @@
     <t>gwbjl_-leakage_canal_length_gwbjl_leak1</t>
   </si>
   <si>
-    <t>nboe-length_nboe</t>
-  </si>
-  <si>
     <t>Sum all repeat lengths</t>
   </si>
   <si>
@@ -916,9 +904,6 @@
     <t>ncg_-chainage_ncg_to</t>
   </si>
   <si>
-    <t>gwbjl_-leakage_canal_length_gwbjl_leak1, ltcb_-canal_damaged_length_leak1</t>
-  </si>
-  <si>
     <t>Leakage Canal Length</t>
   </si>
   <si>
@@ -985,30 +970,6 @@
     <t>Canal_guidewall_height_increase_-chainage_canal_guidewall_height_increase_to</t>
   </si>
   <si>
-    <t>nboe_-canal_side</t>
-  </si>
-  <si>
-    <t>nboe_-chainage_from_nboe</t>
-  </si>
-  <si>
-    <t>nboe_-chainage_to_nboe</t>
-  </si>
-  <si>
-    <t>nboe_-length_nboe</t>
-  </si>
-  <si>
-    <t>Sum repeat lengths by side</t>
-  </si>
-  <si>
-    <t>Total NBOE length by side</t>
-  </si>
-  <si>
-    <t>nboe</t>
-  </si>
-  <si>
-    <t>nboe/nboe_</t>
-  </si>
-  <si>
     <t>avg_length_gwl</t>
   </si>
   <si>
@@ -1037,6 +998,36 @@
   </si>
   <si>
     <t>H71</t>
+  </si>
+  <si>
+    <t>Right side Canal - new bed over the exising bed</t>
+  </si>
+  <si>
+    <t>Hunch to arrest the leakages through bed and guidewall joint- Right canal</t>
+  </si>
+  <si>
+    <t>Hunch to arrest the leakages through bed and guidewall joint- Left canal</t>
+  </si>
+  <si>
+    <t>E55</t>
+  </si>
+  <si>
+    <t>E56</t>
+  </si>
+  <si>
+    <t>H72</t>
+  </si>
+  <si>
+    <t>H73</t>
+  </si>
+  <si>
+    <t>ltcb_-canal_side</t>
+  </si>
+  <si>
+    <t>ltcb_-canal_damaged_length_leak2</t>
+  </si>
+  <si>
+    <t>gwbjl_-leakage_canal_length_gwbjl_leak2</t>
   </si>
 </sst>
 </file>
@@ -1323,7 +1314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1484,9 +1475,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1878,7 +1866,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BD40E3A-47FB-49F4-898A-F101DAF5E071}">
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -1920,8 +1908,8 @@
       <c r="I1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="59" t="s">
-        <v>80</v>
+      <c r="J1" s="58" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15.75">
@@ -1932,7 +1920,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D2" s="32" t="s">
         <v>8</v>
@@ -1941,7 +1929,7 @@
         <v>13</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>22</v>
@@ -1953,7 +1941,7 @@
         <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.75">
@@ -1964,7 +1952,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D3" s="32" t="s">
         <v>10</v>
@@ -1973,7 +1961,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>22</v>
@@ -1985,7 +1973,7 @@
         <v>9</v>
       </c>
       <c r="J3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75">
@@ -1996,7 +1984,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>14</v>
@@ -2005,7 +1993,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>22</v>
@@ -2017,7 +2005,7 @@
         <v>9</v>
       </c>
       <c r="J4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75">
@@ -2028,7 +2016,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>15</v>
@@ -2037,7 +2025,7 @@
         <v>13</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>22</v>
@@ -2049,7 +2037,7 @@
         <v>9</v>
       </c>
       <c r="J5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.75">
@@ -2060,7 +2048,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>16</v>
@@ -2069,7 +2057,7 @@
         <v>13</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>22</v>
@@ -2081,7 +2069,7 @@
         <v>12</v>
       </c>
       <c r="J6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.75">
@@ -2092,7 +2080,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D7" s="33" t="s">
         <v>17</v>
@@ -2101,7 +2089,7 @@
         <v>13</v>
       </c>
       <c r="F7" s="36" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>22</v>
@@ -2113,7 +2101,7 @@
         <v>12</v>
       </c>
       <c r="J7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.75">
@@ -2124,7 +2112,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>18</v>
@@ -2132,8 +2120,8 @@
       <c r="E8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="76" t="s">
-        <v>104</v>
+      <c r="F8" s="75" t="s">
+        <v>103</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>22</v>
@@ -2145,7 +2133,7 @@
         <v>9</v>
       </c>
       <c r="J8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.75">
@@ -2156,7 +2144,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>19</v>
@@ -2166,14 +2154,14 @@
       <c r="G9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="60" t="s">
+      <c r="H9" s="59" t="s">
         <v>23</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J9" s="61" t="s">
-        <v>82</v>
+      <c r="J9" s="60" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.75">
@@ -2184,16 +2172,16 @@
         <v>7</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E10" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="65" t="s">
-        <v>135</v>
+      <c r="F10" s="64" t="s">
+        <v>134</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>22</v>
@@ -2204,8 +2192,8 @@
       <c r="I10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J10" s="61" t="s">
-        <v>81</v>
+      <c r="J10" s="60" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15.75">
@@ -2216,7 +2204,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>25</v>
@@ -2234,8 +2222,8 @@
       <c r="I11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J11" s="61" t="s">
-        <v>82</v>
+      <c r="J11" s="60" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.75">
@@ -2244,16 +2232,16 @@
         <v>7</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="65" t="s">
-        <v>137</v>
+      <c r="F12" s="64" t="s">
+        <v>136</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>22</v>
@@ -2265,7 +2253,7 @@
         <v>9</v>
       </c>
       <c r="J12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15.75">
@@ -2276,7 +2264,7 @@
         <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>27</v>
@@ -2285,7 +2273,7 @@
         <v>13</v>
       </c>
       <c r="F13" s="37" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>22</v>
@@ -2297,7 +2285,7 @@
         <v>9</v>
       </c>
       <c r="J13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15.75">
@@ -2308,16 +2296,16 @@
         <v>7</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="64" t="s">
-        <v>140</v>
+      <c r="F14" s="63" t="s">
+        <v>139</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>22</v>
@@ -2329,7 +2317,7 @@
         <v>9</v>
       </c>
       <c r="J14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15.75">
@@ -2338,16 +2326,16 @@
         <v>7</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="64" t="s">
-        <v>90</v>
+      <c r="F15" s="63" t="s">
+        <v>89</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>22</v>
@@ -2359,7 +2347,7 @@
         <v>9</v>
       </c>
       <c r="J15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="31.5">
@@ -2370,16 +2358,16 @@
         <v>7</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="64" t="s">
-        <v>143</v>
+      <c r="F16" s="63" t="s">
+        <v>142</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>22</v>
@@ -2391,23 +2379,23 @@
         <v>9</v>
       </c>
       <c r="J16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="31.5">
       <c r="A17" s="6"/>
       <c r="B17" s="5"/>
       <c r="C17" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="64" t="s">
-        <v>144</v>
+      <c r="F17" s="63" t="s">
+        <v>143</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>22</v>
@@ -2419,7 +2407,7 @@
         <v>9</v>
       </c>
       <c r="J17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15.75">
@@ -2430,7 +2418,7 @@
         <v>7</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>28</v>
@@ -2439,7 +2427,7 @@
         <v>13</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>22</v>
@@ -2451,7 +2439,7 @@
         <v>9</v>
       </c>
       <c r="J18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="8" customFormat="1" ht="15.75">
@@ -2462,16 +2450,16 @@
         <v>7</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="D19" s="62" t="s">
-        <v>126</v>
+        <v>121</v>
+      </c>
+      <c r="D19" s="61" t="s">
+        <v>125</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F19" s="63" t="s">
-        <v>128</v>
+      <c r="F19" s="62" t="s">
+        <v>127</v>
       </c>
       <c r="G19" s="16" t="s">
         <v>22</v>
@@ -2483,7 +2471,7 @@
         <v>9</v>
       </c>
       <c r="J19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="8" customFormat="1" ht="15.75">
@@ -2494,16 +2482,16 @@
         <v>7</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="D20" s="62" t="s">
-        <v>127</v>
+        <v>122</v>
+      </c>
+      <c r="D20" s="61" t="s">
+        <v>126</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F20" s="63" t="s">
-        <v>129</v>
+      <c r="F20" s="62" t="s">
+        <v>128</v>
       </c>
       <c r="G20" s="16" t="s">
         <v>22</v>
@@ -2515,7 +2503,7 @@
         <v>9</v>
       </c>
       <c r="J20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15.75">
@@ -2526,7 +2514,7 @@
         <v>7</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D21" s="20" t="s">
         <v>30</v>
@@ -2535,7 +2523,7 @@
         <v>13</v>
       </c>
       <c r="F21" s="36" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G21" s="16" t="s">
         <v>22</v>
@@ -2547,7 +2535,7 @@
         <v>9</v>
       </c>
       <c r="J21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15.75">
@@ -2558,16 +2546,16 @@
         <v>11</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D22" s="18" t="s">
         <v>31</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G22" s="16" t="s">
         <v>22</v>
@@ -2579,7 +2567,7 @@
         <v>9</v>
       </c>
       <c r="J22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="15.75">
@@ -2590,16 +2578,16 @@
         <v>11</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D23" s="18" t="s">
         <v>32</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F23" s="38" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G23" s="16" t="s">
         <v>22</v>
@@ -2611,7 +2599,7 @@
         <v>9</v>
       </c>
       <c r="J23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="18.75">
@@ -2622,7 +2610,7 @@
         <v>11</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D24" s="22" t="s">
         <v>33</v>
@@ -2638,8 +2626,8 @@
       <c r="I24" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="J24" s="61" t="s">
-        <v>82</v>
+      <c r="J24" s="60" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="15.75">
@@ -2648,16 +2636,16 @@
         <v>11</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="D25" s="66" t="s">
-        <v>146</v>
+        <v>192</v>
+      </c>
+      <c r="D25" s="65" t="s">
+        <v>145</v>
       </c>
       <c r="E25" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F25" s="38" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G25" s="16" t="s">
         <v>22</v>
@@ -2669,7 +2657,7 @@
         <v>9</v>
       </c>
       <c r="J25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15.75">
@@ -2678,16 +2666,16 @@
         <v>11</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="D26" s="66" t="s">
-        <v>147</v>
+        <v>149</v>
+      </c>
+      <c r="D26" s="65" t="s">
+        <v>146</v>
       </c>
       <c r="E26" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F26" s="61" t="s">
-        <v>149</v>
+      <c r="F26" s="60" t="s">
+        <v>148</v>
       </c>
       <c r="G26" s="16" t="s">
         <v>22</v>
@@ -2699,7 +2687,7 @@
         <v>9</v>
       </c>
       <c r="J26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="31.5">
@@ -2710,7 +2698,7 @@
         <v>11</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D27" s="18" t="s">
         <v>34</v>
@@ -2719,7 +2707,7 @@
         <v>29</v>
       </c>
       <c r="F27" s="39" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G27" s="16" t="s">
         <v>22</v>
@@ -2731,7 +2719,7 @@
         <v>9</v>
       </c>
       <c r="J27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="18.75">
@@ -2742,7 +2730,7 @@
         <v>11</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D28" s="22" t="s">
         <v>35</v>
@@ -2758,8 +2746,8 @@
       <c r="I28" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="J28" s="61" t="s">
-        <v>82</v>
+      <c r="J28" s="60" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="15.75">
@@ -2770,16 +2758,16 @@
         <v>11</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E29" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F29" s="40" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G29" s="16" t="s">
         <v>22</v>
@@ -2791,7 +2779,7 @@
         <v>9</v>
       </c>
       <c r="J29" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="15.75">
@@ -2802,16 +2790,16 @@
         <v>11</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E30" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F30" s="40" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G30" s="16" t="s">
         <v>22</v>
@@ -2823,7 +2811,7 @@
         <v>9</v>
       </c>
       <c r="J30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="15.75">
@@ -2834,16 +2822,16 @@
         <v>11</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D31" s="47" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E31" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F31" s="40" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G31" s="16" t="s">
         <v>22</v>
@@ -2855,7 +2843,7 @@
         <v>9</v>
       </c>
       <c r="J31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="15.75">
@@ -2866,16 +2854,16 @@
         <v>11</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D32" s="47" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E32" s="48" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="49" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G32" s="50" t="s">
         <v>22</v>
@@ -2887,7 +2875,7 @@
         <v>9</v>
       </c>
       <c r="J32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="15.75">
@@ -2898,16 +2886,16 @@
         <v>11</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D33" s="47" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E33" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="F33" s="67" t="s">
-        <v>159</v>
+      <c r="F33" s="66" t="s">
+        <v>158</v>
       </c>
       <c r="G33" s="50" t="s">
         <v>22</v>
@@ -2919,7 +2907,7 @@
         <v>9</v>
       </c>
       <c r="J33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="15.75">
@@ -2930,7 +2918,7 @@
         <v>11</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D34" s="18" t="s">
         <v>39</v>
@@ -2939,7 +2927,7 @@
         <v>29</v>
       </c>
       <c r="F34" s="49" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G34" s="16" t="s">
         <v>22</v>
@@ -2951,7 +2939,7 @@
         <v>9</v>
       </c>
       <c r="J34" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="15.75">
@@ -2962,16 +2950,16 @@
         <v>11</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D35" s="52" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E35" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F35" s="49" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G35" s="16" t="s">
         <v>22</v>
@@ -2983,7 +2971,7 @@
         <v>9</v>
       </c>
       <c r="J35" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="15.75">
@@ -2994,7 +2982,7 @@
         <v>11</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D36" s="18" t="s">
         <v>41</v>
@@ -3003,7 +2991,7 @@
         <v>29</v>
       </c>
       <c r="F36" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G36" s="16" t="s">
         <v>22</v>
@@ -3015,7 +3003,7 @@
         <v>9</v>
       </c>
       <c r="J36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="15.75">
@@ -3026,7 +3014,7 @@
         <v>11</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D37" s="18" t="s">
         <v>42</v>
@@ -3035,7 +3023,7 @@
         <v>29</v>
       </c>
       <c r="F37" s="49" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G37" s="16" t="s">
         <v>22</v>
@@ -3047,7 +3035,7 @@
         <v>9</v>
       </c>
       <c r="J37" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="15.75">
@@ -3058,7 +3046,7 @@
         <v>11</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D38" s="18" t="s">
         <v>43</v>
@@ -3067,7 +3055,7 @@
         <v>29</v>
       </c>
       <c r="F38" s="51" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G38" s="16" t="s">
         <v>22</v>
@@ -3079,7 +3067,7 @@
         <v>9</v>
       </c>
       <c r="J38" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="15.75">
@@ -3090,7 +3078,7 @@
         <v>11</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D39" s="18" t="s">
         <v>44</v>
@@ -3099,7 +3087,7 @@
         <v>29</v>
       </c>
       <c r="F39" s="51" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G39" s="16" t="s">
         <v>22</v>
@@ -3111,7 +3099,7 @@
         <v>9</v>
       </c>
       <c r="J39" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="15.75">
@@ -3122,16 +3110,16 @@
         <v>11</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E40" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F40" s="69" t="s">
-        <v>259</v>
+      <c r="F40" s="68" t="s">
+        <v>256</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>22</v>
@@ -3143,7 +3131,7 @@
         <v>9</v>
       </c>
       <c r="J40" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="15.75">
@@ -3154,16 +3142,16 @@
         <v>11</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E41" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F41" s="69" t="s">
-        <v>258</v>
+      <c r="F41" s="68" t="s">
+        <v>255</v>
       </c>
       <c r="G41" s="16" t="s">
         <v>22</v>
@@ -3175,7 +3163,7 @@
         <v>9</v>
       </c>
       <c r="J41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="57" customFormat="1" ht="15.75">
@@ -3186,7 +3174,7 @@
         <v>11</v>
       </c>
       <c r="C42" s="55" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D42" s="23" t="s">
         <v>47</v>
@@ -3205,7 +3193,7 @@
         <v>26</v>
       </c>
       <c r="J42" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="18.75">
@@ -3216,7 +3204,7 @@
         <v>11</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D43" s="22" t="s">
         <v>48</v>
@@ -3232,8 +3220,8 @@
       <c r="I43" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="J43" s="61" t="s">
-        <v>82</v>
+      <c r="J43" s="60" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="15.75">
@@ -3244,16 +3232,16 @@
         <v>11</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D44" s="18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E44" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F44" s="49" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>22</v>
@@ -3265,7 +3253,7 @@
         <v>26</v>
       </c>
       <c r="J44" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="15.75">
@@ -3276,16 +3264,16 @@
         <v>11</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E45" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F45" s="67" t="s">
-        <v>159</v>
+      <c r="F45" s="66" t="s">
+        <v>158</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>22</v>
@@ -3297,7 +3285,7 @@
         <v>26</v>
       </c>
       <c r="J45" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="15.75">
@@ -3308,7 +3296,7 @@
         <v>11</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D46" s="18" t="s">
         <v>39</v>
@@ -3317,7 +3305,7 @@
         <v>29</v>
       </c>
       <c r="F46" s="49" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G46" s="16" t="s">
         <v>22</v>
@@ -3329,7 +3317,7 @@
         <v>9</v>
       </c>
       <c r="J46" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="15.75">
@@ -3340,7 +3328,7 @@
         <v>11</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D47" s="18" t="s">
         <v>40</v>
@@ -3349,7 +3337,7 @@
         <v>29</v>
       </c>
       <c r="F47" s="49" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>22</v>
@@ -3361,7 +3349,7 @@
         <v>26</v>
       </c>
       <c r="J47" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="15.75">
@@ -3372,7 +3360,7 @@
         <v>11</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D48" s="18" t="s">
         <v>41</v>
@@ -3381,7 +3369,7 @@
         <v>29</v>
       </c>
       <c r="F48" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>22</v>
@@ -3393,7 +3381,7 @@
         <v>26</v>
       </c>
       <c r="J48" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="15.75">
@@ -3404,7 +3392,7 @@
         <v>11</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D49" s="18" t="s">
         <v>42</v>
@@ -3413,7 +3401,7 @@
         <v>29</v>
       </c>
       <c r="F49" s="49" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>22</v>
@@ -3425,7 +3413,7 @@
         <v>26</v>
       </c>
       <c r="J49" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="15.75">
@@ -3436,7 +3424,7 @@
         <v>11</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D50" s="25" t="s">
         <v>45</v>
@@ -3444,8 +3432,8 @@
       <c r="E50" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F50" s="69" t="s">
-        <v>259</v>
+      <c r="F50" s="68" t="s">
+        <v>256</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>22</v>
@@ -3457,7 +3445,7 @@
         <v>26</v>
       </c>
       <c r="J50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="15.75">
@@ -3468,7 +3456,7 @@
         <v>11</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D51" s="25" t="s">
         <v>46</v>
@@ -3476,8 +3464,8 @@
       <c r="E51" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F51" s="69" t="s">
-        <v>258</v>
+      <c r="F51" s="68" t="s">
+        <v>255</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>22</v>
@@ -3489,7 +3477,7 @@
         <v>26</v>
       </c>
       <c r="J51" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="52" spans="1:10" s="57" customFormat="1" ht="15.75">
@@ -3500,7 +3488,7 @@
         <v>11</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D52" s="23" t="s">
         <v>47</v>
@@ -3517,7 +3505,7 @@
         <v>26</v>
       </c>
       <c r="J52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="18.75">
@@ -3528,7 +3516,7 @@
         <v>11</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D53" s="22" t="s">
         <v>49</v>
@@ -3544,8 +3532,8 @@
       <c r="I53" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="J53" s="61" t="s">
-        <v>82</v>
+      <c r="J53" s="60" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="15.75">
@@ -3556,7 +3544,7 @@
         <v>11</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D54" s="18" t="s">
         <v>36</v>
@@ -3565,7 +3553,7 @@
         <v>29</v>
       </c>
       <c r="F54" s="40" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>22</v>
@@ -3577,7 +3565,7 @@
         <v>26</v>
       </c>
       <c r="J54" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="15.75">
@@ -3588,7 +3576,7 @@
         <v>11</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D55" s="18" t="s">
         <v>37</v>
@@ -3597,7 +3585,7 @@
         <v>29</v>
       </c>
       <c r="F55" s="40" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>22</v>
@@ -3609,7 +3597,7 @@
         <v>26</v>
       </c>
       <c r="J55" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="15.75">
@@ -3620,7 +3608,7 @@
         <v>11</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D56" s="18" t="s">
         <v>38</v>
@@ -3629,7 +3617,7 @@
         <v>29</v>
       </c>
       <c r="F56" s="40" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>22</v>
@@ -3641,7 +3629,7 @@
         <v>26</v>
       </c>
       <c r="J56" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="15.75">
@@ -3652,7 +3640,7 @@
         <v>11</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D57" s="18" t="s">
         <v>50</v>
@@ -3661,7 +3649,7 @@
         <v>29</v>
       </c>
       <c r="F57" s="49" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>22</v>
@@ -3673,7 +3661,7 @@
         <v>26</v>
       </c>
       <c r="J57" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="15.75">
@@ -3684,7 +3672,7 @@
         <v>11</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D58" s="18" t="s">
         <v>51</v>
@@ -3692,8 +3680,8 @@
       <c r="E58" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F58" s="67" t="s">
-        <v>159</v>
+      <c r="F58" s="66" t="s">
+        <v>158</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>22</v>
@@ -3705,7 +3693,7 @@
         <v>26</v>
       </c>
       <c r="J58" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="15.75">
@@ -3716,7 +3704,7 @@
         <v>11</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D59" s="18" t="s">
         <v>39</v>
@@ -3725,7 +3713,7 @@
         <v>29</v>
       </c>
       <c r="F59" s="49" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G59" s="16" t="s">
         <v>22</v>
@@ -3737,7 +3725,7 @@
         <v>9</v>
       </c>
       <c r="J59" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="15.75">
@@ -3748,16 +3736,16 @@
         <v>11</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="E60" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F60" s="49" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>22</v>
@@ -3769,7 +3757,7 @@
         <v>26</v>
       </c>
       <c r="J60" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="54" customHeight="1">
@@ -3780,7 +3768,7 @@
         <v>11</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D61" s="18" t="s">
         <v>52</v>
@@ -3788,8 +3776,8 @@
       <c r="E61" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F61" s="70" t="s">
-        <v>266</v>
+      <c r="F61" s="69" t="s">
+        <v>262</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>22</v>
@@ -3801,7 +3789,7 @@
         <v>26</v>
       </c>
       <c r="J61" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="51" customHeight="1">
@@ -3812,7 +3800,7 @@
         <v>11</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D62" s="18" t="s">
         <v>53</v>
@@ -3820,8 +3808,8 @@
       <c r="E62" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F62" s="70" t="s">
-        <v>267</v>
+      <c r="F62" s="69" t="s">
+        <v>263</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>22</v>
@@ -3833,7 +3821,7 @@
         <v>26</v>
       </c>
       <c r="J62" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="15.75">
@@ -3844,16 +3832,16 @@
         <v>11</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="E63" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F63" s="40" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="G63" s="16" t="s">
         <v>22</v>
@@ -3865,7 +3853,7 @@
         <v>9</v>
       </c>
       <c r="J63" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="15.75">
@@ -3876,16 +3864,16 @@
         <v>11</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="E64" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F64" s="72" t="s">
-        <v>321</v>
+      <c r="F64" s="71" t="s">
+        <v>308</v>
       </c>
       <c r="G64" s="16" t="s">
         <v>22</v>
@@ -3897,7 +3885,7 @@
         <v>9</v>
       </c>
       <c r="J64" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="15.75">
@@ -3908,7 +3896,7 @@
         <v>11</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D65" s="25" t="s">
         <v>45</v>
@@ -3916,8 +3904,8 @@
       <c r="E65" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F65" s="69" t="s">
-        <v>259</v>
+      <c r="F65" s="68" t="s">
+        <v>256</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>22</v>
@@ -3929,7 +3917,7 @@
         <v>26</v>
       </c>
       <c r="J65" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="15.75">
@@ -3940,7 +3928,7 @@
         <v>11</v>
       </c>
       <c r="C66" s="17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D66" s="25" t="s">
         <v>46</v>
@@ -3948,8 +3936,8 @@
       <c r="E66" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F66" s="69" t="s">
-        <v>258</v>
+      <c r="F66" s="68" t="s">
+        <v>255</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>22</v>
@@ -3961,7 +3949,7 @@
         <v>26</v>
       </c>
       <c r="J66" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="67" spans="1:10" s="57" customFormat="1" ht="15.75">
@@ -3972,7 +3960,7 @@
         <v>11</v>
       </c>
       <c r="C67" s="17" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D67" s="23" t="s">
         <v>47</v>
@@ -3989,7 +3977,7 @@
         <v>26</v>
       </c>
       <c r="J67" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="18.75">
@@ -4000,7 +3988,7 @@
         <v>11</v>
       </c>
       <c r="C68" s="17" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D68" s="22" t="s">
         <v>54</v>
@@ -4016,8 +4004,8 @@
       <c r="I68" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="J68" s="61" t="s">
-        <v>82</v>
+      <c r="J68" s="60" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="15.75">
@@ -4028,7 +4016,7 @@
         <v>11</v>
       </c>
       <c r="C69" s="17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D69" s="18" t="s">
         <v>55</v>
@@ -4037,7 +4025,7 @@
         <v>29</v>
       </c>
       <c r="F69" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>22</v>
@@ -4049,7 +4037,7 @@
         <v>9</v>
       </c>
       <c r="J69" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="15.75">
@@ -4060,7 +4048,7 @@
         <v>11</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D70" s="18" t="s">
         <v>56</v>
@@ -4069,7 +4057,7 @@
         <v>29</v>
       </c>
       <c r="F70" s="49" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>22</v>
@@ -4078,10 +4066,10 @@
         <v>23</v>
       </c>
       <c r="I70" s="26" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J70" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="31.5">
@@ -4092,16 +4080,16 @@
         <v>11</v>
       </c>
       <c r="C71" s="17" t="s">
-        <v>237</v>
-      </c>
-      <c r="D71" s="18" t="s">
-        <v>57</v>
+        <v>236</v>
+      </c>
+      <c r="D71" s="47" t="s">
+        <v>314</v>
       </c>
       <c r="E71" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F71" s="70" t="s">
-        <v>285</v>
+      <c r="F71" s="71" t="s">
+        <v>257</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>22</v>
@@ -4110,30 +4098,30 @@
         <v>23</v>
       </c>
       <c r="I71" s="26" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J71" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="31.5">
       <c r="A72" s="6">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="17" t="s">
-        <v>238</v>
-      </c>
-      <c r="D72" s="18" t="s">
-        <v>58</v>
+        <v>237</v>
+      </c>
+      <c r="D72" s="47" t="s">
+        <v>315</v>
       </c>
       <c r="E72" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F72" s="58" t="s">
-        <v>261</v>
+      <c r="F72" s="71" t="s">
+        <v>322</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>22</v>
@@ -4142,58 +4130,62 @@
         <v>23</v>
       </c>
       <c r="I72" s="26" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J72" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" ht="37.5">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="31.5">
       <c r="A73" s="6">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="D73" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="E73" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="F73" s="71" t="s">
+        <v>282</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I73" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="J73" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="31.5">
+      <c r="A74" s="6">
+        <v>67</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="D73" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="E73" s="29"/>
-      <c r="F73" s="44"/>
-      <c r="G73" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H73" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I73" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="J73" s="61" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" ht="15.75">
-      <c r="A74" s="6">
-        <v>69</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C74" s="17" t="s">
-        <v>240</v>
-      </c>
       <c r="D74" s="18" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E74" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="F74" s="40" t="s">
-        <v>170</v>
+      <c r="F74" s="71" t="s">
+        <v>321</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>22</v>
@@ -4205,147 +4197,143 @@
         <v>9</v>
       </c>
       <c r="J74" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="37.5">
+      <c r="A75" s="6">
+        <v>68</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="D75" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="E75" s="29"/>
+      <c r="F75" s="44"/>
+      <c r="G75" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H75" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I75" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="J75" s="60" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="75" spans="1:10" s="57" customFormat="1" ht="15.75">
-      <c r="A75" s="6">
+    <row r="76" spans="1:10" ht="15.75">
+      <c r="A76" s="6">
+        <v>69</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="D76" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E76" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="F76" s="40" t="s">
+        <v>169</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I76" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="J76" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" s="57" customFormat="1" ht="15.75">
+      <c r="A77" s="6">
         <v>70</v>
       </c>
-      <c r="B75" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="C75" s="17" t="s">
+      <c r="B77" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="C77" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="D77" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="E77" s="24"/>
+      <c r="F77" s="41"/>
+      <c r="G77" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="H77" s="56" t="s">
+        <v>23</v>
+      </c>
+      <c r="I77" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="J77" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="18.75">
+      <c r="A78" s="6">
+        <v>71</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="D75" s="23" t="s">
+      <c r="D78" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="E75" s="24"/>
-      <c r="F75" s="41"/>
-      <c r="G75" s="56" t="s">
-        <v>22</v>
-      </c>
-      <c r="H75" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="I75" s="53" t="s">
-        <v>26</v>
-      </c>
-      <c r="J75" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" ht="18.75">
-      <c r="A76" s="6">
-        <v>71</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C76" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="D76" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="E76" s="27"/>
-      <c r="F76" s="43"/>
-      <c r="G76" s="2" t="s">
+      <c r="E78" s="27"/>
+      <c r="F78" s="43"/>
+      <c r="G78" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H76" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I76" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="J76" s="61" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" ht="15.75">
-      <c r="A77" s="6">
-        <v>72</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C77" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="D77" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="E77" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="F77" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="G77" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H77" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I77" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="J77" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" ht="15.75">
-      <c r="A78" s="6">
-        <v>73</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C78" s="17" t="s">
-        <v>244</v>
-      </c>
-      <c r="D78" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="E78" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="F78" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="G78" s="16" t="s">
-        <v>22</v>
-      </c>
       <c r="H78" s="16" t="s">
         <v>23</v>
       </c>
       <c r="I78" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="J78" t="s">
+      <c r="J78" s="60" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="15.75">
       <c r="A79" s="6">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="17" t="s">
-        <v>245</v>
-      </c>
-      <c r="D79" s="18" t="s">
-        <v>65</v>
+        <v>242</v>
+      </c>
+      <c r="D79" s="30" t="s">
+        <v>62</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="F79" s="40" t="s">
-        <v>97</v>
+        <v>77</v>
+      </c>
+      <c r="F79" s="45" t="s">
+        <v>94</v>
       </c>
       <c r="G79" s="16" t="s">
         <v>22</v>
@@ -4357,27 +4345,27 @@
         <v>9</v>
       </c>
       <c r="J79" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="15.75">
       <c r="A80" s="6">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="17" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D80" s="18" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F80" s="40" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G80" s="16" t="s">
         <v>22</v>
@@ -4389,27 +4377,27 @@
         <v>9</v>
       </c>
       <c r="J80" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" ht="31.5">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="15.75">
       <c r="A81" s="6">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D81" s="18" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F81" s="40" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G81" s="16" t="s">
         <v>22</v>
@@ -4421,29 +4409,29 @@
         <v>9</v>
       </c>
       <c r="J81" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="15.75">
       <c r="A82" s="6">
+        <v>75</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="D82" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="E82" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="B82" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C82" s="17" t="s">
-        <v>248</v>
-      </c>
-      <c r="D82" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E82" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="F82" s="43" t="s">
-        <v>132</v>
-      </c>
-      <c r="G82" s="60" t="s">
+      <c r="F82" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="G82" s="16" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="16" t="s">
@@ -4453,61 +4441,61 @@
         <v>9</v>
       </c>
       <c r="J82" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" ht="15.75">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="31.5">
       <c r="A83" s="6">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C83" s="17" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D83" s="18" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F83" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I83" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="J83" s="61" t="s">
-        <v>82</v>
+        <v>98</v>
+      </c>
+      <c r="G83" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H83" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I83" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J83" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="15.75">
       <c r="A84" s="6">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>250</v>
-      </c>
-      <c r="D84" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="E84" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="F84" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="G84" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="D84" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="E84" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="F84" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="G84" s="59" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="16" t="s">
@@ -4517,61 +4505,61 @@
         <v>9</v>
       </c>
       <c r="J84" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="15.75">
       <c r="A85" s="6">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C85" s="17" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D85" s="18" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="F85" s="39" t="s">
-        <v>101</v>
-      </c>
-      <c r="G85" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H85" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I85" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="J85" t="s">
+        <v>77</v>
+      </c>
+      <c r="F85" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I85" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="J85" s="60" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="15.75">
       <c r="A86" s="6">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C86" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="D86" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="E86" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="F86" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="G86" s="60" t="s">
+        <v>249</v>
+      </c>
+      <c r="D86" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="F86" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="G86" s="16" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="16" t="s">
@@ -4581,155 +4569,155 @@
         <v>9</v>
       </c>
       <c r="J86" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="15.75">
       <c r="A87" s="6">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C87" s="17" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D87" s="18" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F87" s="40" t="s">
-        <v>130</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I87" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="J87" s="61" t="s">
-        <v>82</v>
+        <v>77</v>
+      </c>
+      <c r="F87" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="G87" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H87" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I87" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J87" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="15.75">
-      <c r="A88" s="81">
-        <v>83</v>
-      </c>
-      <c r="B88" s="82" t="s">
-        <v>11</v>
-      </c>
-      <c r="C88" s="83" t="s">
-        <v>254</v>
-      </c>
-      <c r="D88" s="84" t="s">
-        <v>73</v>
-      </c>
-      <c r="E88" s="85" t="s">
-        <v>78</v>
-      </c>
-      <c r="F88" s="86" t="s">
-        <v>98</v>
-      </c>
-      <c r="G88" s="87" t="s">
-        <v>22</v>
-      </c>
-      <c r="H88" s="87" t="s">
-        <v>23</v>
-      </c>
-      <c r="I88" s="83" t="s">
+      <c r="A88" s="6">
+        <v>81</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="D88" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E88" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="F88" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="G88" s="59" t="s">
+        <v>22</v>
+      </c>
+      <c r="H88" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I88" s="17" t="s">
         <v>9</v>
       </c>
       <c r="J88" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="15.75">
       <c r="A89" s="6">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C89" s="17" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D89" s="18" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="F89" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="G89" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H89" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I89" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="J89" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I89" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="J89" s="60" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="15.75">
-      <c r="A90" s="6">
-        <v>85</v>
-      </c>
-      <c r="B90" s="5" t="s">
+      <c r="A90" s="80">
+        <v>83</v>
+      </c>
+      <c r="B90" s="81" t="s">
         <v>11</v>
       </c>
       <c r="C90" s="17" t="s">
-        <v>256</v>
-      </c>
-      <c r="D90" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="E90" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="F90" s="43" t="s">
-        <v>132</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H90" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I90" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="J90" s="1" t="s">
-        <v>81</v>
+        <v>253</v>
+      </c>
+      <c r="D90" s="83" t="s">
+        <v>72</v>
+      </c>
+      <c r="E90" s="84" t="s">
+        <v>77</v>
+      </c>
+      <c r="F90" s="85" t="s">
+        <v>97</v>
+      </c>
+      <c r="G90" s="86" t="s">
+        <v>22</v>
+      </c>
+      <c r="H90" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="I90" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="J90" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="15.75">
       <c r="A91" s="6">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C91" s="17" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D91" s="18" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="F91" s="42" t="s">
-        <v>103</v>
+        <v>77</v>
+      </c>
+      <c r="F91" s="40" t="s">
+        <v>98</v>
       </c>
       <c r="G91" s="16" t="s">
         <v>22</v>
@@ -4741,39 +4729,103 @@
         <v>9</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="15.75">
       <c r="A92" s="6">
+        <v>85</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C92" s="17" t="s">
+        <v>312</v>
+      </c>
+      <c r="D92" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="E92" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="F92" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I92" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="15.75">
+      <c r="A93" s="6">
+        <v>86</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C93" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="D93" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="E93" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="F93" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="G93" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H93" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I93" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="15.75">
+      <c r="A94" s="6">
         <v>87</v>
       </c>
-      <c r="B92" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C92" s="26" t="s">
-        <v>325</v>
-      </c>
-      <c r="D92" s="18" t="s">
+      <c r="B94" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C94" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="D94" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E94" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="E92" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="F92" s="40" t="s">
-        <v>97</v>
-      </c>
-      <c r="G92" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H92" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I92" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="J92" s="1" t="s">
-        <v>81</v>
+      <c r="F94" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="G94" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H94" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I94" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -4785,7 +4837,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14526625-C6E6-4A6B-94C7-2E3FA4EA86BF}">
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
@@ -4803,1173 +4855,1129 @@
     <col min="13" max="13" width="16.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="68" customFormat="1" ht="30">
+    <row r="1" spans="1:13" s="67" customFormat="1" ht="30">
       <c r="A1" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>5</v>
       </c>
       <c r="D1" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="J1" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="K1" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="I1" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="J1" s="9" t="s">
+      <c r="L1" s="70" t="s">
+        <v>264</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="30">
+      <c r="A2" s="71" t="s">
         <v>180</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="B2" s="71" t="s">
+        <v>187</v>
+      </c>
+      <c r="C2" s="71" t="s">
+        <v>279</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="F2" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="G2" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="H2" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="I2" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="K2" s="32" t="s">
+        <v>274</v>
+      </c>
+      <c r="L2" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="30">
+      <c r="A3" s="71" t="s">
+        <v>180</v>
+      </c>
+      <c r="B3" s="71" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3" s="71" t="s">
+        <v>280</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="H3" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="I3" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="K3" s="32" t="s">
+        <v>274</v>
+      </c>
+      <c r="L3" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" s="8" customFormat="1">
+      <c r="A4" s="72" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" s="77" t="s">
+        <v>187</v>
+      </c>
+      <c r="C4" s="73" t="s">
+        <v>181</v>
+      </c>
+      <c r="D4" s="74" t="s">
+        <v>182</v>
+      </c>
+      <c r="E4" s="74" t="s">
+        <v>183</v>
+      </c>
+      <c r="F4" s="74" t="s">
+        <v>183</v>
+      </c>
+      <c r="G4" s="74" t="s">
+        <v>183</v>
+      </c>
+      <c r="H4" s="74" t="s">
+        <v>183</v>
+      </c>
+      <c r="I4" s="72" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
+      <c r="L4" s="74" t="s">
+        <v>268</v>
+      </c>
+      <c r="M4" s="78" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" s="8" customFormat="1">
+      <c r="A5" s="72" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" s="77" t="s">
+        <v>187</v>
+      </c>
+      <c r="C5" s="73" t="s">
+        <v>255</v>
+      </c>
+      <c r="D5" s="74" t="s">
+        <v>184</v>
+      </c>
+      <c r="E5" s="74" t="s">
+        <v>206</v>
+      </c>
+      <c r="F5" s="72" t="s">
+        <v>266</v>
+      </c>
+      <c r="G5" s="74" t="s">
+        <v>182</v>
+      </c>
+      <c r="H5" s="74" t="s">
         <v>174</v>
       </c>
-      <c r="L1" s="71" t="s">
+      <c r="I5" s="72" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="74" t="s">
         <v>268</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M5" s="78" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="30">
-      <c r="A2" s="72" t="s">
-        <v>181</v>
-      </c>
-      <c r="B2" s="72" t="s">
-        <v>188</v>
-      </c>
-      <c r="C2" s="72" t="s">
-        <v>283</v>
-      </c>
-      <c r="D2" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="E2" s="32" t="s">
+    <row r="6" spans="1:13" s="8" customFormat="1">
+      <c r="A6" s="72" t="s">
+        <v>180</v>
+      </c>
+      <c r="B6" s="77" t="s">
+        <v>187</v>
+      </c>
+      <c r="C6" s="73" t="s">
+        <v>256</v>
+      </c>
+      <c r="D6" s="74" t="s">
         <v>184</v>
       </c>
-      <c r="F2" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="G2" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="H2" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="I2" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="K2" s="32" t="s">
-        <v>278</v>
-      </c>
-      <c r="L2" s="72" t="s">
-        <v>272</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="30">
-      <c r="A3" s="72" t="s">
-        <v>181</v>
-      </c>
-      <c r="B3" s="72" t="s">
-        <v>188</v>
-      </c>
-      <c r="C3" s="72" t="s">
-        <v>284</v>
-      </c>
-      <c r="D3" s="32" t="s">
-        <v>281</v>
-      </c>
-      <c r="E3" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="F3" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="G3" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="H3" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="I3" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="K3" s="32" t="s">
-        <v>278</v>
-      </c>
-      <c r="L3" s="72" t="s">
-        <v>272</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" s="8" customFormat="1">
-      <c r="A4" s="73" t="s">
-        <v>181</v>
-      </c>
-      <c r="B4" s="78" t="s">
-        <v>188</v>
-      </c>
-      <c r="C4" s="74" t="s">
+      <c r="E6" s="74" t="s">
+        <v>205</v>
+      </c>
+      <c r="F6" s="72" t="s">
+        <v>266</v>
+      </c>
+      <c r="G6" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="D4" s="75" t="s">
-        <v>183</v>
-      </c>
-      <c r="E4" s="75" t="s">
-        <v>184</v>
-      </c>
-      <c r="F4" s="75" t="s">
-        <v>184</v>
-      </c>
-      <c r="G4" s="75" t="s">
-        <v>184</v>
-      </c>
-      <c r="H4" s="75" t="s">
-        <v>184</v>
-      </c>
-      <c r="I4" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="75" t="s">
-        <v>272</v>
-      </c>
-      <c r="M4" s="79" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" s="8" customFormat="1">
-      <c r="A5" s="73" t="s">
-        <v>181</v>
-      </c>
-      <c r="B5" s="78" t="s">
-        <v>188</v>
-      </c>
-      <c r="C5" s="74" t="s">
-        <v>258</v>
-      </c>
-      <c r="D5" s="75" t="s">
-        <v>185</v>
-      </c>
-      <c r="E5" s="75" t="s">
-        <v>207</v>
-      </c>
-      <c r="F5" s="73" t="s">
-        <v>270</v>
-      </c>
-      <c r="G5" s="75" t="s">
-        <v>183</v>
-      </c>
-      <c r="H5" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="I5" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="73"/>
-      <c r="K5" s="73"/>
-      <c r="L5" s="75" t="s">
-        <v>272</v>
-      </c>
-      <c r="M5" s="79" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" s="8" customFormat="1">
-      <c r="A6" s="73" t="s">
-        <v>181</v>
-      </c>
-      <c r="B6" s="78" t="s">
-        <v>188</v>
-      </c>
-      <c r="C6" s="74" t="s">
-        <v>259</v>
-      </c>
-      <c r="D6" s="75" t="s">
-        <v>185</v>
-      </c>
-      <c r="E6" s="75" t="s">
-        <v>206</v>
-      </c>
-      <c r="F6" s="73" t="s">
-        <v>270</v>
-      </c>
-      <c r="G6" s="75" t="s">
-        <v>183</v>
-      </c>
-      <c r="H6" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="I6" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="73"/>
-      <c r="K6" s="73"/>
-      <c r="L6" s="75" t="s">
-        <v>272</v>
-      </c>
-      <c r="M6" s="79" t="s">
-        <v>273</v>
+      <c r="H6" s="74" t="s">
+        <v>174</v>
+      </c>
+      <c r="I6" s="72" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="72"/>
+      <c r="K6" s="72"/>
+      <c r="L6" s="74" t="s">
+        <v>268</v>
+      </c>
+      <c r="M6" s="78" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="8" customFormat="1" ht="30">
       <c r="A7" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="B7" s="32" t="s">
         <v>189</v>
       </c>
-      <c r="B7" s="32" t="s">
-        <v>190</v>
-      </c>
-      <c r="C7" s="74" t="s">
-        <v>319</v>
-      </c>
-      <c r="D7" s="75" t="s">
-        <v>183</v>
+      <c r="C7" s="73" t="s">
+        <v>306</v>
+      </c>
+      <c r="D7" s="74" t="s">
+        <v>182</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F7" s="32" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I7" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J7" s="32" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K7" s="32" t="s">
-        <v>275</v>
-      </c>
-      <c r="L7" s="72" t="s">
-        <v>272</v>
+        <v>271</v>
+      </c>
+      <c r="L7" s="71" t="s">
+        <v>268</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="30">
       <c r="A8" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" s="32" t="s">
         <v>189</v>
       </c>
-      <c r="B8" s="32" t="s">
-        <v>190</v>
-      </c>
-      <c r="C8" s="72" t="s">
-        <v>320</v>
+      <c r="C8" s="71" t="s">
+        <v>307</v>
       </c>
       <c r="D8" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="E8" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="F8" s="72" t="s">
+        <v>266</v>
+      </c>
+      <c r="G8" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="E8" s="32" t="s">
-        <v>229</v>
-      </c>
-      <c r="F8" s="73" t="s">
-        <v>270</v>
-      </c>
-      <c r="G8" s="32" t="s">
-        <v>186</v>
-      </c>
       <c r="H8" s="32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I8" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="26" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="30">
       <c r="A9" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="B9" s="32" t="s">
         <v>189</v>
       </c>
-      <c r="B9" s="32" t="s">
-        <v>190</v>
-      </c>
-      <c r="C9" s="72" t="s">
-        <v>321</v>
+      <c r="C9" s="71" t="s">
+        <v>308</v>
       </c>
       <c r="D9" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="E9" s="32" t="s">
+        <v>229</v>
+      </c>
+      <c r="F9" s="72" t="s">
+        <v>266</v>
+      </c>
+      <c r="G9" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="E9" s="32" t="s">
-        <v>230</v>
-      </c>
-      <c r="F9" s="73" t="s">
-        <v>270</v>
-      </c>
-      <c r="G9" s="32" t="s">
-        <v>186</v>
-      </c>
       <c r="H9" s="32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I9" s="32" t="s">
         <v>22</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="26" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="30">
       <c r="A10" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="B10" s="32" t="s">
         <v>189</v>
       </c>
-      <c r="B10" s="32" t="s">
-        <v>190</v>
-      </c>
-      <c r="C10" s="72" t="s">
-        <v>306</v>
+      <c r="C10" s="71" t="s">
+        <v>301</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="E10" s="73" t="s">
-        <v>184</v>
-      </c>
-      <c r="F10" s="73" t="s">
-        <v>184</v>
-      </c>
-      <c r="G10" s="73" t="s">
-        <v>184</v>
-      </c>
-      <c r="H10" s="73" t="s">
-        <v>184</v>
+        <v>273</v>
+      </c>
+      <c r="E10" s="72" t="s">
+        <v>183</v>
+      </c>
+      <c r="F10" s="72" t="s">
+        <v>183</v>
+      </c>
+      <c r="G10" s="72" t="s">
+        <v>183</v>
+      </c>
+      <c r="H10" s="72" t="s">
+        <v>183</v>
       </c>
       <c r="I10" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="J10" s="73" t="s">
-        <v>184</v>
+      <c r="J10" s="72" t="s">
+        <v>183</v>
       </c>
       <c r="K10" s="32" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="L10" s="32" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="M10" s="26" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="30">
       <c r="A11" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="B11" s="32" t="s">
         <v>189</v>
       </c>
-      <c r="B11" s="32" t="s">
-        <v>190</v>
-      </c>
-      <c r="C11" s="72" t="s">
-        <v>307</v>
+      <c r="C11" s="71" t="s">
+        <v>302</v>
       </c>
       <c r="D11" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="E11" s="72" t="s">
+        <v>183</v>
+      </c>
+      <c r="F11" s="72" t="s">
+        <v>183</v>
+      </c>
+      <c r="G11" s="72" t="s">
+        <v>183</v>
+      </c>
+      <c r="H11" s="72" t="s">
+        <v>183</v>
+      </c>
+      <c r="I11" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="72" t="s">
+        <v>183</v>
+      </c>
+      <c r="K11" s="32" t="s">
+        <v>274</v>
+      </c>
+      <c r="L11" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="M11" s="26" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="71" t="s">
+        <v>259</v>
+      </c>
+      <c r="B12" s="71" t="s">
+        <v>260</v>
+      </c>
+      <c r="C12" s="71" t="s">
+        <v>261</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>226</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="G12" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="H12" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="I12" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="32" t="s">
+        <v>305</v>
+      </c>
+      <c r="K12" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="L12" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="M12" s="79" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="71" t="s">
+        <v>259</v>
+      </c>
+      <c r="B13" s="71" t="s">
+        <v>260</v>
+      </c>
+      <c r="C13" s="71" t="s">
+        <v>303</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="E13" s="32" t="s">
+        <v>227</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="G13" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="H13" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="I13" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="32" t="s">
+        <v>304</v>
+      </c>
+      <c r="K13" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="L13" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="M13" s="79" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="30">
+      <c r="A14" s="71" t="s">
+        <v>259</v>
+      </c>
+      <c r="B14" s="71" t="s">
+        <v>260</v>
+      </c>
+      <c r="C14" s="71" t="s">
+        <v>270</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="E14" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="F14" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="G14" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="H14" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="I14" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="K14" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="L14" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="30">
+      <c r="A15" s="71" t="s">
+        <v>259</v>
+      </c>
+      <c r="B15" s="71" t="s">
+        <v>260</v>
+      </c>
+      <c r="C15" s="71" t="s">
+        <v>272</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="E15" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="G15" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="H15" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="I15" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="K15" s="32" t="s">
+        <v>274</v>
+      </c>
+      <c r="L15" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="30">
+      <c r="A16" s="71" t="s">
+        <v>259</v>
+      </c>
+      <c r="B16" s="71" t="s">
+        <v>260</v>
+      </c>
+      <c r="C16" s="71" t="s">
+        <v>276</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="E16" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="G16" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="H16" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="I16" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="K16" s="32" t="s">
+        <v>274</v>
+      </c>
+      <c r="L16" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="30">
+      <c r="A17" s="71" t="s">
+        <v>284</v>
+      </c>
+      <c r="B17" s="71" t="s">
+        <v>300</v>
+      </c>
+      <c r="C17" s="71" t="s">
+        <v>297</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="E17" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="G17" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="H17" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="I17" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="K17" s="32" t="s">
+        <v>274</v>
+      </c>
+      <c r="L17" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="30">
+      <c r="A18" s="71" t="s">
+        <v>284</v>
+      </c>
+      <c r="B18" s="71" t="s">
+        <v>300</v>
+      </c>
+      <c r="C18" s="71" t="s">
+        <v>298</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="E18" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="F18" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="G18" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="H18" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="I18" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="K18" s="32" t="s">
+        <v>274</v>
+      </c>
+      <c r="L18" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="30">
+      <c r="A19" s="71" t="s">
+        <v>284</v>
+      </c>
+      <c r="B19" s="71" t="s">
+        <v>286</v>
+      </c>
+      <c r="C19" s="71" t="s">
+        <v>257</v>
+      </c>
+      <c r="D19" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="E11" s="73" t="s">
+      <c r="E19" s="70" t="s">
+        <v>236</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="G19" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="H19" s="70" t="s">
+        <v>174</v>
+      </c>
+      <c r="I19" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="K19" s="32"/>
+      <c r="L19" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="30">
+      <c r="A20" s="71" t="s">
+        <v>284</v>
+      </c>
+      <c r="B20" s="71" t="s">
+        <v>286</v>
+      </c>
+      <c r="C20" s="71" t="s">
+        <v>322</v>
+      </c>
+      <c r="D20" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="E20" s="70" t="s">
+        <v>237</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="G20" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="H20" s="70" t="s">
+        <v>174</v>
+      </c>
+      <c r="I20" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="30">
+      <c r="A21" s="71" t="s">
+        <v>285</v>
+      </c>
+      <c r="B21" s="71" t="s">
+        <v>287</v>
+      </c>
+      <c r="C21" s="71" t="s">
+        <v>320</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="E21" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="F21" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="G21" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="H21" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="I21" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="K21" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="L21" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="30">
+      <c r="A22" s="71" t="s">
+        <v>285</v>
+      </c>
+      <c r="B22" s="71" t="s">
+        <v>299</v>
+      </c>
+      <c r="C22" s="71" t="s">
+        <v>295</v>
+      </c>
+      <c r="D22" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="E22" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="F22" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="G22" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="H22" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="I22" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="K22" s="32" t="s">
+        <v>274</v>
+      </c>
+      <c r="L22" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="30">
+      <c r="A23" s="71" t="s">
+        <v>285</v>
+      </c>
+      <c r="B23" s="71" t="s">
+        <v>299</v>
+      </c>
+      <c r="C23" s="71" t="s">
+        <v>296</v>
+      </c>
+      <c r="D23" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="E23" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="F23" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="G23" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="H23" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="I23" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="K23" s="32" t="s">
+        <v>274</v>
+      </c>
+      <c r="L23" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="M23" s="9" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="45">
+      <c r="A24" s="71" t="s">
+        <v>285</v>
+      </c>
+      <c r="B24" s="71" t="s">
+        <v>287</v>
+      </c>
+      <c r="C24" s="71" t="s">
+        <v>282</v>
+      </c>
+      <c r="D24" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="E24" s="70" t="s">
+        <v>238</v>
+      </c>
+      <c r="F24" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="G24" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="H24" s="70" t="s">
+        <v>174</v>
+      </c>
+      <c r="I24" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="K24" s="1"/>
+      <c r="L24" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="M24" s="9" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="45">
+      <c r="A25" s="71" t="s">
+        <v>285</v>
+      </c>
+      <c r="B25" s="71" t="s">
+        <v>287</v>
+      </c>
+      <c r="C25" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="D25" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="E25" s="70" t="s">
+        <v>239</v>
+      </c>
+      <c r="F25" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="G25" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="H25" s="70" t="s">
+        <v>174</v>
+      </c>
+      <c r="I25" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="K25" s="1"/>
+      <c r="L25" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" s="67" customFormat="1" ht="30">
+      <c r="A26" s="32" t="s">
+        <v>288</v>
+      </c>
+      <c r="B26" s="32" t="s">
+        <v>289</v>
+      </c>
+      <c r="C26" s="71" t="s">
+        <v>293</v>
+      </c>
+      <c r="D26" s="32" t="s">
         <v>184</v>
       </c>
-      <c r="F11" s="73" t="s">
-        <v>184</v>
-      </c>
-      <c r="G11" s="73" t="s">
-        <v>184</v>
-      </c>
-      <c r="H11" s="73" t="s">
-        <v>184</v>
-      </c>
-      <c r="I11" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="73" t="s">
-        <v>184</v>
-      </c>
-      <c r="K11" s="32" t="s">
+      <c r="E26" s="70" t="s">
+        <v>235</v>
+      </c>
+      <c r="F26" s="70" t="s">
+        <v>266</v>
+      </c>
+      <c r="G26" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="H26" s="70" t="s">
+        <v>174</v>
+      </c>
+      <c r="I26" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="K26" s="32" t="s">
+        <v>294</v>
+      </c>
+      <c r="L26" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="M26" s="9" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="30">
+      <c r="A27" s="76" t="s">
+        <v>288</v>
+      </c>
+      <c r="B27" s="76" t="s">
+        <v>290</v>
+      </c>
+      <c r="C27" s="71" t="s">
+        <v>291</v>
+      </c>
+      <c r="D27" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="E27" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="F27" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="G27" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="H27" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="I27" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="K27" s="32" t="s">
+        <v>274</v>
+      </c>
+      <c r="L27" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="M27" s="9" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="30">
+      <c r="A28" s="76" t="s">
+        <v>288</v>
+      </c>
+      <c r="B28" s="76" t="s">
+        <v>290</v>
+      </c>
+      <c r="C28" s="71" t="s">
+        <v>292</v>
+      </c>
+      <c r="D28" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="E28" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="F28" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="G28" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="H28" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="I28" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="J28" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="K28" s="32" t="s">
+        <v>274</v>
+      </c>
+      <c r="L28" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="M28" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="L11" s="32" t="s">
-        <v>272</v>
-      </c>
-      <c r="M11" s="26" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="72" t="s">
-        <v>263</v>
-      </c>
-      <c r="B12" s="72" t="s">
-        <v>264</v>
-      </c>
-      <c r="C12" s="72" t="s">
-        <v>265</v>
-      </c>
-      <c r="D12" s="32" t="s">
-        <v>185</v>
-      </c>
-      <c r="E12" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="F12" s="32" t="s">
-        <v>270</v>
-      </c>
-      <c r="G12" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="H12" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="I12" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" s="32" t="s">
-        <v>318</v>
-      </c>
-      <c r="K12" s="32" t="s">
-        <v>271</v>
-      </c>
-      <c r="L12" s="32" t="s">
-        <v>272</v>
-      </c>
-      <c r="M12" s="80" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="72" t="s">
-        <v>263</v>
-      </c>
-      <c r="B13" s="72" t="s">
-        <v>264</v>
-      </c>
-      <c r="C13" s="72" t="s">
-        <v>316</v>
-      </c>
-      <c r="D13" s="32" t="s">
-        <v>185</v>
-      </c>
-      <c r="E13" s="32" t="s">
-        <v>228</v>
-      </c>
-      <c r="F13" s="32" t="s">
-        <v>270</v>
-      </c>
-      <c r="G13" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="H13" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="I13" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="32" t="s">
-        <v>317</v>
-      </c>
-      <c r="K13" s="32" t="s">
-        <v>271</v>
-      </c>
-      <c r="L13" s="32" t="s">
-        <v>272</v>
-      </c>
-      <c r="M13" s="80" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="30">
-      <c r="A14" s="72" t="s">
-        <v>263</v>
-      </c>
-      <c r="B14" s="72" t="s">
-        <v>264</v>
-      </c>
-      <c r="C14" s="72" t="s">
-        <v>274</v>
-      </c>
-      <c r="D14" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="E14" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="F14" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="G14" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="H14" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="I14" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="K14" s="32" t="s">
-        <v>275</v>
-      </c>
-      <c r="L14" s="72" t="s">
-        <v>272</v>
-      </c>
-      <c r="M14" s="9" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="30">
-      <c r="A15" s="72" t="s">
-        <v>263</v>
-      </c>
-      <c r="B15" s="72" t="s">
-        <v>264</v>
-      </c>
-      <c r="C15" s="72" t="s">
-        <v>276</v>
-      </c>
-      <c r="D15" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="E15" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="F15" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="G15" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="H15" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="I15" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J15" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="K15" s="32" t="s">
-        <v>278</v>
-      </c>
-      <c r="L15" s="72" t="s">
-        <v>272</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="30">
-      <c r="A16" s="72" t="s">
-        <v>263</v>
-      </c>
-      <c r="B16" s="72" t="s">
-        <v>264</v>
-      </c>
-      <c r="C16" s="72" t="s">
-        <v>280</v>
-      </c>
-      <c r="D16" s="32" t="s">
-        <v>281</v>
-      </c>
-      <c r="E16" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="F16" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="G16" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="H16" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="I16" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J16" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="K16" s="32" t="s">
-        <v>278</v>
-      </c>
-      <c r="L16" s="72" t="s">
-        <v>272</v>
-      </c>
-      <c r="M16" s="9" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="30">
-      <c r="A17" s="72" t="s">
-        <v>289</v>
-      </c>
-      <c r="B17" s="72" t="s">
-        <v>291</v>
-      </c>
-      <c r="C17" s="72" t="s">
-        <v>260</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>286</v>
-      </c>
-      <c r="E17" s="71" t="s">
-        <v>236</v>
-      </c>
-      <c r="F17" s="32" t="s">
-        <v>270</v>
-      </c>
-      <c r="G17" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="H17" s="71" t="s">
-        <v>175</v>
-      </c>
-      <c r="I17" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32" t="s">
-        <v>272</v>
-      </c>
-      <c r="M17" s="9" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="45">
-      <c r="A18" s="72" t="s">
-        <v>290</v>
-      </c>
-      <c r="B18" s="72" t="s">
-        <v>292</v>
-      </c>
-      <c r="C18" s="72" t="s">
-        <v>287</v>
-      </c>
-      <c r="D18" s="32" t="s">
-        <v>288</v>
-      </c>
-      <c r="E18" s="71" t="s">
-        <v>236</v>
-      </c>
-      <c r="F18" s="32" t="s">
-        <v>270</v>
-      </c>
-      <c r="G18" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="H18" s="71" t="s">
-        <v>175</v>
-      </c>
-      <c r="I18" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J18" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="K18" s="1"/>
-      <c r="L18" s="32" t="s">
-        <v>272</v>
-      </c>
-      <c r="M18" s="9" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="30">
-      <c r="A19" s="77" t="s">
-        <v>293</v>
-      </c>
-      <c r="B19" s="77" t="s">
-        <v>294</v>
-      </c>
-      <c r="C19" s="72" t="s">
-        <v>298</v>
-      </c>
-      <c r="D19" s="32" t="s">
-        <v>185</v>
-      </c>
-      <c r="E19" s="71" t="s">
-        <v>236</v>
-      </c>
-      <c r="F19" s="71" t="s">
-        <v>270</v>
-      </c>
-      <c r="G19" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="H19" s="71" t="s">
-        <v>175</v>
-      </c>
-      <c r="I19" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J19" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="K19" s="32" t="s">
-        <v>299</v>
-      </c>
-      <c r="L19" s="32" t="s">
-        <v>272</v>
-      </c>
-      <c r="M19" s="9" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="30">
-      <c r="A20" s="72" t="s">
-        <v>290</v>
-      </c>
-      <c r="B20" s="72" t="s">
-        <v>304</v>
-      </c>
-      <c r="C20" s="72" t="s">
-        <v>300</v>
-      </c>
-      <c r="D20" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="E20" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="F20" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="G20" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="H20" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="I20" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J20" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="K20" s="32" t="s">
-        <v>278</v>
-      </c>
-      <c r="L20" s="32" t="s">
-        <v>272</v>
-      </c>
-      <c r="M20" s="9" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="30">
-      <c r="A21" s="72" t="s">
-        <v>290</v>
-      </c>
-      <c r="B21" s="72" t="s">
-        <v>304</v>
-      </c>
-      <c r="C21" s="72" t="s">
-        <v>301</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>281</v>
-      </c>
-      <c r="E21" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="F21" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="G21" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="H21" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="I21" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J21" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="K21" s="32" t="s">
-        <v>278</v>
-      </c>
-      <c r="L21" s="32" t="s">
-        <v>272</v>
-      </c>
-      <c r="M21" s="9" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="30">
-      <c r="A22" s="72" t="s">
-        <v>289</v>
-      </c>
-      <c r="B22" s="72" t="s">
-        <v>305</v>
-      </c>
-      <c r="C22" s="72" t="s">
-        <v>302</v>
-      </c>
-      <c r="D22" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="E22" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="F22" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="G22" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="H22" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="I22" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J22" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="K22" s="32" t="s">
-        <v>278</v>
-      </c>
-      <c r="L22" s="32" t="s">
-        <v>272</v>
-      </c>
-      <c r="M22" s="9" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="30">
-      <c r="A23" s="72" t="s">
-        <v>289</v>
-      </c>
-      <c r="B23" s="72" t="s">
-        <v>305</v>
-      </c>
-      <c r="C23" s="72" t="s">
-        <v>303</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>281</v>
-      </c>
-      <c r="E23" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="F23" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="G23" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="H23" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="I23" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J23" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="K23" s="32" t="s">
-        <v>278</v>
-      </c>
-      <c r="L23" s="32" t="s">
-        <v>272</v>
-      </c>
-      <c r="M23" s="9" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="30">
-      <c r="A24" s="77" t="s">
-        <v>293</v>
-      </c>
-      <c r="B24" s="77" t="s">
-        <v>295</v>
-      </c>
-      <c r="C24" s="72" t="s">
-        <v>296</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="E24" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="F24" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="G24" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="H24" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="I24" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J24" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="K24" s="32" t="s">
-        <v>278</v>
-      </c>
-      <c r="L24" s="32" t="s">
-        <v>272</v>
-      </c>
-      <c r="M24" s="9" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="30">
-      <c r="A25" s="77" t="s">
-        <v>293</v>
-      </c>
-      <c r="B25" s="77" t="s">
-        <v>295</v>
-      </c>
-      <c r="C25" s="72" t="s">
-        <v>297</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>281</v>
-      </c>
-      <c r="E25" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="F25" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="G25" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="H25" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="I25" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J25" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="K25" s="32" t="s">
-        <v>278</v>
-      </c>
-      <c r="L25" s="32" t="s">
-        <v>272</v>
-      </c>
-      <c r="M25" s="9" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="30">
-      <c r="A26" s="72" t="s">
-        <v>314</v>
-      </c>
-      <c r="B26" s="72" t="s">
-        <v>315</v>
-      </c>
-      <c r="C26" s="72" t="s">
-        <v>308</v>
-      </c>
-      <c r="D26" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="E26" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="F26" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="G26" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="H26" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="I26" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J26" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="K26" s="32" t="s">
-        <v>275</v>
-      </c>
-      <c r="L26" s="32" t="s">
-        <v>272</v>
-      </c>
-      <c r="M26" s="9" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="30">
-      <c r="A27" s="72" t="s">
-        <v>314</v>
-      </c>
-      <c r="B27" s="72" t="s">
-        <v>315</v>
-      </c>
-      <c r="C27" s="72" t="s">
-        <v>309</v>
-      </c>
-      <c r="D27" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="E27" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="F27" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="G27" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="H27" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="I27" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J27" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="K27" s="32" t="s">
-        <v>278</v>
-      </c>
-      <c r="L27" s="32" t="s">
-        <v>272</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="30">
-      <c r="A28" s="72" t="s">
-        <v>314</v>
-      </c>
-      <c r="B28" s="72" t="s">
-        <v>315</v>
-      </c>
-      <c r="C28" s="72" t="s">
-        <v>310</v>
-      </c>
-      <c r="D28" s="32" t="s">
-        <v>281</v>
-      </c>
-      <c r="E28" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="F28" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="G28" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="H28" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="I28" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J28" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="K28" s="32" t="s">
-        <v>278</v>
-      </c>
-      <c r="L28" s="32" t="s">
-        <v>272</v>
-      </c>
-      <c r="M28" s="9" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
-      <c r="A29" s="72" t="s">
-        <v>314</v>
-      </c>
-      <c r="B29" s="72" t="s">
-        <v>315</v>
-      </c>
-      <c r="C29" s="72" t="s">
-        <v>311</v>
-      </c>
-      <c r="D29" s="32" t="s">
-        <v>185</v>
-      </c>
-      <c r="E29" s="71" t="s">
-        <v>237</v>
-      </c>
-      <c r="F29" s="71" t="s">
-        <v>270</v>
-      </c>
-      <c r="G29" s="71" t="s">
-        <v>183</v>
-      </c>
-      <c r="H29" s="71" t="s">
-        <v>175</v>
-      </c>
-      <c r="I29" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J29" s="32" t="s">
-        <v>312</v>
-      </c>
-      <c r="K29" s="32" t="s">
-        <v>313</v>
-      </c>
-      <c r="L29" s="32" t="s">
-        <v>272</v>
-      </c>
-      <c r="M29" s="9" t="s">
-        <v>273</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M29" xr:uid="{14526625-C6E6-4A6B-94C7-2E3FA4EA86BF}"/>
+  <autoFilter ref="A1:M28" xr:uid="{14526625-C6E6-4A6B-94C7-2E3FA4EA86BF}"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
